--- a/Audit Report/COMPARISION/PVT LTD/APP EXPORT.xlsx
+++ b/Audit Report/COMPARISION/PVT LTD/APP EXPORT.xlsx
@@ -5,7 +5,7 @@
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <xr:revisionPtr revIDLastSave="1" documentId="11_25914483A7F1B39CFE0ABEEE9C55BBA4CB7D5AAE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DACA520B-D9D7-4196-95F1-04160E637EE5}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14856" firstSheet="2" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14856" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="00_Cover" sheetId="1" r:id="rId1"/>
@@ -109,7 +109,6 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="11">'Notes other2'!$1:$3</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -6816,6 +6815,72 @@
     <xf numFmtId="0" fontId="20" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="57" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="57" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="48" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="48" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="175" fontId="57" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="175" fontId="57" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="174" fontId="57" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="174" fontId="57" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="57" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="57" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="174" fontId="48" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="174" fontId="48" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="70" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="70" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="47" fillId="10" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -6834,90 +6899,30 @@
     <xf numFmtId="0" fontId="47" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="70" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="70" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="69" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="69" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="174" fontId="48" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="174" fontId="48" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="48" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="48" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="174" fontId="57" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="174" fontId="57" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="57" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="57" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="175" fontId="57" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="175" fontId="57" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="57" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="57" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="164" fontId="10" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -6929,30 +6934,102 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="6" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="164" fontId="13" fillId="6" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="6" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="12" fillId="6" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -6981,21 +7058,6 @@
     <xf numFmtId="0" fontId="14" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="6" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="6" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="6" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -7003,69 +7065,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -7083,6 +7082,16 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="167" fontId="22" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="167" fontId="22" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -7106,19 +7115,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="22" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="167" fontId="22" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -7134,11 +7130,77 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="justify" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="43" fontId="41" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="35" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -7151,7 +7213,6 @@
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="35" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -7161,18 +7222,24 @@
     <xf numFmtId="43" fontId="48" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
+    <xf numFmtId="1" fontId="52" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="31" fillId="0" borderId="57" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="58" xfId="0" applyBorder="1"/>
+    <xf numFmtId="1" fontId="19" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -7209,77 +7276,20 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="1" fontId="52" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="31" fillId="0" borderId="57" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="58" xfId="0" applyBorder="1"/>
-    <xf numFmtId="1" fontId="19" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="19" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="19" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="31" fillId="0" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -7304,74 +7314,45 @@
     <xf numFmtId="165" fontId="31" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="19" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="19" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="65" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="165" fontId="22" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -7384,6 +7365,33 @@
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -7393,14 +7401,11 @@
     <xf numFmtId="43" fontId="35" fillId="0" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    <xf numFmtId="170" fontId="28" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="170" fontId="28" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="170" fontId="28" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -7414,30 +7419,24 @@
     <xf numFmtId="0" fontId="28" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="170" fontId="28" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="170" fontId="28" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="76" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="21" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="76" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -7894,10 +7893,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
@@ -8198,291 +8193,325 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="28.2" customHeight="1">
-      <c r="A1" s="710" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="711"/>
-      <c r="C1" s="711"/>
-      <c r="D1" s="711"/>
-      <c r="E1" s="711"/>
-      <c r="F1" s="711"/>
-      <c r="G1" s="711"/>
-      <c r="H1" s="711"/>
+      <c r="A1" s="727" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="728"/>
+      <c r="C1" s="728"/>
+      <c r="D1" s="728"/>
+      <c r="E1" s="728"/>
+      <c r="F1" s="728"/>
+      <c r="G1" s="728"/>
+      <c r="H1" s="728"/>
     </row>
     <row r="2" spans="1:8" ht="19.95" customHeight="1">
-      <c r="A2" s="712" t="s">
+      <c r="A2" s="729" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="713"/>
-      <c r="C2" s="713"/>
-      <c r="D2" s="713"/>
-      <c r="E2" s="713"/>
-      <c r="F2" s="713"/>
-      <c r="G2" s="713"/>
-      <c r="H2" s="713"/>
+      <c r="B2" s="730"/>
+      <c r="C2" s="730"/>
+      <c r="D2" s="730"/>
+      <c r="E2" s="730"/>
+      <c r="F2" s="730"/>
+      <c r="G2" s="730"/>
+      <c r="H2" s="730"/>
     </row>
     <row r="3" spans="1:8" ht="4.95" customHeight="1">
-      <c r="A3" s="714"/>
-      <c r="B3" s="715"/>
-      <c r="C3" s="715"/>
-      <c r="D3" s="715"/>
-      <c r="E3" s="715"/>
-      <c r="F3" s="715"/>
-      <c r="G3" s="715"/>
-      <c r="H3" s="715"/>
+      <c r="A3" s="731"/>
+      <c r="B3" s="732"/>
+      <c r="C3" s="732"/>
+      <c r="D3" s="732"/>
+      <c r="E3" s="732"/>
+      <c r="F3" s="732"/>
+      <c r="G3" s="732"/>
+      <c r="H3" s="732"/>
     </row>
     <row r="5" spans="1:8" ht="22.2" customHeight="1">
-      <c r="B5" s="716" t="s">
+      <c r="B5" s="733" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="717"/>
-      <c r="D5" s="717"/>
-      <c r="E5" s="718" t="s">
+      <c r="C5" s="734"/>
+      <c r="D5" s="734"/>
+      <c r="E5" s="735" t="s">
         <v>3</v>
       </c>
-      <c r="F5" s="717"/>
-      <c r="G5" s="717"/>
+      <c r="F5" s="734"/>
+      <c r="G5" s="734"/>
     </row>
     <row r="6" spans="1:8" ht="19.95" customHeight="1">
-      <c r="B6" s="719" t="s">
+      <c r="B6" s="721" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="720"/>
-      <c r="D6" s="721"/>
-      <c r="E6" s="722" t="s">
+      <c r="C6" s="722"/>
+      <c r="D6" s="723"/>
+      <c r="E6" s="724" t="s">
         <v>5</v>
       </c>
-      <c r="F6" s="723"/>
-      <c r="G6" s="724"/>
+      <c r="F6" s="725"/>
+      <c r="G6" s="726"/>
     </row>
     <row r="7" spans="1:8" ht="19.95" customHeight="1">
-      <c r="B7" s="725" t="s">
+      <c r="B7" s="717" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="726"/>
-      <c r="D7" s="727"/>
-      <c r="E7" s="728" t="s">
+      <c r="C7" s="718"/>
+      <c r="D7" s="719"/>
+      <c r="E7" s="720" t="s">
         <v>7</v>
       </c>
-      <c r="F7" s="726"/>
-      <c r="G7" s="727"/>
+      <c r="F7" s="718"/>
+      <c r="G7" s="719"/>
     </row>
     <row r="8" spans="1:8" ht="19.95" customHeight="1">
-      <c r="B8" s="725" t="s">
+      <c r="B8" s="717" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="726"/>
-      <c r="D8" s="727"/>
-      <c r="E8" s="728" t="s">
+      <c r="C8" s="718"/>
+      <c r="D8" s="719"/>
+      <c r="E8" s="720" t="s">
         <v>9</v>
       </c>
-      <c r="F8" s="726"/>
-      <c r="G8" s="727"/>
+      <c r="F8" s="718"/>
+      <c r="G8" s="719"/>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1">
-      <c r="B9" s="725" t="s">
+      <c r="B9" s="717" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="726"/>
-      <c r="D9" s="727"/>
-      <c r="E9" s="728" t="s">
+      <c r="C9" s="718"/>
+      <c r="D9" s="719"/>
+      <c r="E9" s="720" t="s">
         <v>11</v>
       </c>
-      <c r="F9" s="726"/>
-      <c r="G9" s="727"/>
+      <c r="F9" s="718"/>
+      <c r="G9" s="719"/>
     </row>
     <row r="10" spans="1:8" ht="30" customHeight="1">
-      <c r="B10" s="725" t="s">
+      <c r="B10" s="717" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="726"/>
-      <c r="D10" s="727"/>
-      <c r="E10" s="728" t="s">
+      <c r="C10" s="718"/>
+      <c r="D10" s="719"/>
+      <c r="E10" s="720" t="s">
         <v>13</v>
       </c>
-      <c r="F10" s="726"/>
-      <c r="G10" s="727"/>
+      <c r="F10" s="718"/>
+      <c r="G10" s="719"/>
     </row>
     <row r="11" spans="1:8" ht="19.95" customHeight="1">
-      <c r="B11" s="725" t="s">
+      <c r="B11" s="717" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="726"/>
-      <c r="D11" s="727"/>
-      <c r="E11" s="728" t="s">
+      <c r="C11" s="718"/>
+      <c r="D11" s="719"/>
+      <c r="E11" s="720" t="s">
         <v>15</v>
       </c>
-      <c r="F11" s="726"/>
-      <c r="G11" s="727"/>
+      <c r="F11" s="718"/>
+      <c r="G11" s="719"/>
     </row>
     <row r="12" spans="1:8" ht="19.95" customHeight="1">
-      <c r="B12" s="729" t="s">
+      <c r="B12" s="712" t="s">
         <v>16</v>
       </c>
-      <c r="C12" s="730"/>
-      <c r="D12" s="731"/>
-      <c r="E12" s="732" t="s">
+      <c r="C12" s="713"/>
+      <c r="D12" s="714"/>
+      <c r="E12" s="715" t="s">
         <v>17</v>
       </c>
-      <c r="F12" s="730"/>
-      <c r="G12" s="731"/>
+      <c r="F12" s="713"/>
+      <c r="G12" s="714"/>
     </row>
     <row r="15" spans="1:8" ht="22.2" customHeight="1">
-      <c r="B15" s="733" t="s">
+      <c r="B15" s="716" t="s">
         <v>18</v>
       </c>
-      <c r="C15" s="733"/>
-      <c r="D15" s="733"/>
-      <c r="E15" s="733"/>
-      <c r="F15" s="733"/>
-      <c r="G15" s="733"/>
+      <c r="C15" s="716"/>
+      <c r="D15" s="716"/>
+      <c r="E15" s="716"/>
+      <c r="F15" s="716"/>
+      <c r="G15" s="716"/>
     </row>
     <row r="16" spans="1:8" ht="15" customHeight="1">
-      <c r="B16" s="734" t="s">
+      <c r="B16" s="710" t="s">
         <v>19</v>
       </c>
-      <c r="C16" s="734"/>
-      <c r="D16" s="734"/>
-      <c r="E16" s="735" t="s">
+      <c r="C16" s="710"/>
+      <c r="D16" s="710"/>
+      <c r="E16" s="711" t="s">
         <v>20</v>
       </c>
-      <c r="F16" s="735"/>
-      <c r="G16" s="735"/>
+      <c r="F16" s="711"/>
+      <c r="G16" s="711"/>
     </row>
     <row r="17" spans="2:7" ht="15" customHeight="1">
-      <c r="B17" s="734" t="s">
+      <c r="B17" s="710" t="s">
         <v>21</v>
       </c>
-      <c r="C17" s="734"/>
-      <c r="D17" s="734"/>
-      <c r="E17" s="735" t="s">
+      <c r="C17" s="710"/>
+      <c r="D17" s="710"/>
+      <c r="E17" s="711" t="s">
         <v>22</v>
       </c>
-      <c r="F17" s="735"/>
-      <c r="G17" s="735"/>
+      <c r="F17" s="711"/>
+      <c r="G17" s="711"/>
     </row>
     <row r="18" spans="2:7" ht="15" customHeight="1">
-      <c r="B18" s="734" t="s">
+      <c r="B18" s="710" t="s">
         <v>23</v>
       </c>
-      <c r="C18" s="734"/>
-      <c r="D18" s="734"/>
-      <c r="E18" s="735" t="s">
+      <c r="C18" s="710"/>
+      <c r="D18" s="710"/>
+      <c r="E18" s="711" t="s">
         <v>24</v>
       </c>
-      <c r="F18" s="735"/>
-      <c r="G18" s="735"/>
+      <c r="F18" s="711"/>
+      <c r="G18" s="711"/>
     </row>
     <row r="19" spans="2:7" ht="15" customHeight="1">
-      <c r="B19" s="734" t="s">
+      <c r="B19" s="710" t="s">
         <v>25</v>
       </c>
-      <c r="C19" s="734"/>
-      <c r="D19" s="734"/>
-      <c r="E19" s="735" t="s">
+      <c r="C19" s="710"/>
+      <c r="D19" s="710"/>
+      <c r="E19" s="711" t="s">
         <v>26</v>
       </c>
-      <c r="F19" s="735"/>
-      <c r="G19" s="735"/>
+      <c r="F19" s="711"/>
+      <c r="G19" s="711"/>
     </row>
     <row r="20" spans="2:7" ht="15" customHeight="1">
-      <c r="B20" s="734" t="s">
+      <c r="B20" s="710" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="734"/>
-      <c r="D20" s="734"/>
-      <c r="E20" s="735" t="s">
+      <c r="C20" s="710"/>
+      <c r="D20" s="710"/>
+      <c r="E20" s="711" t="s">
         <v>28</v>
       </c>
-      <c r="F20" s="735"/>
-      <c r="G20" s="735"/>
+      <c r="F20" s="711"/>
+      <c r="G20" s="711"/>
     </row>
     <row r="21" spans="2:7" ht="15" customHeight="1">
-      <c r="B21" s="734" t="s">
+      <c r="B21" s="710" t="s">
         <v>29</v>
       </c>
-      <c r="C21" s="734"/>
-      <c r="D21" s="734"/>
-      <c r="E21" s="735" t="s">
+      <c r="C21" s="710"/>
+      <c r="D21" s="710"/>
+      <c r="E21" s="711" t="s">
         <v>30</v>
       </c>
-      <c r="F21" s="735"/>
-      <c r="G21" s="735"/>
+      <c r="F21" s="711"/>
+      <c r="G21" s="711"/>
     </row>
     <row r="22" spans="2:7" ht="15" customHeight="1">
-      <c r="B22" s="734" t="s">
+      <c r="B22" s="710" t="s">
         <v>31</v>
       </c>
-      <c r="C22" s="734"/>
-      <c r="D22" s="734"/>
-      <c r="E22" s="735" t="s">
+      <c r="C22" s="710"/>
+      <c r="D22" s="710"/>
+      <c r="E22" s="711" t="s">
         <v>32</v>
       </c>
-      <c r="F22" s="735"/>
-      <c r="G22" s="735"/>
+      <c r="F22" s="711"/>
+      <c r="G22" s="711"/>
     </row>
     <row r="23" spans="2:7">
-      <c r="B23" s="734" t="s">
+      <c r="B23" s="710" t="s">
         <v>33</v>
       </c>
-      <c r="C23" s="734"/>
-      <c r="D23" s="734"/>
-      <c r="E23" s="735" t="s">
+      <c r="C23" s="710"/>
+      <c r="D23" s="710"/>
+      <c r="E23" s="711" t="s">
         <v>34</v>
       </c>
-      <c r="F23" s="735"/>
-      <c r="G23" s="735"/>
+      <c r="F23" s="711"/>
+      <c r="G23" s="711"/>
     </row>
     <row r="24" spans="2:7" ht="15" customHeight="1">
-      <c r="B24" s="734" t="s">
+      <c r="B24" s="710" t="s">
         <v>35</v>
       </c>
-      <c r="C24" s="734"/>
-      <c r="D24" s="734"/>
-      <c r="E24" s="735" t="s">
+      <c r="C24" s="710"/>
+      <c r="D24" s="710"/>
+      <c r="E24" s="711" t="s">
         <v>36</v>
       </c>
-      <c r="F24" s="735"/>
-      <c r="G24" s="735"/>
+      <c r="F24" s="711"/>
+      <c r="G24" s="711"/>
     </row>
     <row r="25" spans="2:7" ht="25.95" customHeight="1">
-      <c r="B25" s="734" t="s">
+      <c r="B25" s="710" t="s">
         <v>37</v>
       </c>
-      <c r="C25" s="734"/>
-      <c r="D25" s="734"/>
-      <c r="E25" s="735" t="s">
+      <c r="C25" s="710"/>
+      <c r="D25" s="710"/>
+      <c r="E25" s="711" t="s">
         <v>24</v>
       </c>
-      <c r="F25" s="735"/>
-      <c r="G25" s="735"/>
+      <c r="F25" s="711"/>
+      <c r="G25" s="711"/>
     </row>
     <row r="26" spans="2:7">
-      <c r="B26" s="734" t="s">
+      <c r="B26" s="710" t="s">
         <v>38</v>
       </c>
-      <c r="C26" s="734"/>
-      <c r="D26" s="734"/>
-      <c r="E26" s="735" t="s">
+      <c r="C26" s="710"/>
+      <c r="D26" s="710"/>
+      <c r="E26" s="711" t="s">
         <v>24</v>
       </c>
-      <c r="F26" s="735"/>
-      <c r="G26" s="735"/>
+      <c r="F26" s="711"/>
+      <c r="G26" s="711"/>
     </row>
     <row r="27" spans="2:7">
-      <c r="B27" s="734" t="s">
+      <c r="B27" s="710" t="s">
         <v>39</v>
       </c>
-      <c r="C27" s="734"/>
-      <c r="D27" s="734"/>
-      <c r="E27" s="735" t="s">
+      <c r="C27" s="710"/>
+      <c r="D27" s="710"/>
+      <c r="E27" s="711" t="s">
         <v>24</v>
       </c>
-      <c r="F27" s="735"/>
-      <c r="G27" s="735"/>
+      <c r="F27" s="711"/>
+      <c r="G27" s="711"/>
     </row>
   </sheetData>
   <mergeCells count="44">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="E5:G5"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="E6:G6"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="E7:G7"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="E8:G8"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="E9:G9"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="E10:G10"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="E11:G11"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="E12:G12"/>
+    <mergeCell ref="B15:G15"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="E16:G16"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="E17:G17"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="E18:G18"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="E19:G19"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="E20:G20"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="E21:G21"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="E22:G22"/>
     <mergeCell ref="B26:D26"/>
     <mergeCell ref="E26:G26"/>
     <mergeCell ref="B27:D27"/>
@@ -8493,40 +8522,6 @@
     <mergeCell ref="E24:G24"/>
     <mergeCell ref="B25:D25"/>
     <mergeCell ref="E25:G25"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="E20:G20"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="E21:G21"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="E22:G22"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="E17:G17"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="E18:G18"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="E19:G19"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="E12:G12"/>
-    <mergeCell ref="B15:G15"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="E16:G16"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="E9:G9"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="E10:G10"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="E11:G11"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="E6:G6"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="E7:G7"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="E8:G8"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="E5:G5"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.35" right="0.35" top="0.55000000000000004" bottom="0.55000000000000004" header="0.2" footer="0.2"/>
@@ -8562,16 +8557,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A1" s="890" t="str">
+      <c r="A1" s="901" t="str">
         <f>BS!B2</f>
         <v>KWIKTEAM SUPPORT SERVICES PVT LTD</v>
       </c>
-      <c r="B1" s="890"/>
-      <c r="C1" s="890"/>
-      <c r="D1" s="890"/>
-      <c r="E1" s="890"/>
-      <c r="F1" s="890"/>
-      <c r="G1" s="890"/>
+      <c r="B1" s="901"/>
+      <c r="C1" s="901"/>
+      <c r="D1" s="901"/>
+      <c r="E1" s="901"/>
+      <c r="F1" s="901"/>
+      <c r="G1" s="901"/>
       <c r="H1" s="120"/>
       <c r="I1" s="120"/>
     </row>
@@ -8597,15 +8592,15 @@
       </c>
     </row>
     <row r="3" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A3" s="781" t="s">
+      <c r="A3" s="785" t="s">
         <v>461</v>
       </c>
-      <c r="B3" s="781"/>
-      <c r="C3" s="781"/>
-      <c r="D3" s="781"/>
-      <c r="E3" s="781"/>
-      <c r="F3" s="781"/>
-      <c r="G3" s="781"/>
+      <c r="B3" s="785"/>
+      <c r="C3" s="785"/>
+      <c r="D3" s="785"/>
+      <c r="E3" s="785"/>
+      <c r="F3" s="785"/>
+      <c r="G3" s="785"/>
       <c r="H3" s="120"/>
       <c r="I3" s="120"/>
     </row>
@@ -8641,12 +8636,12 @@
     </row>
     <row r="6" spans="1:11" ht="30" customHeight="1">
       <c r="A6" s="480"/>
-      <c r="B6" s="891" t="s">
+      <c r="B6" s="890" t="s">
         <v>134</v>
       </c>
-      <c r="C6" s="891"/>
-      <c r="D6" s="891"/>
-      <c r="E6" s="891"/>
+      <c r="C6" s="890"/>
+      <c r="D6" s="890"/>
+      <c r="E6" s="890"/>
       <c r="F6" s="481" t="s">
         <v>462</v>
       </c>
@@ -8720,10 +8715,10 @@
     </row>
     <row r="11" spans="1:11" ht="13.95" customHeight="1">
       <c r="A11" s="479"/>
-      <c r="B11" s="892" t="s">
+      <c r="B11" s="899" t="s">
         <v>310</v>
       </c>
-      <c r="C11" s="840"/>
+      <c r="C11" s="807"/>
       <c r="D11" s="321"/>
       <c r="E11" s="322"/>
       <c r="F11" s="323">
@@ -8766,12 +8761,12 @@
     </row>
     <row r="14" spans="1:11" ht="30" customHeight="1">
       <c r="A14" s="480"/>
-      <c r="B14" s="893" t="s">
+      <c r="B14" s="896" t="s">
         <v>134</v>
       </c>
-      <c r="C14" s="894"/>
-      <c r="D14" s="894"/>
-      <c r="E14" s="895"/>
+      <c r="C14" s="897"/>
+      <c r="D14" s="897"/>
+      <c r="E14" s="898"/>
       <c r="F14" s="488" t="str">
         <f>+F6</f>
         <v xml:space="preserve"> For the year ended 31 March, 2026</v>
@@ -8845,10 +8840,10 @@
     </row>
     <row r="19" spans="1:9" ht="13.95" customHeight="1">
       <c r="A19" s="479"/>
-      <c r="B19" s="892" t="s">
+      <c r="B19" s="899" t="s">
         <v>310</v>
       </c>
-      <c r="C19" s="840"/>
+      <c r="C19" s="807"/>
       <c r="D19" s="321"/>
       <c r="E19" s="322"/>
       <c r="F19" s="323">
@@ -8891,12 +8886,12 @@
     </row>
     <row r="22" spans="1:9" ht="30" customHeight="1">
       <c r="A22" s="480"/>
-      <c r="B22" s="893" t="s">
+      <c r="B22" s="896" t="s">
         <v>134</v>
       </c>
-      <c r="C22" s="894"/>
-      <c r="D22" s="894"/>
-      <c r="E22" s="895"/>
+      <c r="C22" s="897"/>
+      <c r="D22" s="897"/>
+      <c r="E22" s="898"/>
       <c r="F22" s="492" t="str">
         <f>+F14</f>
         <v xml:space="preserve"> For the year ended 31 March, 2026</v>
@@ -8985,10 +8980,10 @@
     </row>
     <row r="28" spans="1:9" ht="13.95" customHeight="1">
       <c r="A28" s="479"/>
-      <c r="B28" s="892" t="s">
+      <c r="B28" s="899" t="s">
         <v>310</v>
       </c>
-      <c r="C28" s="840"/>
+      <c r="C28" s="807"/>
       <c r="D28" s="321"/>
       <c r="E28" s="322"/>
       <c r="F28" s="323">
@@ -9030,12 +9025,12 @@
     </row>
     <row r="31" spans="1:9" ht="30" customHeight="1">
       <c r="A31" s="480"/>
-      <c r="B31" s="893" t="s">
+      <c r="B31" s="896" t="s">
         <v>134</v>
       </c>
-      <c r="C31" s="894"/>
-      <c r="D31" s="894"/>
-      <c r="E31" s="895"/>
+      <c r="C31" s="897"/>
+      <c r="D31" s="897"/>
+      <c r="E31" s="898"/>
       <c r="F31" s="492" t="str">
         <f>+F14</f>
         <v xml:space="preserve"> For the year ended 31 March, 2026</v>
@@ -9077,10 +9072,10 @@
     </row>
     <row r="34" spans="1:10" ht="13.95" customHeight="1">
       <c r="A34" s="479"/>
-      <c r="B34" s="892" t="s">
+      <c r="B34" s="899" t="s">
         <v>310</v>
       </c>
-      <c r="C34" s="840"/>
+      <c r="C34" s="807"/>
       <c r="D34" s="321"/>
       <c r="E34" s="322"/>
       <c r="F34" s="323">
@@ -9123,12 +9118,12 @@
     </row>
     <row r="37" spans="1:10" ht="30" customHeight="1">
       <c r="A37" s="480"/>
-      <c r="B37" s="893" t="s">
+      <c r="B37" s="896" t="s">
         <v>134</v>
       </c>
-      <c r="C37" s="894"/>
-      <c r="D37" s="894"/>
-      <c r="E37" s="895"/>
+      <c r="C37" s="897"/>
+      <c r="D37" s="897"/>
+      <c r="E37" s="898"/>
       <c r="F37" s="492" t="str">
         <f>+F31</f>
         <v xml:space="preserve"> For the year ended 31 March, 2026</v>
@@ -9321,12 +9316,12 @@
     </row>
     <row r="50" spans="1:12" ht="30" customHeight="1">
       <c r="A50" s="416"/>
-      <c r="B50" s="893" t="s">
+      <c r="B50" s="896" t="s">
         <v>134</v>
       </c>
-      <c r="C50" s="894"/>
-      <c r="D50" s="894"/>
-      <c r="E50" s="895"/>
+      <c r="C50" s="897"/>
+      <c r="D50" s="897"/>
+      <c r="E50" s="898"/>
       <c r="F50" s="492" t="str">
         <f>+F37</f>
         <v xml:space="preserve"> For the year ended 31 March, 2026</v>
@@ -9421,10 +9416,10 @@
     </row>
     <row r="56" spans="1:12" ht="13.95" customHeight="1">
       <c r="A56" s="479"/>
-      <c r="B56" s="892" t="s">
+      <c r="B56" s="899" t="s">
         <v>310</v>
       </c>
-      <c r="C56" s="840"/>
+      <c r="C56" s="807"/>
       <c r="D56" s="321"/>
       <c r="E56" s="322"/>
       <c r="F56" s="323">
@@ -9464,16 +9459,16 @@
       <c r="L58" s="94"/>
     </row>
     <row r="59" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A59" s="890" t="str">
+      <c r="A59" s="901" t="str">
         <f>+A1</f>
         <v>KWIKTEAM SUPPORT SERVICES PVT LTD</v>
       </c>
-      <c r="B59" s="890"/>
-      <c r="C59" s="890"/>
-      <c r="D59" s="890"/>
-      <c r="E59" s="890"/>
-      <c r="F59" s="890"/>
-      <c r="G59" s="890"/>
+      <c r="B59" s="901"/>
+      <c r="C59" s="901"/>
+      <c r="D59" s="901"/>
+      <c r="E59" s="901"/>
+      <c r="F59" s="901"/>
+      <c r="G59" s="901"/>
       <c r="H59" s="120"/>
       <c r="I59" s="120"/>
     </row>
@@ -9489,16 +9484,16 @@
       <c r="I60" s="120"/>
     </row>
     <row r="61" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A61" s="781" t="str">
+      <c r="A61" s="785" t="str">
         <f>+A3</f>
         <v>Schedules to Profit &amp; Loss A/c. for Financial year 20__ - __</v>
       </c>
-      <c r="B61" s="781"/>
-      <c r="C61" s="781"/>
-      <c r="D61" s="781"/>
-      <c r="E61" s="781"/>
-      <c r="F61" s="781"/>
-      <c r="G61" s="781"/>
+      <c r="B61" s="785"/>
+      <c r="C61" s="785"/>
+      <c r="D61" s="785"/>
+      <c r="E61" s="785"/>
+      <c r="F61" s="785"/>
+      <c r="G61" s="785"/>
       <c r="H61" s="120"/>
       <c r="I61" s="120"/>
     </row>
@@ -9534,12 +9529,12 @@
     </row>
     <row r="64" spans="1:12" ht="30" customHeight="1">
       <c r="A64" s="416"/>
-      <c r="B64" s="893" t="s">
+      <c r="B64" s="896" t="s">
         <v>134</v>
       </c>
-      <c r="C64" s="894"/>
-      <c r="D64" s="894"/>
-      <c r="E64" s="895"/>
+      <c r="C64" s="897"/>
+      <c r="D64" s="897"/>
+      <c r="E64" s="898"/>
       <c r="F64" s="492" t="str">
         <f>+F50</f>
         <v xml:space="preserve"> For the year ended 31 March, 2026</v>
@@ -9628,10 +9623,10 @@
     </row>
     <row r="70" spans="1:12" ht="13.95" customHeight="1">
       <c r="A70" s="479"/>
-      <c r="B70" s="892" t="s">
+      <c r="B70" s="899" t="s">
         <v>310</v>
       </c>
-      <c r="C70" s="840"/>
+      <c r="C70" s="807"/>
       <c r="D70" s="321"/>
       <c r="E70" s="322"/>
       <c r="F70" s="323">
@@ -9647,10 +9642,10 @@
       <c r="L70" s="94"/>
     </row>
     <row r="71" spans="1:12" ht="11.7" customHeight="1">
-      <c r="A71" s="896"/>
-      <c r="B71" s="798"/>
-      <c r="C71" s="798"/>
-      <c r="D71" s="798"/>
+      <c r="A71" s="900"/>
+      <c r="B71" s="797"/>
+      <c r="C71" s="797"/>
+      <c r="D71" s="797"/>
       <c r="E71" s="120"/>
       <c r="F71" s="163"/>
       <c r="G71" s="428"/>
@@ -9675,12 +9670,12 @@
     </row>
     <row r="73" spans="1:12" ht="30" customHeight="1">
       <c r="A73" s="416"/>
-      <c r="B73" s="891" t="s">
+      <c r="B73" s="890" t="s">
         <v>134</v>
       </c>
-      <c r="C73" s="891"/>
-      <c r="D73" s="891"/>
-      <c r="E73" s="891"/>
+      <c r="C73" s="890"/>
+      <c r="D73" s="890"/>
+      <c r="E73" s="890"/>
       <c r="F73" s="488" t="str">
         <f>+F64</f>
         <v xml:space="preserve"> For the year ended 31 March, 2026</v>
@@ -10382,10 +10377,10 @@
     </row>
     <row r="112" spans="1:12" ht="13.95" customHeight="1">
       <c r="A112" s="479"/>
-      <c r="B112" s="892" t="s">
+      <c r="B112" s="899" t="s">
         <v>310</v>
       </c>
-      <c r="C112" s="840"/>
+      <c r="C112" s="807"/>
       <c r="D112" s="321"/>
       <c r="E112" s="322"/>
       <c r="F112" s="323">
@@ -10429,12 +10424,12 @@
     </row>
     <row r="115" spans="1:10" ht="30" customHeight="1">
       <c r="A115" s="480"/>
-      <c r="B115" s="891" t="s">
+      <c r="B115" s="890" t="s">
         <v>134</v>
       </c>
-      <c r="C115" s="891"/>
-      <c r="D115" s="891"/>
-      <c r="E115" s="891"/>
+      <c r="C115" s="890"/>
+      <c r="D115" s="890"/>
+      <c r="E115" s="890"/>
       <c r="F115" s="492" t="str">
         <f>+F73</f>
         <v xml:space="preserve"> For the year ended 31 March, 2026</v>
@@ -10498,12 +10493,12 @@
     </row>
     <row r="119" spans="1:10" ht="11.4">
       <c r="A119" s="480"/>
-      <c r="B119" s="897" t="s">
+      <c r="B119" s="891" t="s">
         <v>532</v>
       </c>
-      <c r="C119" s="798"/>
-      <c r="D119" s="798"/>
-      <c r="E119" s="798"/>
+      <c r="C119" s="797"/>
+      <c r="D119" s="797"/>
+      <c r="E119" s="797"/>
       <c r="F119" s="285">
         <v>0</v>
       </c>
@@ -10515,12 +10510,12 @@
     </row>
     <row r="120" spans="1:10" ht="11.4">
       <c r="A120" s="480"/>
-      <c r="B120" s="897" t="s">
+      <c r="B120" s="891" t="s">
         <v>533</v>
       </c>
-      <c r="C120" s="798"/>
-      <c r="D120" s="798"/>
-      <c r="E120" s="798"/>
+      <c r="C120" s="797"/>
+      <c r="D120" s="797"/>
+      <c r="E120" s="797"/>
       <c r="F120" s="387"/>
       <c r="G120" s="387"/>
       <c r="H120" s="120"/>
@@ -10528,12 +10523,12 @@
     </row>
     <row r="121" spans="1:10" ht="11.4">
       <c r="A121" s="480"/>
-      <c r="B121" s="898" t="s">
+      <c r="B121" s="892" t="s">
         <v>534</v>
       </c>
-      <c r="C121" s="899"/>
-      <c r="D121" s="899"/>
-      <c r="E121" s="900"/>
+      <c r="C121" s="893"/>
+      <c r="D121" s="893"/>
+      <c r="E121" s="894"/>
       <c r="F121" s="412">
         <f>IFERROR((F117/F119)*100,0)</f>
         <v>0</v>
@@ -10600,15 +10595,15 @@
       <c r="H126" s="120"/>
     </row>
     <row r="127" spans="1:10" ht="11.4">
-      <c r="A127" s="901" t="s">
+      <c r="A127" s="895" t="s">
         <v>379</v>
       </c>
-      <c r="B127" s="798"/>
-      <c r="C127" s="798"/>
-      <c r="D127" s="798"/>
-      <c r="E127" s="798"/>
+      <c r="B127" s="797"/>
+      <c r="C127" s="797"/>
+      <c r="D127" s="797"/>
+      <c r="E127" s="797"/>
       <c r="F127" s="809"/>
-      <c r="G127" s="798"/>
+      <c r="G127" s="797"/>
       <c r="H127" s="120"/>
     </row>
     <row r="128" spans="1:10" ht="11.4">
@@ -10647,31 +10642,31 @@
   </sheetData>
   <autoFilter ref="I74:I134" xr:uid="{00000000-0009-0000-0000-000009000000}"/>
   <mergeCells count="25">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B14:E14"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B22:E22"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B31:E31"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B37:E37"/>
+    <mergeCell ref="B50:E50"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="A59:G59"/>
+    <mergeCell ref="A61:G61"/>
+    <mergeCell ref="B64:E64"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="A71:D71"/>
+    <mergeCell ref="B73:E73"/>
+    <mergeCell ref="B112:C112"/>
     <mergeCell ref="B115:E115"/>
     <mergeCell ref="B119:E119"/>
     <mergeCell ref="B120:E120"/>
     <mergeCell ref="B121:E121"/>
     <mergeCell ref="A127:G127"/>
-    <mergeCell ref="B64:E64"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="A71:D71"/>
-    <mergeCell ref="B73:E73"/>
-    <mergeCell ref="B112:C112"/>
-    <mergeCell ref="B37:E37"/>
-    <mergeCell ref="B50:E50"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="A59:G59"/>
-    <mergeCell ref="A61:G61"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B22:E22"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B31:E31"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B14:E14"/>
   </mergeCells>
   <conditionalFormatting sqref="F6:G6 F14:G14 F31:G31 F37:G37 F50:G50 G74">
     <cfRule type="cellIs" dxfId="11" priority="61" operator="lessThan">
@@ -10770,8 +10765,8 @@
       <c r="E3" s="213"/>
     </row>
     <row r="4" spans="1:7" ht="11.4">
-      <c r="B4" s="902"/>
-      <c r="C4" s="798"/>
+      <c r="B4" s="905"/>
+      <c r="C4" s="797"/>
       <c r="D4" s="476"/>
       <c r="E4" s="476"/>
     </row>
@@ -10792,10 +10787,10 @@
         <v>134</v>
       </c>
       <c r="D6" s="517"/>
-      <c r="E6" s="903" t="s">
+      <c r="E6" s="906" t="s">
         <v>537</v>
       </c>
-      <c r="F6" s="830"/>
+      <c r="F6" s="862"/>
       <c r="G6" s="518" t="s">
         <v>537</v>
       </c>
@@ -10805,11 +10800,11 @@
       <c r="B7" s="514"/>
       <c r="C7" s="519"/>
       <c r="D7" s="520"/>
-      <c r="E7" s="904">
+      <c r="E7" s="907">
         <f>'Note PL'!F9</f>
         <v>0</v>
       </c>
-      <c r="F7" s="830"/>
+      <c r="F7" s="862"/>
       <c r="G7" s="521">
         <v>0</v>
       </c>
@@ -10839,10 +10834,10 @@
         <v>134</v>
       </c>
       <c r="D10" s="517"/>
-      <c r="E10" s="903" t="s">
+      <c r="E10" s="906" t="s">
         <v>537</v>
       </c>
-      <c r="F10" s="830"/>
+      <c r="F10" s="862"/>
       <c r="G10" s="518" t="s">
         <v>537</v>
       </c>
@@ -10852,11 +10847,11 @@
       <c r="B11" s="514"/>
       <c r="C11" s="519"/>
       <c r="D11" s="520"/>
-      <c r="E11" s="904">
+      <c r="E11" s="907">
         <f>'Note PL'!F13</f>
         <v>0</v>
       </c>
-      <c r="F11" s="830"/>
+      <c r="F11" s="862"/>
       <c r="G11" s="521">
         <v>0</v>
       </c>
@@ -11014,7 +11009,7 @@
       <c r="A26" s="514"/>
       <c r="B26" s="514"/>
       <c r="C26" s="549"/>
-      <c r="D26" s="798"/>
+      <c r="D26" s="797"/>
       <c r="E26" s="809"/>
       <c r="F26" s="549"/>
       <c r="G26" s="549"/>
@@ -11148,8 +11143,8 @@
       <c r="C39" s="395"/>
       <c r="D39" s="565"/>
       <c r="E39" s="565"/>
-      <c r="F39" s="905"/>
-      <c r="G39" s="906"/>
+      <c r="F39" s="902"/>
+      <c r="G39" s="903"/>
     </row>
     <row r="40" spans="1:7" ht="12.75" customHeight="1">
       <c r="A40" s="514"/>
@@ -11284,13 +11279,13 @@
     </row>
     <row r="54" spans="1:7" ht="42.75" customHeight="1">
       <c r="B54" s="396"/>
-      <c r="C54" s="907" t="s">
+      <c r="C54" s="904" t="s">
         <v>568</v>
       </c>
-      <c r="D54" s="906"/>
-      <c r="E54" s="906"/>
-      <c r="F54" s="906"/>
-      <c r="G54" s="906"/>
+      <c r="D54" s="903"/>
+      <c r="E54" s="903"/>
+      <c r="F54" s="903"/>
+      <c r="G54" s="903"/>
     </row>
     <row r="55" spans="1:7" ht="15" customHeight="1"/>
     <row r="56" spans="1:7" ht="15" customHeight="1"/>
@@ -11446,44 +11441,44 @@
     </row>
     <row r="6" spans="2:14" ht="5.25" customHeight="1"/>
     <row r="7" spans="2:14" ht="20.25" customHeight="1">
-      <c r="B7" s="682" t="s">
+      <c r="B7" s="704" t="s">
         <v>542</v>
       </c>
-      <c r="C7" s="684" t="s">
+      <c r="C7" s="706" t="s">
         <v>134</v>
       </c>
       <c r="D7" s="592" t="s">
         <v>570</v>
       </c>
-      <c r="E7" s="682" t="s">
+      <c r="E7" s="704" t="s">
         <v>571</v>
       </c>
-      <c r="F7" s="686" t="s">
+      <c r="F7" s="708" t="s">
         <v>572</v>
       </c>
-      <c r="G7" s="686" t="s">
+      <c r="G7" s="708" t="s">
         <v>573</v>
       </c>
-      <c r="H7" s="688" t="s">
+      <c r="H7" s="702" t="s">
         <v>574</v>
       </c>
     </row>
     <row r="8" spans="2:14" ht="13.8">
-      <c r="B8" s="683"/>
-      <c r="C8" s="685"/>
+      <c r="B8" s="705"/>
+      <c r="C8" s="707"/>
       <c r="D8" s="593" t="s">
         <v>575</v>
       </c>
-      <c r="E8" s="683"/>
-      <c r="F8" s="687"/>
-      <c r="G8" s="687"/>
-      <c r="H8" s="689"/>
+      <c r="E8" s="705"/>
+      <c r="F8" s="709"/>
+      <c r="G8" s="709"/>
+      <c r="H8" s="703"/>
     </row>
     <row r="9" spans="2:14" ht="14.25" customHeight="1">
-      <c r="B9" s="690">
+      <c r="B9" s="682">
         <v>1</v>
       </c>
-      <c r="C9" s="692" t="s">
+      <c r="C9" s="698" t="s">
         <v>576</v>
       </c>
       <c r="D9" s="594" t="s">
@@ -11492,30 +11487,30 @@
       <c r="E9" s="595">
         <v>0</v>
       </c>
-      <c r="F9" s="694">
+      <c r="F9" s="700">
         <f>+IFERROR(E9/E10,0)</f>
         <v>0</v>
       </c>
-      <c r="G9" s="694">
-        <v>0</v>
-      </c>
-      <c r="H9" s="696">
+      <c r="G9" s="700">
+        <v>0</v>
+      </c>
+      <c r="H9" s="688">
         <f>+IFERROR(((F9-G9)/G9),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="2:14" ht="13.8">
-      <c r="B10" s="691"/>
-      <c r="C10" s="693"/>
+      <c r="B10" s="683"/>
+      <c r="C10" s="699"/>
       <c r="D10" s="594" t="s">
         <v>578</v>
       </c>
       <c r="E10" s="595">
         <v>0</v>
       </c>
-      <c r="F10" s="695"/>
-      <c r="G10" s="695"/>
-      <c r="H10" s="697"/>
+      <c r="F10" s="701"/>
+      <c r="G10" s="701"/>
+      <c r="H10" s="689"/>
     </row>
     <row r="11" spans="2:14" ht="8.1" customHeight="1">
       <c r="B11" s="596"/>
@@ -11527,10 +11522,10 @@
       <c r="H11" s="602"/>
     </row>
     <row r="12" spans="2:14" ht="14.25" customHeight="1">
-      <c r="B12" s="690">
+      <c r="B12" s="682">
         <v>2</v>
       </c>
-      <c r="C12" s="692" t="s">
+      <c r="C12" s="698" t="s">
         <v>579</v>
       </c>
       <c r="D12" s="603" t="s">
@@ -11539,30 +11534,30 @@
       <c r="E12" s="595">
         <v>0</v>
       </c>
-      <c r="F12" s="694">
+      <c r="F12" s="700">
         <f>+IFERROR(E12/E13,0)</f>
         <v>0</v>
       </c>
-      <c r="G12" s="698">
-        <v>0</v>
-      </c>
-      <c r="H12" s="696">
+      <c r="G12" s="694">
+        <v>0</v>
+      </c>
+      <c r="H12" s="688">
         <f>IFERROR(((F12-G12)/G12),0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="2:14" ht="13.8">
-      <c r="B13" s="691"/>
-      <c r="C13" s="693"/>
+      <c r="B13" s="683"/>
+      <c r="C13" s="699"/>
       <c r="D13" s="594" t="s">
         <v>581</v>
       </c>
       <c r="E13" s="595">
         <v>0</v>
       </c>
-      <c r="F13" s="695"/>
-      <c r="G13" s="699"/>
-      <c r="H13" s="697"/>
+      <c r="F13" s="701"/>
+      <c r="G13" s="695"/>
+      <c r="H13" s="689"/>
     </row>
     <row r="14" spans="2:14" ht="8.1" customHeight="1">
       <c r="B14" s="596"/>
@@ -11576,10 +11571,10 @@
       <c r="H14" s="602"/>
     </row>
     <row r="15" spans="2:14" ht="15" customHeight="1">
-      <c r="B15" s="690">
+      <c r="B15" s="682">
         <v>3</v>
       </c>
-      <c r="C15" s="700" t="str">
+      <c r="C15" s="690" t="str">
         <f>N15</f>
         <v>Debt Service Coverage Ratio (In Times)</v>
       </c>
@@ -11589,14 +11584,14 @@
       <c r="E15" s="595">
         <v>0</v>
       </c>
-      <c r="F15" s="698" t="str">
+      <c r="F15" s="694" t="str">
         <f>+IF(ISNUMBER(E15/E16),E15/E16,"N.A.")</f>
         <v>N.A.</v>
       </c>
-      <c r="G15" s="698">
-        <v>0</v>
-      </c>
-      <c r="H15" s="696">
+      <c r="G15" s="694">
+        <v>0</v>
+      </c>
+      <c r="H15" s="688">
         <f>+IFERROR(((F15-G15)/G15),0)</f>
         <v>0</v>
       </c>
@@ -11605,17 +11600,17 @@
       </c>
     </row>
     <row r="16" spans="2:14" ht="20.25" customHeight="1">
-      <c r="B16" s="691"/>
-      <c r="C16" s="701"/>
+      <c r="B16" s="683"/>
+      <c r="C16" s="691"/>
       <c r="D16" s="594" t="s">
         <v>584</v>
       </c>
       <c r="E16" s="607">
         <v>0</v>
       </c>
-      <c r="F16" s="699"/>
-      <c r="G16" s="699"/>
-      <c r="H16" s="697"/>
+      <c r="F16" s="695"/>
+      <c r="G16" s="695"/>
+      <c r="H16" s="689"/>
       <c r="N16" s="585" t="s">
         <v>24</v>
       </c>
@@ -11644,10 +11639,10 @@
       <c r="H18" s="611"/>
     </row>
     <row r="19" spans="2:14" ht="15" customHeight="1">
-      <c r="B19" s="690">
+      <c r="B19" s="682">
         <v>4</v>
       </c>
-      <c r="C19" s="700" t="s">
+      <c r="C19" s="690" t="s">
         <v>585</v>
       </c>
       <c r="D19" s="594" t="s">
@@ -11656,14 +11651,14 @@
       <c r="E19" s="595">
         <v>0</v>
       </c>
-      <c r="F19" s="696">
+      <c r="F19" s="688">
         <f>+IFERROR(E19/E20,0)</f>
         <v>0</v>
       </c>
-      <c r="G19" s="702">
-        <v>0</v>
-      </c>
-      <c r="H19" s="696">
+      <c r="G19" s="696">
+        <v>0</v>
+      </c>
+      <c r="H19" s="688">
         <f>+IFERROR(((F19-G19)/G19),0)</f>
         <v>0</v>
       </c>
@@ -11672,17 +11667,17 @@
       </c>
     </row>
     <row r="20" spans="2:14" ht="13.8">
-      <c r="B20" s="691"/>
-      <c r="C20" s="701"/>
+      <c r="B20" s="683"/>
+      <c r="C20" s="691"/>
       <c r="D20" s="594" t="s">
         <v>587</v>
       </c>
       <c r="E20" s="595">
         <v>0</v>
       </c>
-      <c r="F20" s="697"/>
-      <c r="G20" s="703"/>
-      <c r="H20" s="697"/>
+      <c r="F20" s="689"/>
+      <c r="G20" s="697"/>
+      <c r="H20" s="689"/>
       <c r="N20" s="585" t="s">
         <v>24</v>
       </c>
@@ -11709,10 +11704,10 @@
       </c>
     </row>
     <row r="23" spans="2:14" ht="15" customHeight="1">
-      <c r="B23" s="690">
+      <c r="B23" s="682">
         <v>5</v>
       </c>
-      <c r="C23" s="700" t="s">
+      <c r="C23" s="690" t="s">
         <v>588</v>
       </c>
       <c r="D23" s="594" t="s">
@@ -11721,14 +11716,14 @@
       <c r="E23" s="595">
         <v>0</v>
       </c>
-      <c r="F23" s="698" t="str">
+      <c r="F23" s="694" t="str">
         <f t="shared" ref="F23" si="0">+IF(ISNUMBER(E23/E24),E23/E24,"N.A.")</f>
         <v>N.A.</v>
       </c>
-      <c r="G23" s="698">
-        <v>0</v>
-      </c>
-      <c r="H23" s="696">
+      <c r="G23" s="694">
+        <v>0</v>
+      </c>
+      <c r="H23" s="688">
         <f>+IFERROR(((F23-G23)/G23),0)</f>
         <v>0</v>
       </c>
@@ -11737,17 +11732,17 @@
       </c>
     </row>
     <row r="24" spans="2:14" ht="23.25" customHeight="1">
-      <c r="B24" s="691"/>
-      <c r="C24" s="701"/>
+      <c r="B24" s="683"/>
+      <c r="C24" s="691"/>
       <c r="D24" s="594" t="s">
         <v>590</v>
       </c>
       <c r="E24" s="595">
         <v>0</v>
       </c>
-      <c r="F24" s="699"/>
-      <c r="G24" s="699"/>
-      <c r="H24" s="697"/>
+      <c r="F24" s="695"/>
+      <c r="G24" s="695"/>
+      <c r="H24" s="689"/>
       <c r="K24" s="585" t="str">
         <f t="shared" ref="K24:K26" si="1">PROPER(C24)</f>
         <v/>
@@ -11784,10 +11779,10 @@
       </c>
     </row>
     <row r="27" spans="2:14" ht="15" customHeight="1">
-      <c r="B27" s="690">
+      <c r="B27" s="682">
         <v>6</v>
       </c>
-      <c r="C27" s="700" t="s">
+      <c r="C27" s="690" t="s">
         <v>591</v>
       </c>
       <c r="D27" s="594" t="s">
@@ -11796,14 +11791,14 @@
       <c r="E27" s="595">
         <v>0</v>
       </c>
-      <c r="F27" s="698" t="str">
+      <c r="F27" s="694" t="str">
         <f t="shared" ref="F27" si="2">+IF(ISNUMBER(E27/E28),E27/E28,"N.A.")</f>
         <v>N.A.</v>
       </c>
-      <c r="G27" s="698">
-        <v>0</v>
-      </c>
-      <c r="H27" s="696">
+      <c r="G27" s="694">
+        <v>0</v>
+      </c>
+      <c r="H27" s="688">
         <f>+IFERROR(((F27-G27)/G27),0)</f>
         <v>0</v>
       </c>
@@ -11812,17 +11807,17 @@
       </c>
     </row>
     <row r="28" spans="2:14" ht="26.25" customHeight="1">
-      <c r="B28" s="691"/>
-      <c r="C28" s="701"/>
+      <c r="B28" s="683"/>
+      <c r="C28" s="691"/>
       <c r="D28" s="594" t="s">
         <v>593</v>
       </c>
       <c r="E28" s="595">
         <v>0</v>
       </c>
-      <c r="F28" s="699"/>
-      <c r="G28" s="699"/>
-      <c r="H28" s="697"/>
+      <c r="F28" s="695"/>
+      <c r="G28" s="695"/>
+      <c r="H28" s="689"/>
       <c r="N28" s="585" t="s">
         <v>24</v>
       </c>
@@ -11849,10 +11844,10 @@
       <c r="H30" s="602"/>
     </row>
     <row r="31" spans="2:14" ht="15" customHeight="1">
-      <c r="B31" s="690">
+      <c r="B31" s="682">
         <v>7</v>
       </c>
-      <c r="C31" s="700" t="s">
+      <c r="C31" s="690" t="s">
         <v>594</v>
       </c>
       <c r="D31" s="594" t="s">
@@ -11861,14 +11856,14 @@
       <c r="E31" s="595">
         <v>0</v>
       </c>
-      <c r="F31" s="698" t="str">
+      <c r="F31" s="694" t="str">
         <f>+IF(ISNUMBER(E31/E32),E31/E32,"N.A.")</f>
         <v>N.A.</v>
       </c>
-      <c r="G31" s="698">
-        <v>0</v>
-      </c>
-      <c r="H31" s="696">
+      <c r="G31" s="694">
+        <v>0</v>
+      </c>
+      <c r="H31" s="688">
         <f>+IFERROR(((F31-G31)/G31),0)</f>
         <v>0</v>
       </c>
@@ -11877,17 +11872,17 @@
       </c>
     </row>
     <row r="32" spans="2:14" ht="24.75" customHeight="1">
-      <c r="B32" s="691"/>
-      <c r="C32" s="701"/>
+      <c r="B32" s="683"/>
+      <c r="C32" s="691"/>
       <c r="D32" s="594" t="s">
         <v>596</v>
       </c>
       <c r="E32" s="595">
         <v>0</v>
       </c>
-      <c r="F32" s="699"/>
-      <c r="G32" s="699"/>
-      <c r="H32" s="697"/>
+      <c r="F32" s="695"/>
+      <c r="G32" s="695"/>
+      <c r="H32" s="689"/>
       <c r="N32" s="585" t="s">
         <v>24</v>
       </c>
@@ -11914,10 +11909,10 @@
       </c>
     </row>
     <row r="35" spans="2:14" ht="15" customHeight="1">
-      <c r="B35" s="690">
+      <c r="B35" s="682">
         <v>8</v>
       </c>
-      <c r="C35" s="700" t="s">
+      <c r="C35" s="690" t="s">
         <v>597</v>
       </c>
       <c r="D35" s="594" t="s">
@@ -11926,14 +11921,14 @@
       <c r="E35" s="595">
         <v>0</v>
       </c>
-      <c r="F35" s="698">
+      <c r="F35" s="694">
         <f>+IFERROR(E35/E36,0)</f>
         <v>0</v>
       </c>
-      <c r="G35" s="698">
-        <v>0</v>
-      </c>
-      <c r="H35" s="696">
+      <c r="G35" s="694">
+        <v>0</v>
+      </c>
+      <c r="H35" s="688">
         <f>+IFERROR(((F35-G35)/G35),0)</f>
         <v>0</v>
       </c>
@@ -11942,17 +11937,17 @@
       </c>
     </row>
     <row r="36" spans="2:14" ht="23.25" customHeight="1">
-      <c r="B36" s="691"/>
-      <c r="C36" s="701"/>
+      <c r="B36" s="683"/>
+      <c r="C36" s="691"/>
       <c r="D36" s="594" t="s">
         <v>598</v>
       </c>
       <c r="E36" s="595">
         <v>0</v>
       </c>
-      <c r="F36" s="699"/>
-      <c r="G36" s="699"/>
-      <c r="H36" s="697"/>
+      <c r="F36" s="695"/>
+      <c r="G36" s="695"/>
+      <c r="H36" s="689"/>
       <c r="N36" s="585" t="s">
         <v>24</v>
       </c>
@@ -11970,10 +11965,10 @@
       </c>
     </row>
     <row r="38" spans="2:14" ht="14.25" customHeight="1">
-      <c r="B38" s="690">
+      <c r="B38" s="682">
         <v>9</v>
       </c>
-      <c r="C38" s="700" t="s">
+      <c r="C38" s="690" t="s">
         <v>599</v>
       </c>
       <c r="D38" s="594" t="s">
@@ -11982,14 +11977,14 @@
       <c r="E38" s="595">
         <v>0</v>
       </c>
-      <c r="F38" s="704">
+      <c r="F38" s="692">
         <f>+IFERROR(E38/E39,0)</f>
         <v>0</v>
       </c>
-      <c r="G38" s="704">
-        <v>0</v>
-      </c>
-      <c r="H38" s="696">
+      <c r="G38" s="692">
+        <v>0</v>
+      </c>
+      <c r="H38" s="688">
         <f>+IFERROR(((F38-G38)/G38),0)</f>
         <v>0</v>
       </c>
@@ -11998,17 +11993,17 @@
       </c>
     </row>
     <row r="39" spans="2:14" ht="13.8">
-      <c r="B39" s="691"/>
-      <c r="C39" s="701"/>
+      <c r="B39" s="683"/>
+      <c r="C39" s="691"/>
       <c r="D39" s="594" t="s">
         <v>592</v>
       </c>
       <c r="E39" s="595">
         <v>0</v>
       </c>
-      <c r="F39" s="705"/>
-      <c r="G39" s="705"/>
-      <c r="H39" s="697"/>
+      <c r="F39" s="693"/>
+      <c r="G39" s="693"/>
+      <c r="H39" s="689"/>
       <c r="N39" s="585" t="s">
         <v>24</v>
       </c>
@@ -12035,10 +12030,10 @@
       </c>
     </row>
     <row r="42" spans="2:14" ht="15" customHeight="1">
-      <c r="B42" s="690">
+      <c r="B42" s="682">
         <v>10</v>
       </c>
-      <c r="C42" s="700" t="s">
+      <c r="C42" s="690" t="s">
         <v>600</v>
       </c>
       <c r="D42" s="594" t="s">
@@ -12047,14 +12042,14 @@
       <c r="E42" s="595">
         <v>0</v>
       </c>
-      <c r="F42" s="706">
+      <c r="F42" s="686">
         <f>+IFERROR(E42/E43,0)</f>
         <v>0</v>
       </c>
-      <c r="G42" s="706">
-        <v>0</v>
-      </c>
-      <c r="H42" s="696">
+      <c r="G42" s="686">
+        <v>0</v>
+      </c>
+      <c r="H42" s="688">
         <f>+IFERROR(((F42-G42)/G42),0)</f>
         <v>0</v>
       </c>
@@ -12063,17 +12058,17 @@
       </c>
     </row>
     <row r="43" spans="2:14" ht="13.8">
-      <c r="B43" s="691"/>
-      <c r="C43" s="701"/>
+      <c r="B43" s="683"/>
+      <c r="C43" s="691"/>
       <c r="D43" s="594" t="s">
         <v>602</v>
       </c>
       <c r="E43" s="595">
         <v>0</v>
       </c>
-      <c r="F43" s="707"/>
-      <c r="G43" s="707"/>
-      <c r="H43" s="697"/>
+      <c r="F43" s="687"/>
+      <c r="G43" s="687"/>
+      <c r="H43" s="689"/>
       <c r="N43" s="585" t="s">
         <v>24</v>
       </c>
@@ -12103,10 +12098,10 @@
       </c>
     </row>
     <row r="46" spans="2:14" ht="15.75" customHeight="1">
-      <c r="B46" s="690">
+      <c r="B46" s="682">
         <v>11</v>
       </c>
-      <c r="C46" s="708" t="s">
+      <c r="C46" s="684" t="s">
         <v>603</v>
       </c>
       <c r="D46" s="603" t="s">
@@ -12115,14 +12110,14 @@
       <c r="E46" s="607">
         <v>0</v>
       </c>
-      <c r="F46" s="706" t="str">
+      <c r="F46" s="686" t="str">
         <f>+IF(ISNUMBER(E46/E47),E46/E47,"N.A.")</f>
         <v>N.A.</v>
       </c>
-      <c r="G46" s="706">
-        <v>0</v>
-      </c>
-      <c r="H46" s="696">
+      <c r="G46" s="686">
+        <v>0</v>
+      </c>
+      <c r="H46" s="688">
         <f>+IFERROR(((F46-G46)/G46),0)</f>
         <v>0</v>
       </c>
@@ -12131,17 +12126,17 @@
       </c>
     </row>
     <row r="47" spans="2:14" ht="13.8">
-      <c r="B47" s="691"/>
-      <c r="C47" s="709"/>
+      <c r="B47" s="683"/>
+      <c r="C47" s="685"/>
       <c r="D47" s="603" t="s">
         <v>605</v>
       </c>
       <c r="E47" s="607">
         <v>0</v>
       </c>
-      <c r="F47" s="707"/>
-      <c r="G47" s="707"/>
-      <c r="H47" s="697"/>
+      <c r="F47" s="687"/>
+      <c r="G47" s="687"/>
+      <c r="H47" s="689"/>
       <c r="N47" s="585" t="s">
         <v>24</v>
       </c>
@@ -12174,56 +12169,6 @@
     </row>
   </sheetData>
   <mergeCells count="61">
-    <mergeCell ref="B46:B47"/>
-    <mergeCell ref="C46:C47"/>
-    <mergeCell ref="F46:F47"/>
-    <mergeCell ref="G46:G47"/>
-    <mergeCell ref="H46:H47"/>
-    <mergeCell ref="B42:B43"/>
-    <mergeCell ref="C42:C43"/>
-    <mergeCell ref="F42:F43"/>
-    <mergeCell ref="G42:G43"/>
-    <mergeCell ref="H42:H43"/>
-    <mergeCell ref="B38:B39"/>
-    <mergeCell ref="C38:C39"/>
-    <mergeCell ref="F38:F39"/>
-    <mergeCell ref="G38:G39"/>
-    <mergeCell ref="H38:H39"/>
-    <mergeCell ref="B35:B36"/>
-    <mergeCell ref="C35:C36"/>
-    <mergeCell ref="F35:F36"/>
-    <mergeCell ref="G35:G36"/>
-    <mergeCell ref="H35:H36"/>
-    <mergeCell ref="B31:B32"/>
-    <mergeCell ref="C31:C32"/>
-    <mergeCell ref="F31:F32"/>
-    <mergeCell ref="G31:G32"/>
-    <mergeCell ref="H31:H32"/>
-    <mergeCell ref="B27:B28"/>
-    <mergeCell ref="C27:C28"/>
-    <mergeCell ref="F27:F28"/>
-    <mergeCell ref="G27:G28"/>
-    <mergeCell ref="H27:H28"/>
-    <mergeCell ref="B23:B24"/>
-    <mergeCell ref="C23:C24"/>
-    <mergeCell ref="F23:F24"/>
-    <mergeCell ref="G23:G24"/>
-    <mergeCell ref="H23:H24"/>
-    <mergeCell ref="B19:B20"/>
-    <mergeCell ref="C19:C20"/>
-    <mergeCell ref="F19:F20"/>
-    <mergeCell ref="G19:G20"/>
-    <mergeCell ref="H19:H20"/>
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="C15:C16"/>
-    <mergeCell ref="F15:F16"/>
-    <mergeCell ref="G15:G16"/>
-    <mergeCell ref="H15:H16"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="H12:H13"/>
     <mergeCell ref="H7:H8"/>
     <mergeCell ref="B9:B10"/>
     <mergeCell ref="C9:C10"/>
@@ -12235,6 +12180,56 @@
     <mergeCell ref="E7:E8"/>
     <mergeCell ref="F7:F8"/>
     <mergeCell ref="G7:G8"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="H12:H13"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="F15:F16"/>
+    <mergeCell ref="G15:G16"/>
+    <mergeCell ref="H15:H16"/>
+    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="C19:C20"/>
+    <mergeCell ref="F19:F20"/>
+    <mergeCell ref="G19:G20"/>
+    <mergeCell ref="H19:H20"/>
+    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="C23:C24"/>
+    <mergeCell ref="F23:F24"/>
+    <mergeCell ref="G23:G24"/>
+    <mergeCell ref="H23:H24"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="C27:C28"/>
+    <mergeCell ref="F27:F28"/>
+    <mergeCell ref="G27:G28"/>
+    <mergeCell ref="H27:H28"/>
+    <mergeCell ref="B31:B32"/>
+    <mergeCell ref="C31:C32"/>
+    <mergeCell ref="F31:F32"/>
+    <mergeCell ref="G31:G32"/>
+    <mergeCell ref="H31:H32"/>
+    <mergeCell ref="B35:B36"/>
+    <mergeCell ref="C35:C36"/>
+    <mergeCell ref="F35:F36"/>
+    <mergeCell ref="G35:G36"/>
+    <mergeCell ref="H35:H36"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="C38:C39"/>
+    <mergeCell ref="F38:F39"/>
+    <mergeCell ref="G38:G39"/>
+    <mergeCell ref="H38:H39"/>
+    <mergeCell ref="B42:B43"/>
+    <mergeCell ref="C42:C43"/>
+    <mergeCell ref="F42:F43"/>
+    <mergeCell ref="G42:G43"/>
+    <mergeCell ref="H42:H43"/>
+    <mergeCell ref="B46:B47"/>
+    <mergeCell ref="C46:C47"/>
+    <mergeCell ref="F46:F47"/>
+    <mergeCell ref="G46:G47"/>
+    <mergeCell ref="H46:H47"/>
   </mergeCells>
   <conditionalFormatting sqref="G7:H8 I9:J9">
     <cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
@@ -12322,42 +12317,42 @@
       </c>
     </row>
     <row r="4" spans="1:8" s="395" customFormat="1" ht="24" customHeight="1">
-      <c r="A4" s="910" t="s">
+      <c r="A4" s="912" t="s">
         <v>610</v>
       </c>
-      <c r="B4" s="910" t="s">
+      <c r="B4" s="912" t="s">
         <v>611</v>
       </c>
-      <c r="C4" s="912" t="s">
+      <c r="C4" s="908" t="s">
         <v>612</v>
       </c>
-      <c r="D4" s="908" t="s">
+      <c r="D4" s="910" t="s">
         <v>613</v>
       </c>
-      <c r="E4" s="909"/>
-      <c r="F4" s="912" t="s">
+      <c r="E4" s="911"/>
+      <c r="F4" s="908" t="s">
         <v>310</v>
       </c>
-      <c r="G4" s="912" t="s">
+      <c r="G4" s="908" t="s">
         <v>614</v>
       </c>
-      <c r="H4" s="912" t="s">
+      <c r="H4" s="908" t="s">
         <v>615</v>
       </c>
     </row>
     <row r="5" spans="1:8" s="395" customFormat="1" ht="29.25" customHeight="1">
-      <c r="A5" s="911"/>
-      <c r="B5" s="911"/>
-      <c r="C5" s="913"/>
+      <c r="A5" s="913"/>
+      <c r="B5" s="913"/>
+      <c r="C5" s="909"/>
       <c r="D5" s="630" t="s">
         <v>616</v>
       </c>
       <c r="E5" s="630" t="s">
         <v>617</v>
       </c>
-      <c r="F5" s="913"/>
-      <c r="G5" s="913"/>
-      <c r="H5" s="913"/>
+      <c r="F5" s="909"/>
+      <c r="G5" s="909"/>
+      <c r="H5" s="909"/>
     </row>
     <row r="6" spans="1:8" ht="13.2">
       <c r="A6" s="631" t="s">
@@ -12669,12 +12664,12 @@
       <c r="E4" s="648"/>
     </row>
     <row r="5" spans="1:5" ht="28.5" customHeight="1">
-      <c r="A5" s="787" t="s">
+      <c r="A5" s="791" t="s">
         <v>134</v>
       </c>
-      <c r="B5" s="788"/>
-      <c r="C5" s="788"/>
-      <c r="D5" s="788"/>
+      <c r="B5" s="792"/>
+      <c r="C5" s="792"/>
+      <c r="D5" s="792"/>
       <c r="E5" s="649" t="str">
         <f>+BS!E5</f>
         <v>(Amount in Rs. `000)</v>
@@ -12935,174 +12930,174 @@
       <c r="H2" s="775"/>
     </row>
     <row r="3" spans="1:8" ht="4.95" customHeight="1">
-      <c r="A3" s="914"/>
-      <c r="B3" s="915"/>
-      <c r="C3" s="915"/>
-      <c r="D3" s="915"/>
-      <c r="E3" s="915"/>
-      <c r="F3" s="915"/>
-      <c r="G3" s="915"/>
-      <c r="H3" s="915"/>
+      <c r="A3" s="920"/>
+      <c r="B3" s="921"/>
+      <c r="C3" s="921"/>
+      <c r="D3" s="921"/>
+      <c r="E3" s="921"/>
+      <c r="F3" s="921"/>
+      <c r="G3" s="921"/>
+      <c r="H3" s="921"/>
     </row>
     <row r="4" spans="1:8" ht="25.95" customHeight="1">
-      <c r="B4" s="916" t="s">
+      <c r="B4" s="922" t="s">
         <v>24</v>
       </c>
-      <c r="C4" s="917"/>
-      <c r="D4" s="917"/>
-      <c r="E4" s="917"/>
-      <c r="F4" s="917"/>
-      <c r="G4" s="917"/>
+      <c r="C4" s="919"/>
+      <c r="D4" s="919"/>
+      <c r="E4" s="919"/>
+      <c r="F4" s="919"/>
+      <c r="G4" s="919"/>
     </row>
     <row r="6" spans="1:8" ht="22.2" customHeight="1">
-      <c r="B6" s="918" t="s">
+      <c r="B6" s="916" t="s">
         <v>632</v>
       </c>
-      <c r="C6" s="919"/>
-      <c r="D6" s="919"/>
-      <c r="E6" s="919"/>
-      <c r="F6" s="919"/>
-      <c r="G6" s="919"/>
+      <c r="C6" s="917"/>
+      <c r="D6" s="917"/>
+      <c r="E6" s="917"/>
+      <c r="F6" s="917"/>
+      <c r="G6" s="917"/>
     </row>
     <row r="7" spans="1:8" ht="117" customHeight="1">
-      <c r="B7" s="920" t="s">
+      <c r="B7" s="914" t="s">
         <v>633</v>
       </c>
-      <c r="C7" s="921"/>
-      <c r="D7" s="921"/>
-      <c r="E7" s="921"/>
-      <c r="F7" s="921"/>
-      <c r="G7" s="921"/>
+      <c r="C7" s="915"/>
+      <c r="D7" s="915"/>
+      <c r="E7" s="915"/>
+      <c r="F7" s="915"/>
+      <c r="G7" s="915"/>
     </row>
     <row r="9" spans="1:8" ht="22.2" customHeight="1">
-      <c r="B9" s="918" t="s">
+      <c r="B9" s="916" t="s">
         <v>634</v>
       </c>
-      <c r="C9" s="919"/>
-      <c r="D9" s="919"/>
-      <c r="E9" s="919"/>
-      <c r="F9" s="919"/>
-      <c r="G9" s="919"/>
+      <c r="C9" s="917"/>
+      <c r="D9" s="917"/>
+      <c r="E9" s="917"/>
+      <c r="F9" s="917"/>
+      <c r="G9" s="917"/>
     </row>
     <row r="10" spans="1:8" ht="103.95" customHeight="1">
-      <c r="B10" s="920" t="s">
+      <c r="B10" s="914" t="s">
         <v>635</v>
       </c>
-      <c r="C10" s="921"/>
-      <c r="D10" s="921"/>
-      <c r="E10" s="921"/>
-      <c r="F10" s="921"/>
-      <c r="G10" s="921"/>
+      <c r="C10" s="915"/>
+      <c r="D10" s="915"/>
+      <c r="E10" s="915"/>
+      <c r="F10" s="915"/>
+      <c r="G10" s="915"/>
     </row>
     <row r="12" spans="1:8" ht="22.2" customHeight="1">
-      <c r="B12" s="918" t="s">
+      <c r="B12" s="916" t="s">
         <v>636</v>
       </c>
-      <c r="C12" s="919"/>
-      <c r="D12" s="919"/>
-      <c r="E12" s="919"/>
-      <c r="F12" s="919"/>
-      <c r="G12" s="919"/>
+      <c r="C12" s="917"/>
+      <c r="D12" s="917"/>
+      <c r="E12" s="917"/>
+      <c r="F12" s="917"/>
+      <c r="G12" s="917"/>
     </row>
     <row r="13" spans="1:8" ht="52.2" customHeight="1">
-      <c r="B13" s="920" t="s">
+      <c r="B13" s="914" t="s">
         <v>24</v>
       </c>
-      <c r="C13" s="921"/>
-      <c r="D13" s="921"/>
-      <c r="E13" s="921"/>
-      <c r="F13" s="921"/>
-      <c r="G13" s="921"/>
+      <c r="C13" s="915"/>
+      <c r="D13" s="915"/>
+      <c r="E13" s="915"/>
+      <c r="F13" s="915"/>
+      <c r="G13" s="915"/>
     </row>
     <row r="15" spans="1:8" ht="22.2" customHeight="1">
-      <c r="B15" s="918" t="s">
+      <c r="B15" s="916" t="s">
         <v>637</v>
       </c>
-      <c r="C15" s="919"/>
-      <c r="D15" s="919"/>
-      <c r="E15" s="919"/>
-      <c r="F15" s="919"/>
-      <c r="G15" s="919"/>
+      <c r="C15" s="917"/>
+      <c r="D15" s="917"/>
+      <c r="E15" s="917"/>
+      <c r="F15" s="917"/>
+      <c r="G15" s="917"/>
     </row>
     <row r="16" spans="1:8" ht="103.95" customHeight="1">
-      <c r="B16" s="920" t="s">
+      <c r="B16" s="914" t="s">
         <v>638</v>
       </c>
-      <c r="C16" s="921"/>
-      <c r="D16" s="921"/>
-      <c r="E16" s="921"/>
-      <c r="F16" s="921"/>
-      <c r="G16" s="921"/>
+      <c r="C16" s="915"/>
+      <c r="D16" s="915"/>
+      <c r="E16" s="915"/>
+      <c r="F16" s="915"/>
+      <c r="G16" s="915"/>
     </row>
     <row r="18" spans="2:7" ht="22.2" customHeight="1">
-      <c r="B18" s="918" t="s">
+      <c r="B18" s="916" t="s">
         <v>639</v>
       </c>
-      <c r="C18" s="919"/>
-      <c r="D18" s="919"/>
-      <c r="E18" s="919"/>
-      <c r="F18" s="919"/>
-      <c r="G18" s="919"/>
+      <c r="C18" s="917"/>
+      <c r="D18" s="917"/>
+      <c r="E18" s="917"/>
+      <c r="F18" s="917"/>
+      <c r="G18" s="917"/>
     </row>
     <row r="19" spans="2:7" ht="117" customHeight="1">
-      <c r="B19" s="920" t="s">
+      <c r="B19" s="914" t="s">
         <v>640</v>
       </c>
-      <c r="C19" s="921"/>
-      <c r="D19" s="921"/>
-      <c r="E19" s="921"/>
-      <c r="F19" s="921"/>
-      <c r="G19" s="921"/>
+      <c r="C19" s="915"/>
+      <c r="D19" s="915"/>
+      <c r="E19" s="915"/>
+      <c r="F19" s="915"/>
+      <c r="G19" s="915"/>
     </row>
     <row r="21" spans="2:7" ht="22.2" customHeight="1">
-      <c r="B21" s="918" t="s">
+      <c r="B21" s="916" t="s">
         <v>641</v>
       </c>
-      <c r="C21" s="919"/>
-      <c r="D21" s="919"/>
-      <c r="E21" s="919"/>
-      <c r="F21" s="919"/>
-      <c r="G21" s="919"/>
+      <c r="C21" s="917"/>
+      <c r="D21" s="917"/>
+      <c r="E21" s="917"/>
+      <c r="F21" s="917"/>
+      <c r="G21" s="917"/>
     </row>
     <row r="22" spans="2:7" ht="103.95" customHeight="1">
-      <c r="B22" s="920" t="s">
+      <c r="B22" s="914" t="s">
         <v>642</v>
       </c>
-      <c r="C22" s="921"/>
-      <c r="D22" s="921"/>
-      <c r="E22" s="921"/>
-      <c r="F22" s="921"/>
-      <c r="G22" s="921"/>
+      <c r="C22" s="915"/>
+      <c r="D22" s="915"/>
+      <c r="E22" s="915"/>
+      <c r="F22" s="915"/>
+      <c r="G22" s="915"/>
     </row>
     <row r="24" spans="2:7" ht="22.2" customHeight="1">
-      <c r="B24" s="918" t="s">
+      <c r="B24" s="916" t="s">
         <v>643</v>
       </c>
-      <c r="C24" s="919"/>
-      <c r="D24" s="919"/>
-      <c r="E24" s="919"/>
-      <c r="F24" s="919"/>
-      <c r="G24" s="919"/>
+      <c r="C24" s="917"/>
+      <c r="D24" s="917"/>
+      <c r="E24" s="917"/>
+      <c r="F24" s="917"/>
+      <c r="G24" s="917"/>
     </row>
     <row r="25" spans="2:7" ht="325.2" customHeight="1">
-      <c r="B25" s="920" t="s">
+      <c r="B25" s="914" t="s">
         <v>644</v>
       </c>
-      <c r="C25" s="921"/>
-      <c r="D25" s="921"/>
-      <c r="E25" s="921"/>
-      <c r="F25" s="921"/>
-      <c r="G25" s="921"/>
+      <c r="C25" s="915"/>
+      <c r="D25" s="915"/>
+      <c r="E25" s="915"/>
+      <c r="F25" s="915"/>
+      <c r="G25" s="915"/>
     </row>
     <row r="27" spans="2:7" ht="109.95" customHeight="1">
-      <c r="B27" s="922" t="s">
+      <c r="B27" s="918" t="s">
         <v>645</v>
       </c>
-      <c r="C27" s="917"/>
-      <c r="D27" s="917"/>
-      <c r="E27" s="917"/>
-      <c r="F27" s="917"/>
-      <c r="G27" s="917"/>
+      <c r="C27" s="919"/>
+      <c r="D27" s="919"/>
+      <c r="E27" s="919"/>
+      <c r="F27" s="919"/>
+      <c r="G27" s="919"/>
     </row>
     <row r="29" spans="2:7" ht="25.95" customHeight="1">
       <c r="B29" s="779" t="s">
@@ -13116,26 +13111,26 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="B4:G4"/>
+    <mergeCell ref="B6:G6"/>
+    <mergeCell ref="B7:G7"/>
+    <mergeCell ref="B9:G9"/>
+    <mergeCell ref="B10:G10"/>
+    <mergeCell ref="B12:G12"/>
+    <mergeCell ref="B13:G13"/>
+    <mergeCell ref="B15:G15"/>
+    <mergeCell ref="B16:G16"/>
+    <mergeCell ref="B18:G18"/>
+    <mergeCell ref="B19:G19"/>
+    <mergeCell ref="B21:G21"/>
     <mergeCell ref="B22:G22"/>
     <mergeCell ref="B24:G24"/>
     <mergeCell ref="B25:G25"/>
     <mergeCell ref="B27:G27"/>
     <mergeCell ref="B29:G29"/>
-    <mergeCell ref="B15:G15"/>
-    <mergeCell ref="B16:G16"/>
-    <mergeCell ref="B18:G18"/>
-    <mergeCell ref="B19:G19"/>
-    <mergeCell ref="B21:G21"/>
-    <mergeCell ref="B7:G7"/>
-    <mergeCell ref="B9:G9"/>
-    <mergeCell ref="B10:G10"/>
-    <mergeCell ref="B12:G12"/>
-    <mergeCell ref="B13:G13"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="B4:G4"/>
-    <mergeCell ref="B6:G6"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.35" right="0.35" top="0.55000000000000004" bottom="0.55000000000000004" header="0.2" footer="0.2"/>
@@ -13184,11 +13179,11 @@
       </c>
     </row>
     <row r="3" spans="1:8" ht="4.95" customHeight="1">
-      <c r="A3" s="914"/>
-      <c r="B3" s="915"/>
-      <c r="C3" s="915"/>
-      <c r="D3" s="915"/>
-      <c r="E3" s="915"/>
+      <c r="A3" s="920"/>
+      <c r="B3" s="921"/>
+      <c r="C3" s="921"/>
+      <c r="D3" s="921"/>
+      <c r="E3" s="921"/>
     </row>
     <row r="4" spans="1:8" ht="27.6">
       <c r="A4" s="17" t="s">
@@ -13611,154 +13606,154 @@
       <c r="H2" s="775"/>
     </row>
     <row r="3" spans="1:8" ht="4.95" customHeight="1">
-      <c r="A3" s="914"/>
-      <c r="B3" s="915"/>
-      <c r="C3" s="915"/>
-      <c r="D3" s="915"/>
-      <c r="E3" s="915"/>
-      <c r="F3" s="915"/>
-      <c r="G3" s="915"/>
-      <c r="H3" s="915"/>
+      <c r="A3" s="920"/>
+      <c r="B3" s="921"/>
+      <c r="C3" s="921"/>
+      <c r="D3" s="921"/>
+      <c r="E3" s="921"/>
+      <c r="F3" s="921"/>
+      <c r="G3" s="921"/>
+      <c r="H3" s="921"/>
     </row>
     <row r="4" spans="1:8" ht="25.95" customHeight="1">
-      <c r="B4" s="916" t="s">
+      <c r="B4" s="922" t="s">
         <v>24</v>
       </c>
-      <c r="C4" s="917"/>
-      <c r="D4" s="917"/>
-      <c r="E4" s="917"/>
-      <c r="F4" s="917"/>
-      <c r="G4" s="917"/>
+      <c r="C4" s="919"/>
+      <c r="D4" s="919"/>
+      <c r="E4" s="919"/>
+      <c r="F4" s="919"/>
+      <c r="G4" s="919"/>
     </row>
     <row r="6" spans="1:8" ht="22.2" customHeight="1">
-      <c r="B6" s="918" t="s">
+      <c r="B6" s="916" t="s">
         <v>697</v>
       </c>
-      <c r="C6" s="919"/>
-      <c r="D6" s="919"/>
-      <c r="E6" s="919"/>
-      <c r="F6" s="919"/>
-      <c r="G6" s="919"/>
+      <c r="C6" s="917"/>
+      <c r="D6" s="917"/>
+      <c r="E6" s="917"/>
+      <c r="F6" s="917"/>
+      <c r="G6" s="917"/>
     </row>
     <row r="7" spans="1:8" ht="39" customHeight="1">
-      <c r="B7" s="920" t="s">
+      <c r="B7" s="914" t="s">
         <v>698</v>
       </c>
-      <c r="C7" s="921"/>
-      <c r="D7" s="921"/>
-      <c r="E7" s="921"/>
-      <c r="F7" s="921"/>
-      <c r="G7" s="921"/>
+      <c r="C7" s="915"/>
+      <c r="D7" s="915"/>
+      <c r="E7" s="915"/>
+      <c r="F7" s="915"/>
+      <c r="G7" s="915"/>
     </row>
     <row r="9" spans="1:8" ht="22.2" customHeight="1">
-      <c r="B9" s="918" t="s">
+      <c r="B9" s="916" t="s">
         <v>699</v>
       </c>
-      <c r="C9" s="919"/>
-      <c r="D9" s="919"/>
-      <c r="E9" s="919"/>
-      <c r="F9" s="919"/>
-      <c r="G9" s="919"/>
+      <c r="C9" s="917"/>
+      <c r="D9" s="917"/>
+      <c r="E9" s="917"/>
+      <c r="F9" s="917"/>
+      <c r="G9" s="917"/>
     </row>
     <row r="10" spans="1:8" ht="117" customHeight="1">
-      <c r="B10" s="920" t="s">
+      <c r="B10" s="914" t="s">
         <v>700</v>
       </c>
-      <c r="C10" s="921"/>
-      <c r="D10" s="921"/>
-      <c r="E10" s="921"/>
-      <c r="F10" s="921"/>
-      <c r="G10" s="921"/>
+      <c r="C10" s="915"/>
+      <c r="D10" s="915"/>
+      <c r="E10" s="915"/>
+      <c r="F10" s="915"/>
+      <c r="G10" s="915"/>
     </row>
     <row r="12" spans="1:8" ht="22.2" customHeight="1">
-      <c r="B12" s="918" t="s">
+      <c r="B12" s="916" t="s">
         <v>701</v>
       </c>
-      <c r="C12" s="919"/>
-      <c r="D12" s="919"/>
-      <c r="E12" s="919"/>
-      <c r="F12" s="919"/>
-      <c r="G12" s="919"/>
+      <c r="C12" s="917"/>
+      <c r="D12" s="917"/>
+      <c r="E12" s="917"/>
+      <c r="F12" s="917"/>
+      <c r="G12" s="917"/>
     </row>
     <row r="13" spans="1:8" ht="91.2" customHeight="1">
-      <c r="B13" s="920" t="s">
+      <c r="B13" s="914" t="s">
         <v>702</v>
       </c>
-      <c r="C13" s="921"/>
-      <c r="D13" s="921"/>
-      <c r="E13" s="921"/>
-      <c r="F13" s="921"/>
-      <c r="G13" s="921"/>
+      <c r="C13" s="915"/>
+      <c r="D13" s="915"/>
+      <c r="E13" s="915"/>
+      <c r="F13" s="915"/>
+      <c r="G13" s="915"/>
     </row>
     <row r="15" spans="1:8" ht="22.2" customHeight="1">
-      <c r="B15" s="918" t="s">
+      <c r="B15" s="916" t="s">
         <v>703</v>
       </c>
-      <c r="C15" s="919"/>
-      <c r="D15" s="919"/>
-      <c r="E15" s="919"/>
-      <c r="F15" s="919"/>
-      <c r="G15" s="919"/>
+      <c r="C15" s="917"/>
+      <c r="D15" s="917"/>
+      <c r="E15" s="917"/>
+      <c r="F15" s="917"/>
+      <c r="G15" s="917"/>
     </row>
     <row r="16" spans="1:8" ht="103.95" customHeight="1">
-      <c r="B16" s="920" t="s">
+      <c r="B16" s="914" t="s">
         <v>704</v>
       </c>
-      <c r="C16" s="921"/>
-      <c r="D16" s="921"/>
-      <c r="E16" s="921"/>
-      <c r="F16" s="921"/>
-      <c r="G16" s="921"/>
+      <c r="C16" s="915"/>
+      <c r="D16" s="915"/>
+      <c r="E16" s="915"/>
+      <c r="F16" s="915"/>
+      <c r="G16" s="915"/>
     </row>
     <row r="18" spans="2:7" ht="22.2" customHeight="1">
-      <c r="B18" s="918" t="s">
+      <c r="B18" s="916" t="s">
         <v>705</v>
       </c>
-      <c r="C18" s="919"/>
-      <c r="D18" s="919"/>
-      <c r="E18" s="919"/>
-      <c r="F18" s="919"/>
-      <c r="G18" s="919"/>
+      <c r="C18" s="917"/>
+      <c r="D18" s="917"/>
+      <c r="E18" s="917"/>
+      <c r="F18" s="917"/>
+      <c r="G18" s="917"/>
     </row>
     <row r="19" spans="2:7" ht="78" customHeight="1">
-      <c r="B19" s="920" t="s">
+      <c r="B19" s="914" t="s">
         <v>706</v>
       </c>
-      <c r="C19" s="921"/>
-      <c r="D19" s="921"/>
-      <c r="E19" s="921"/>
-      <c r="F19" s="921"/>
-      <c r="G19" s="921"/>
+      <c r="C19" s="915"/>
+      <c r="D19" s="915"/>
+      <c r="E19" s="915"/>
+      <c r="F19" s="915"/>
+      <c r="G19" s="915"/>
     </row>
     <row r="21" spans="2:7" ht="22.2" customHeight="1">
-      <c r="B21" s="918" t="s">
+      <c r="B21" s="916" t="s">
         <v>632</v>
       </c>
-      <c r="C21" s="919"/>
-      <c r="D21" s="919"/>
-      <c r="E21" s="919"/>
-      <c r="F21" s="919"/>
-      <c r="G21" s="919"/>
+      <c r="C21" s="917"/>
+      <c r="D21" s="917"/>
+      <c r="E21" s="917"/>
+      <c r="F21" s="917"/>
+      <c r="G21" s="917"/>
     </row>
     <row r="22" spans="2:7" ht="78" customHeight="1">
-      <c r="B22" s="920" t="s">
+      <c r="B22" s="914" t="s">
         <v>707</v>
       </c>
-      <c r="C22" s="921"/>
-      <c r="D22" s="921"/>
-      <c r="E22" s="921"/>
-      <c r="F22" s="921"/>
-      <c r="G22" s="921"/>
+      <c r="C22" s="915"/>
+      <c r="D22" s="915"/>
+      <c r="E22" s="915"/>
+      <c r="F22" s="915"/>
+      <c r="G22" s="915"/>
     </row>
     <row r="24" spans="2:7" ht="109.95" customHeight="1">
-      <c r="B24" s="922" t="s">
+      <c r="B24" s="918" t="s">
         <v>645</v>
       </c>
-      <c r="C24" s="917"/>
-      <c r="D24" s="917"/>
-      <c r="E24" s="917"/>
-      <c r="F24" s="917"/>
-      <c r="G24" s="917"/>
+      <c r="C24" s="919"/>
+      <c r="D24" s="919"/>
+      <c r="E24" s="919"/>
+      <c r="F24" s="919"/>
+      <c r="G24" s="919"/>
     </row>
     <row r="26" spans="2:7" ht="15" customHeight="1">
       <c r="B26" s="779" t="s">
@@ -13772,6 +13767,16 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="B4:G4"/>
+    <mergeCell ref="B6:G6"/>
+    <mergeCell ref="B7:G7"/>
+    <mergeCell ref="B9:G9"/>
+    <mergeCell ref="B10:G10"/>
+    <mergeCell ref="B12:G12"/>
+    <mergeCell ref="B13:G13"/>
     <mergeCell ref="B22:G22"/>
     <mergeCell ref="B24:G24"/>
     <mergeCell ref="B26:G26"/>
@@ -13780,16 +13785,6 @@
     <mergeCell ref="B18:G18"/>
     <mergeCell ref="B19:G19"/>
     <mergeCell ref="B21:G21"/>
-    <mergeCell ref="B7:G7"/>
-    <mergeCell ref="B9:G9"/>
-    <mergeCell ref="B10:G10"/>
-    <mergeCell ref="B12:G12"/>
-    <mergeCell ref="B13:G13"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="B4:G4"/>
-    <mergeCell ref="B6:G6"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.35" right="0.35" top="0.55000000000000004" bottom="0.55000000000000004" header="0.2" footer="0.2"/>
@@ -13824,211 +13819,211 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:10" ht="29.25" customHeight="1">
-      <c r="A2" s="736" t="s">
+      <c r="A2" s="762" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="737"/>
-      <c r="C2" s="737"/>
-      <c r="D2" s="737"/>
-      <c r="E2" s="737"/>
-      <c r="F2" s="737"/>
-      <c r="G2" s="737"/>
-      <c r="H2" s="737"/>
-      <c r="I2" s="737"/>
-      <c r="J2" s="738"/>
+      <c r="B2" s="763"/>
+      <c r="C2" s="763"/>
+      <c r="D2" s="763"/>
+      <c r="E2" s="763"/>
+      <c r="F2" s="763"/>
+      <c r="G2" s="763"/>
+      <c r="H2" s="763"/>
+      <c r="I2" s="763"/>
+      <c r="J2" s="764"/>
     </row>
     <row r="3" spans="1:10" ht="22.2" customHeight="1">
-      <c r="A3" s="739" t="s">
+      <c r="A3" s="765" t="s">
         <v>41</v>
       </c>
-      <c r="B3" s="740"/>
-      <c r="C3" s="740"/>
-      <c r="D3" s="740"/>
-      <c r="E3" s="740"/>
-      <c r="F3" s="740"/>
-      <c r="G3" s="740"/>
-      <c r="H3" s="740"/>
-      <c r="I3" s="740"/>
-      <c r="J3" s="741"/>
+      <c r="B3" s="766"/>
+      <c r="C3" s="766"/>
+      <c r="D3" s="766"/>
+      <c r="E3" s="766"/>
+      <c r="F3" s="766"/>
+      <c r="G3" s="766"/>
+      <c r="H3" s="766"/>
+      <c r="I3" s="766"/>
+      <c r="J3" s="767"/>
     </row>
     <row r="4" spans="1:10" ht="15" customHeight="1">
-      <c r="A4" s="742"/>
-      <c r="B4" s="743"/>
-      <c r="C4" s="743"/>
-      <c r="D4" s="743"/>
-      <c r="E4" s="743"/>
-      <c r="F4" s="743"/>
-      <c r="G4" s="743"/>
-      <c r="H4" s="743"/>
-      <c r="I4" s="743"/>
-      <c r="J4" s="744"/>
+      <c r="A4" s="768"/>
+      <c r="B4" s="769"/>
+      <c r="C4" s="769"/>
+      <c r="D4" s="769"/>
+      <c r="E4" s="769"/>
+      <c r="F4" s="769"/>
+      <c r="G4" s="769"/>
+      <c r="H4" s="769"/>
+      <c r="I4" s="769"/>
+      <c r="J4" s="770"/>
     </row>
     <row r="5" spans="1:10" ht="15" customHeight="1">
-      <c r="A5" s="745" t="s">
+      <c r="A5" s="742" t="s">
         <v>42</v>
       </c>
-      <c r="B5" s="746"/>
-      <c r="C5" s="746"/>
-      <c r="D5" s="746"/>
-      <c r="E5" s="746"/>
-      <c r="F5" s="746"/>
-      <c r="G5" s="746"/>
-      <c r="H5" s="746"/>
-      <c r="I5" s="746"/>
-      <c r="J5" s="747"/>
+      <c r="B5" s="743"/>
+      <c r="C5" s="743"/>
+      <c r="D5" s="743"/>
+      <c r="E5" s="743"/>
+      <c r="F5" s="743"/>
+      <c r="G5" s="743"/>
+      <c r="H5" s="743"/>
+      <c r="I5" s="743"/>
+      <c r="J5" s="744"/>
     </row>
     <row r="6" spans="1:10" ht="13.8">
       <c r="A6" s="2"/>
-      <c r="B6" s="748" t="s">
+      <c r="B6" s="754" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="748"/>
-      <c r="D6" s="748"/>
-      <c r="E6" s="749"/>
-      <c r="F6" s="750" t="s">
+      <c r="C6" s="754"/>
+      <c r="D6" s="754"/>
+      <c r="E6" s="755"/>
+      <c r="F6" s="771" t="s">
         <v>43</v>
       </c>
-      <c r="G6" s="751"/>
-      <c r="H6" s="751"/>
-      <c r="I6" s="751"/>
-      <c r="J6" s="752"/>
+      <c r="G6" s="772"/>
+      <c r="H6" s="772"/>
+      <c r="I6" s="772"/>
+      <c r="J6" s="773"/>
     </row>
     <row r="7" spans="1:10" ht="13.8">
       <c r="A7" s="3"/>
-      <c r="B7" s="753" t="s">
+      <c r="B7" s="746" t="s">
         <v>44</v>
       </c>
-      <c r="C7" s="753"/>
-      <c r="D7" s="753"/>
-      <c r="E7" s="754"/>
-      <c r="F7" s="755" t="s">
+      <c r="C7" s="746"/>
+      <c r="D7" s="746"/>
+      <c r="E7" s="747"/>
+      <c r="F7" s="759" t="s">
         <v>45</v>
       </c>
-      <c r="G7" s="756"/>
-      <c r="H7" s="756"/>
-      <c r="I7" s="756"/>
-      <c r="J7" s="757"/>
+      <c r="G7" s="760"/>
+      <c r="H7" s="760"/>
+      <c r="I7" s="760"/>
+      <c r="J7" s="761"/>
     </row>
     <row r="8" spans="1:10" ht="13.8">
       <c r="A8" s="3"/>
-      <c r="B8" s="753" t="s">
+      <c r="B8" s="746" t="s">
         <v>46</v>
       </c>
-      <c r="C8" s="753"/>
-      <c r="D8" s="753"/>
-      <c r="E8" s="754"/>
-      <c r="F8" s="755" t="s">
+      <c r="C8" s="746"/>
+      <c r="D8" s="746"/>
+      <c r="E8" s="747"/>
+      <c r="F8" s="759" t="s">
         <v>47</v>
       </c>
-      <c r="G8" s="756"/>
-      <c r="H8" s="756"/>
-      <c r="I8" s="756"/>
-      <c r="J8" s="757"/>
+      <c r="G8" s="760"/>
+      <c r="H8" s="760"/>
+      <c r="I8" s="760"/>
+      <c r="J8" s="761"/>
     </row>
     <row r="9" spans="1:10" ht="13.8">
       <c r="A9" s="3"/>
-      <c r="B9" s="753" t="s">
+      <c r="B9" s="746" t="s">
         <v>48</v>
       </c>
-      <c r="C9" s="753"/>
-      <c r="D9" s="753"/>
-      <c r="E9" s="754"/>
-      <c r="F9" s="755" t="s">
+      <c r="C9" s="746"/>
+      <c r="D9" s="746"/>
+      <c r="E9" s="747"/>
+      <c r="F9" s="759" t="s">
         <v>49</v>
       </c>
-      <c r="G9" s="756"/>
-      <c r="H9" s="756"/>
-      <c r="I9" s="756"/>
-      <c r="J9" s="757"/>
+      <c r="G9" s="760"/>
+      <c r="H9" s="760"/>
+      <c r="I9" s="760"/>
+      <c r="J9" s="761"/>
     </row>
     <row r="10" spans="1:10" ht="22.2" customHeight="1">
       <c r="A10" s="3"/>
-      <c r="B10" s="753" t="s">
+      <c r="B10" s="746" t="s">
         <v>50</v>
       </c>
-      <c r="C10" s="753"/>
-      <c r="D10" s="753"/>
-      <c r="E10" s="754"/>
-      <c r="F10" s="755" t="s">
+      <c r="C10" s="746"/>
+      <c r="D10" s="746"/>
+      <c r="E10" s="747"/>
+      <c r="F10" s="759" t="s">
         <v>51</v>
       </c>
-      <c r="G10" s="756"/>
-      <c r="H10" s="756"/>
-      <c r="I10" s="756"/>
-      <c r="J10" s="757"/>
+      <c r="G10" s="760"/>
+      <c r="H10" s="760"/>
+      <c r="I10" s="760"/>
+      <c r="J10" s="761"/>
     </row>
     <row r="11" spans="1:10" ht="13.8">
       <c r="A11" s="3"/>
-      <c r="B11" s="753" t="s">
+      <c r="B11" s="746" t="s">
         <v>52</v>
       </c>
-      <c r="C11" s="753"/>
-      <c r="D11" s="753"/>
-      <c r="E11" s="754"/>
-      <c r="F11" s="755" t="s">
+      <c r="C11" s="746"/>
+      <c r="D11" s="746"/>
+      <c r="E11" s="747"/>
+      <c r="F11" s="759" t="s">
         <v>53</v>
       </c>
-      <c r="G11" s="756"/>
-      <c r="H11" s="756"/>
-      <c r="I11" s="756"/>
-      <c r="J11" s="757"/>
+      <c r="G11" s="760"/>
+      <c r="H11" s="760"/>
+      <c r="I11" s="760"/>
+      <c r="J11" s="761"/>
     </row>
     <row r="12" spans="1:10" ht="13.8">
       <c r="A12" s="3"/>
-      <c r="B12" s="753" t="s">
+      <c r="B12" s="746" t="s">
         <v>54</v>
       </c>
-      <c r="C12" s="753"/>
-      <c r="D12" s="753"/>
-      <c r="E12" s="754"/>
-      <c r="F12" s="755" t="s">
+      <c r="C12" s="746"/>
+      <c r="D12" s="746"/>
+      <c r="E12" s="747"/>
+      <c r="F12" s="759" t="s">
         <v>55</v>
       </c>
-      <c r="G12" s="756"/>
-      <c r="H12" s="756"/>
-      <c r="I12" s="756"/>
-      <c r="J12" s="757"/>
+      <c r="G12" s="760"/>
+      <c r="H12" s="760"/>
+      <c r="I12" s="760"/>
+      <c r="J12" s="761"/>
     </row>
     <row r="13" spans="1:10" ht="13.8">
       <c r="A13" s="3"/>
-      <c r="B13" s="753" t="s">
+      <c r="B13" s="746" t="s">
         <v>56</v>
       </c>
-      <c r="C13" s="753"/>
-      <c r="D13" s="753"/>
-      <c r="E13" s="754"/>
-      <c r="F13" s="755" t="s">
+      <c r="C13" s="746"/>
+      <c r="D13" s="746"/>
+      <c r="E13" s="747"/>
+      <c r="F13" s="759" t="s">
         <v>57</v>
       </c>
-      <c r="G13" s="756"/>
-      <c r="H13" s="756"/>
-      <c r="I13" s="756"/>
-      <c r="J13" s="757"/>
+      <c r="G13" s="760"/>
+      <c r="H13" s="760"/>
+      <c r="I13" s="760"/>
+      <c r="J13" s="761"/>
     </row>
     <row r="14" spans="1:10" ht="13.8">
       <c r="A14" s="3"/>
-      <c r="B14" s="753" t="s">
+      <c r="B14" s="746" t="s">
         <v>33</v>
       </c>
-      <c r="C14" s="753"/>
-      <c r="D14" s="753"/>
-      <c r="E14" s="754"/>
-      <c r="F14" s="755" t="s">
+      <c r="C14" s="746"/>
+      <c r="D14" s="746"/>
+      <c r="E14" s="747"/>
+      <c r="F14" s="759" t="s">
         <v>58</v>
       </c>
-      <c r="G14" s="756"/>
-      <c r="H14" s="756"/>
-      <c r="I14" s="756"/>
-      <c r="J14" s="757"/>
+      <c r="G14" s="760"/>
+      <c r="H14" s="760"/>
+      <c r="I14" s="760"/>
+      <c r="J14" s="761"/>
     </row>
     <row r="15" spans="1:10" ht="22.2" customHeight="1">
       <c r="A15" s="3"/>
-      <c r="B15" s="753" t="s">
+      <c r="B15" s="746" t="s">
         <v>59</v>
       </c>
-      <c r="C15" s="753"/>
-      <c r="D15" s="753"/>
-      <c r="E15" s="754"/>
+      <c r="C15" s="746"/>
+      <c r="D15" s="746"/>
+      <c r="E15" s="747"/>
       <c r="F15" s="4" t="s">
         <v>60</v>
       </c>
@@ -14041,12 +14036,12 @@
     </row>
     <row r="16" spans="1:10" ht="25.95" customHeight="1">
       <c r="A16" s="3"/>
-      <c r="B16" s="753" t="s">
+      <c r="B16" s="746" t="s">
         <v>62</v>
       </c>
-      <c r="C16" s="753"/>
-      <c r="D16" s="753"/>
-      <c r="E16" s="754"/>
+      <c r="C16" s="746"/>
+      <c r="D16" s="746"/>
+      <c r="E16" s="747"/>
       <c r="F16" s="4" t="s">
         <v>63</v>
       </c>
@@ -14059,238 +14054,238 @@
     </row>
     <row r="17" spans="1:11" ht="25.95" customHeight="1">
       <c r="A17" s="8"/>
-      <c r="B17" s="758" t="s">
+      <c r="B17" s="737" t="s">
         <v>64</v>
       </c>
-      <c r="C17" s="758"/>
-      <c r="D17" s="758"/>
-      <c r="E17" s="759"/>
-      <c r="F17" s="760" t="s">
+      <c r="C17" s="737"/>
+      <c r="D17" s="737"/>
+      <c r="E17" s="738"/>
+      <c r="F17" s="751" t="s">
         <v>65</v>
       </c>
-      <c r="G17" s="761"/>
-      <c r="H17" s="761"/>
-      <c r="I17" s="761"/>
-      <c r="J17" s="762"/>
+      <c r="G17" s="752"/>
+      <c r="H17" s="752"/>
+      <c r="I17" s="752"/>
+      <c r="J17" s="753"/>
     </row>
     <row r="18" spans="1:11" ht="25.95" customHeight="1">
-      <c r="A18" s="745" t="s">
+      <c r="A18" s="742" t="s">
         <v>66</v>
       </c>
-      <c r="B18" s="746"/>
-      <c r="C18" s="746"/>
-      <c r="D18" s="746"/>
-      <c r="E18" s="746"/>
-      <c r="F18" s="746"/>
-      <c r="G18" s="746"/>
-      <c r="H18" s="746"/>
-      <c r="I18" s="746"/>
-      <c r="J18" s="747"/>
+      <c r="B18" s="743"/>
+      <c r="C18" s="743"/>
+      <c r="D18" s="743"/>
+      <c r="E18" s="743"/>
+      <c r="F18" s="743"/>
+      <c r="G18" s="743"/>
+      <c r="H18" s="743"/>
+      <c r="I18" s="743"/>
+      <c r="J18" s="744"/>
     </row>
     <row r="19" spans="1:11" ht="25.95" customHeight="1">
       <c r="A19" s="2"/>
-      <c r="B19" s="748" t="s">
+      <c r="B19" s="754" t="s">
         <v>67</v>
       </c>
-      <c r="C19" s="748"/>
-      <c r="D19" s="748"/>
-      <c r="E19" s="749"/>
-      <c r="F19" s="763" t="s">
+      <c r="C19" s="754"/>
+      <c r="D19" s="754"/>
+      <c r="E19" s="755"/>
+      <c r="F19" s="756" t="s">
         <v>26</v>
       </c>
-      <c r="G19" s="764"/>
-      <c r="H19" s="764"/>
-      <c r="I19" s="764"/>
-      <c r="J19" s="765"/>
+      <c r="G19" s="757"/>
+      <c r="H19" s="757"/>
+      <c r="I19" s="757"/>
+      <c r="J19" s="758"/>
       <c r="K19" s="9"/>
     </row>
     <row r="20" spans="1:11" ht="13.8">
       <c r="A20" s="3"/>
-      <c r="B20" s="753" t="s">
+      <c r="B20" s="746" t="s">
         <v>68</v>
       </c>
-      <c r="C20" s="753"/>
-      <c r="D20" s="753"/>
-      <c r="E20" s="754"/>
-      <c r="F20" s="766" t="s">
+      <c r="C20" s="746"/>
+      <c r="D20" s="746"/>
+      <c r="E20" s="747"/>
+      <c r="F20" s="748" t="s">
         <v>36</v>
       </c>
-      <c r="G20" s="767"/>
-      <c r="H20" s="767"/>
-      <c r="I20" s="767"/>
-      <c r="J20" s="768"/>
+      <c r="G20" s="749"/>
+      <c r="H20" s="749"/>
+      <c r="I20" s="749"/>
+      <c r="J20" s="750"/>
       <c r="K20" s="9"/>
     </row>
     <row r="21" spans="1:11" ht="13.8">
       <c r="A21" s="3"/>
-      <c r="B21" s="753" t="s">
+      <c r="B21" s="746" t="s">
         <v>69</v>
       </c>
-      <c r="C21" s="753"/>
-      <c r="D21" s="753"/>
-      <c r="E21" s="754"/>
-      <c r="F21" s="766" t="s">
+      <c r="C21" s="746"/>
+      <c r="D21" s="746"/>
+      <c r="E21" s="747"/>
+      <c r="F21" s="748" t="s">
         <v>70</v>
       </c>
-      <c r="G21" s="767"/>
-      <c r="H21" s="767"/>
-      <c r="I21" s="767"/>
-      <c r="J21" s="768"/>
+      <c r="G21" s="749"/>
+      <c r="H21" s="749"/>
+      <c r="I21" s="749"/>
+      <c r="J21" s="750"/>
       <c r="K21" s="9"/>
     </row>
     <row r="22" spans="1:11" ht="13.8">
       <c r="A22" s="3"/>
-      <c r="B22" s="753" t="s">
+      <c r="B22" s="746" t="s">
         <v>71</v>
       </c>
-      <c r="C22" s="753"/>
-      <c r="D22" s="753"/>
-      <c r="E22" s="754"/>
-      <c r="F22" s="766" t="s">
+      <c r="C22" s="746"/>
+      <c r="D22" s="746"/>
+      <c r="E22" s="747"/>
+      <c r="F22" s="748" t="s">
         <v>72</v>
       </c>
-      <c r="G22" s="767"/>
-      <c r="H22" s="767"/>
-      <c r="I22" s="767"/>
-      <c r="J22" s="768"/>
+      <c r="G22" s="749"/>
+      <c r="H22" s="749"/>
+      <c r="I22" s="749"/>
+      <c r="J22" s="750"/>
       <c r="K22" s="9"/>
     </row>
     <row r="23" spans="1:11" ht="13.8">
       <c r="A23" s="3"/>
-      <c r="B23" s="753" t="s">
+      <c r="B23" s="746" t="s">
         <v>39</v>
       </c>
-      <c r="C23" s="753"/>
-      <c r="D23" s="753"/>
-      <c r="E23" s="754"/>
-      <c r="F23" s="766" t="s">
+      <c r="C23" s="746"/>
+      <c r="D23" s="746"/>
+      <c r="E23" s="747"/>
+      <c r="F23" s="748" t="s">
         <v>24</v>
       </c>
-      <c r="G23" s="767"/>
-      <c r="H23" s="767"/>
-      <c r="I23" s="767"/>
-      <c r="J23" s="768"/>
+      <c r="G23" s="749"/>
+      <c r="H23" s="749"/>
+      <c r="I23" s="749"/>
+      <c r="J23" s="750"/>
       <c r="K23" s="9"/>
     </row>
     <row r="24" spans="1:11" ht="13.8">
       <c r="A24" s="3"/>
-      <c r="B24" s="753" t="s">
+      <c r="B24" s="746" t="s">
         <v>23</v>
       </c>
-      <c r="C24" s="753"/>
-      <c r="D24" s="753"/>
-      <c r="E24" s="754"/>
-      <c r="F24" s="766" t="s">
+      <c r="C24" s="746"/>
+      <c r="D24" s="746"/>
+      <c r="E24" s="747"/>
+      <c r="F24" s="748" t="s">
         <v>24</v>
       </c>
-      <c r="G24" s="767"/>
-      <c r="H24" s="767"/>
-      <c r="I24" s="767"/>
-      <c r="J24" s="768"/>
+      <c r="G24" s="749"/>
+      <c r="H24" s="749"/>
+      <c r="I24" s="749"/>
+      <c r="J24" s="750"/>
       <c r="K24" s="9"/>
     </row>
     <row r="25" spans="1:11" ht="13.8">
       <c r="A25" s="3"/>
-      <c r="B25" s="753" t="s">
+      <c r="B25" s="746" t="s">
         <v>73</v>
       </c>
-      <c r="C25" s="753"/>
-      <c r="D25" s="753"/>
-      <c r="E25" s="754"/>
-      <c r="F25" s="766" t="s">
+      <c r="C25" s="746"/>
+      <c r="D25" s="746"/>
+      <c r="E25" s="747"/>
+      <c r="F25" s="748" t="s">
         <v>74</v>
       </c>
-      <c r="G25" s="767"/>
-      <c r="H25" s="767"/>
-      <c r="I25" s="767"/>
-      <c r="J25" s="768"/>
+      <c r="G25" s="749"/>
+      <c r="H25" s="749"/>
+      <c r="I25" s="749"/>
+      <c r="J25" s="750"/>
       <c r="K25" s="9"/>
     </row>
     <row r="26" spans="1:11" ht="13.8">
       <c r="A26" s="8"/>
-      <c r="B26" s="758" t="s">
+      <c r="B26" s="737" t="s">
         <v>75</v>
       </c>
-      <c r="C26" s="758"/>
-      <c r="D26" s="758"/>
-      <c r="E26" s="759"/>
-      <c r="F26" s="769" t="s">
+      <c r="C26" s="737"/>
+      <c r="D26" s="737"/>
+      <c r="E26" s="738"/>
+      <c r="F26" s="739" t="s">
         <v>24</v>
       </c>
-      <c r="G26" s="770"/>
-      <c r="H26" s="770"/>
-      <c r="I26" s="770"/>
-      <c r="J26" s="771"/>
+      <c r="G26" s="740"/>
+      <c r="H26" s="740"/>
+      <c r="I26" s="740"/>
+      <c r="J26" s="741"/>
       <c r="K26" s="9"/>
     </row>
     <row r="27" spans="1:11" ht="15" customHeight="1">
-      <c r="A27" s="745" t="s">
+      <c r="A27" s="742" t="s">
         <v>76</v>
       </c>
-      <c r="B27" s="746"/>
-      <c r="C27" s="746"/>
-      <c r="D27" s="746"/>
-      <c r="E27" s="746"/>
-      <c r="F27" s="746"/>
-      <c r="G27" s="746"/>
-      <c r="H27" s="746"/>
-      <c r="I27" s="746"/>
-      <c r="J27" s="747"/>
+      <c r="B27" s="743"/>
+      <c r="C27" s="743"/>
+      <c r="D27" s="743"/>
+      <c r="E27" s="743"/>
+      <c r="F27" s="743"/>
+      <c r="G27" s="743"/>
+      <c r="H27" s="743"/>
+      <c r="I27" s="743"/>
+      <c r="J27" s="744"/>
     </row>
     <row r="28" spans="1:11" ht="13.8">
       <c r="A28" s="10"/>
-      <c r="B28" s="772" t="s">
+      <c r="B28" s="745" t="s">
         <v>77</v>
       </c>
-      <c r="C28" s="772"/>
-      <c r="D28" s="772"/>
-      <c r="E28" s="772"/>
-      <c r="F28" s="772"/>
-      <c r="G28" s="772"/>
-      <c r="H28" s="772"/>
-      <c r="I28" s="772"/>
+      <c r="C28" s="745"/>
+      <c r="D28" s="745"/>
+      <c r="E28" s="745"/>
+      <c r="F28" s="745"/>
+      <c r="G28" s="745"/>
+      <c r="H28" s="745"/>
+      <c r="I28" s="745"/>
       <c r="J28" s="11"/>
     </row>
     <row r="29" spans="1:11" ht="13.8">
       <c r="A29" s="12"/>
-      <c r="B29" s="773" t="s">
+      <c r="B29" s="736" t="s">
         <v>78</v>
       </c>
-      <c r="C29" s="773"/>
-      <c r="D29" s="773"/>
-      <c r="E29" s="773"/>
-      <c r="F29" s="773"/>
-      <c r="G29" s="773"/>
-      <c r="H29" s="773"/>
-      <c r="I29" s="773"/>
+      <c r="C29" s="736"/>
+      <c r="D29" s="736"/>
+      <c r="E29" s="736"/>
+      <c r="F29" s="736"/>
+      <c r="G29" s="736"/>
+      <c r="H29" s="736"/>
+      <c r="I29" s="736"/>
       <c r="J29" s="13"/>
     </row>
     <row r="30" spans="1:11" ht="13.8">
       <c r="A30" s="12"/>
-      <c r="B30" s="773" t="s">
+      <c r="B30" s="736" t="s">
         <v>79</v>
       </c>
-      <c r="C30" s="773"/>
-      <c r="D30" s="773"/>
-      <c r="E30" s="773"/>
-      <c r="F30" s="773"/>
-      <c r="G30" s="773"/>
-      <c r="H30" s="773"/>
-      <c r="I30" s="773"/>
+      <c r="C30" s="736"/>
+      <c r="D30" s="736"/>
+      <c r="E30" s="736"/>
+      <c r="F30" s="736"/>
+      <c r="G30" s="736"/>
+      <c r="H30" s="736"/>
+      <c r="I30" s="736"/>
       <c r="J30" s="13"/>
     </row>
     <row r="31" spans="1:11" ht="13.8">
       <c r="A31" s="12"/>
-      <c r="B31" s="773" t="s">
+      <c r="B31" s="736" t="s">
         <v>80</v>
       </c>
-      <c r="C31" s="773"/>
-      <c r="D31" s="773"/>
-      <c r="E31" s="773"/>
-      <c r="F31" s="773"/>
-      <c r="G31" s="773"/>
-      <c r="H31" s="773"/>
-      <c r="I31" s="773"/>
+      <c r="C31" s="736"/>
+      <c r="D31" s="736"/>
+      <c r="E31" s="736"/>
+      <c r="F31" s="736"/>
+      <c r="G31" s="736"/>
+      <c r="H31" s="736"/>
+      <c r="I31" s="736"/>
       <c r="J31" s="13"/>
     </row>
     <row r="32" spans="1:11" ht="13.8">
@@ -14307,6 +14302,47 @@
     </row>
   </sheetData>
   <mergeCells count="48">
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A4:J4"/>
+    <mergeCell ref="A5:J5"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="F6:J6"/>
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="F7:J7"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="F8:J8"/>
+    <mergeCell ref="B9:E9"/>
+    <mergeCell ref="F9:J9"/>
+    <mergeCell ref="B10:E10"/>
+    <mergeCell ref="F10:J10"/>
+    <mergeCell ref="B11:E11"/>
+    <mergeCell ref="F11:J11"/>
+    <mergeCell ref="B12:E12"/>
+    <mergeCell ref="F12:J12"/>
+    <mergeCell ref="B13:E13"/>
+    <mergeCell ref="F13:J13"/>
+    <mergeCell ref="B14:E14"/>
+    <mergeCell ref="F14:J14"/>
+    <mergeCell ref="B15:E15"/>
+    <mergeCell ref="B16:E16"/>
+    <mergeCell ref="B17:E17"/>
+    <mergeCell ref="F17:J17"/>
+    <mergeCell ref="A18:J18"/>
+    <mergeCell ref="B19:E19"/>
+    <mergeCell ref="F19:J19"/>
+    <mergeCell ref="B20:E20"/>
+    <mergeCell ref="F20:J20"/>
+    <mergeCell ref="B21:E21"/>
+    <mergeCell ref="F21:J21"/>
+    <mergeCell ref="B22:E22"/>
+    <mergeCell ref="F22:J22"/>
+    <mergeCell ref="B23:E23"/>
+    <mergeCell ref="F23:J23"/>
+    <mergeCell ref="B24:E24"/>
+    <mergeCell ref="F24:J24"/>
+    <mergeCell ref="B25:E25"/>
+    <mergeCell ref="F25:J25"/>
     <mergeCell ref="B30:I30"/>
     <mergeCell ref="B31:I31"/>
     <mergeCell ref="B26:E26"/>
@@ -14314,47 +14350,6 @@
     <mergeCell ref="A27:J27"/>
     <mergeCell ref="B28:I28"/>
     <mergeCell ref="B29:I29"/>
-    <mergeCell ref="B23:E23"/>
-    <mergeCell ref="F23:J23"/>
-    <mergeCell ref="B24:E24"/>
-    <mergeCell ref="F24:J24"/>
-    <mergeCell ref="B25:E25"/>
-    <mergeCell ref="F25:J25"/>
-    <mergeCell ref="B20:E20"/>
-    <mergeCell ref="F20:J20"/>
-    <mergeCell ref="B21:E21"/>
-    <mergeCell ref="F21:J21"/>
-    <mergeCell ref="B22:E22"/>
-    <mergeCell ref="F22:J22"/>
-    <mergeCell ref="B16:E16"/>
-    <mergeCell ref="B17:E17"/>
-    <mergeCell ref="F17:J17"/>
-    <mergeCell ref="A18:J18"/>
-    <mergeCell ref="B19:E19"/>
-    <mergeCell ref="F19:J19"/>
-    <mergeCell ref="B13:E13"/>
-    <mergeCell ref="F13:J13"/>
-    <mergeCell ref="B14:E14"/>
-    <mergeCell ref="F14:J14"/>
-    <mergeCell ref="B15:E15"/>
-    <mergeCell ref="B10:E10"/>
-    <mergeCell ref="F10:J10"/>
-    <mergeCell ref="B11:E11"/>
-    <mergeCell ref="F11:J11"/>
-    <mergeCell ref="B12:E12"/>
-    <mergeCell ref="F12:J12"/>
-    <mergeCell ref="B7:E7"/>
-    <mergeCell ref="F7:J7"/>
-    <mergeCell ref="B8:E8"/>
-    <mergeCell ref="F8:J8"/>
-    <mergeCell ref="B9:E9"/>
-    <mergeCell ref="F9:J9"/>
-    <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A3:J3"/>
-    <mergeCell ref="A4:J4"/>
-    <mergeCell ref="A5:J5"/>
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="F6:J6"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.35" right="0.35" top="0.55000000000000004" bottom="0.55000000000000004" header="0.2" footer="0.2"/>
@@ -14404,64 +14399,64 @@
       <c r="H2" s="775"/>
     </row>
     <row r="3" spans="1:8" ht="4.95" customHeight="1">
-      <c r="A3" s="914"/>
-      <c r="B3" s="915"/>
-      <c r="C3" s="915"/>
-      <c r="D3" s="915"/>
-      <c r="E3" s="915"/>
-      <c r="F3" s="915"/>
-      <c r="G3" s="915"/>
-      <c r="H3" s="915"/>
+      <c r="A3" s="920"/>
+      <c r="B3" s="921"/>
+      <c r="C3" s="921"/>
+      <c r="D3" s="921"/>
+      <c r="E3" s="921"/>
+      <c r="F3" s="921"/>
+      <c r="G3" s="921"/>
+      <c r="H3" s="921"/>
     </row>
     <row r="4" spans="1:8" ht="24" customHeight="1">
-      <c r="B4" s="916" t="s">
+      <c r="B4" s="922" t="s">
         <v>24</v>
       </c>
-      <c r="C4" s="917"/>
-      <c r="D4" s="917"/>
-      <c r="E4" s="917"/>
-      <c r="F4" s="917"/>
-      <c r="G4" s="917"/>
+      <c r="C4" s="919"/>
+      <c r="D4" s="919"/>
+      <c r="E4" s="919"/>
+      <c r="F4" s="919"/>
+      <c r="G4" s="919"/>
     </row>
     <row r="6" spans="1:8" ht="64.95" customHeight="1">
-      <c r="B6" s="920" t="s">
+      <c r="B6" s="914" t="s">
         <v>711</v>
       </c>
-      <c r="C6" s="921"/>
-      <c r="D6" s="921"/>
-      <c r="E6" s="921"/>
-      <c r="F6" s="921"/>
-      <c r="G6" s="921"/>
+      <c r="C6" s="915"/>
+      <c r="D6" s="915"/>
+      <c r="E6" s="915"/>
+      <c r="F6" s="915"/>
+      <c r="G6" s="915"/>
     </row>
     <row r="8" spans="1:8" ht="42" customHeight="1">
-      <c r="B8" s="920" t="s">
+      <c r="B8" s="914" t="s">
         <v>712</v>
       </c>
-      <c r="C8" s="921"/>
-      <c r="D8" s="921"/>
-      <c r="E8" s="921"/>
-      <c r="F8" s="921"/>
-      <c r="G8" s="921"/>
+      <c r="C8" s="915"/>
+      <c r="D8" s="915"/>
+      <c r="E8" s="915"/>
+      <c r="F8" s="915"/>
+      <c r="G8" s="915"/>
     </row>
     <row r="10" spans="1:8" ht="52.2" customHeight="1">
-      <c r="B10" s="920" t="s">
+      <c r="B10" s="914" t="s">
         <v>713</v>
       </c>
-      <c r="C10" s="921"/>
-      <c r="D10" s="921"/>
-      <c r="E10" s="921"/>
-      <c r="F10" s="921"/>
-      <c r="G10" s="921"/>
+      <c r="C10" s="915"/>
+      <c r="D10" s="915"/>
+      <c r="E10" s="915"/>
+      <c r="F10" s="915"/>
+      <c r="G10" s="915"/>
     </row>
     <row r="12" spans="1:8" ht="79.95" customHeight="1">
-      <c r="B12" s="922" t="s">
+      <c r="B12" s="918" t="s">
         <v>714</v>
       </c>
-      <c r="C12" s="917"/>
-      <c r="D12" s="917"/>
-      <c r="E12" s="917"/>
-      <c r="F12" s="917"/>
-      <c r="G12" s="917"/>
+      <c r="C12" s="919"/>
+      <c r="D12" s="919"/>
+      <c r="E12" s="919"/>
+      <c r="F12" s="919"/>
+      <c r="G12" s="919"/>
     </row>
     <row r="14" spans="1:8" ht="39" customHeight="1">
       <c r="B14" s="779" t="s">
@@ -14526,10 +14521,10 @@
       <c r="D2" s="775"/>
     </row>
     <row r="3" spans="1:4" ht="4.95" customHeight="1">
-      <c r="A3" s="914"/>
-      <c r="B3" s="915"/>
-      <c r="C3" s="915"/>
-      <c r="D3" s="915"/>
+      <c r="A3" s="920"/>
+      <c r="B3" s="921"/>
+      <c r="C3" s="921"/>
+      <c r="D3" s="921"/>
     </row>
     <row r="4" spans="1:4" ht="22.2" customHeight="1">
       <c r="A4" s="17" t="s">
@@ -14709,10 +14704,10 @@
       <c r="D2" s="775"/>
     </row>
     <row r="3" spans="1:4" ht="4.95" customHeight="1">
-      <c r="A3" s="914"/>
-      <c r="B3" s="915"/>
-      <c r="C3" s="915"/>
-      <c r="D3" s="915"/>
+      <c r="A3" s="920"/>
+      <c r="B3" s="921"/>
+      <c r="C3" s="921"/>
+      <c r="D3" s="921"/>
     </row>
     <row r="4" spans="1:4" ht="22.2" customHeight="1">
       <c r="A4" s="17" t="s">
@@ -15070,10 +15065,10 @@
       <c r="D2" s="775"/>
     </row>
     <row r="3" spans="1:4" ht="4.95" customHeight="1">
-      <c r="A3" s="914"/>
-      <c r="B3" s="915"/>
-      <c r="C3" s="915"/>
-      <c r="D3" s="915"/>
+      <c r="A3" s="920"/>
+      <c r="B3" s="921"/>
+      <c r="C3" s="921"/>
+      <c r="D3" s="921"/>
     </row>
     <row r="4" spans="1:4" ht="22.2" customHeight="1">
       <c r="A4" s="17" t="s">
@@ -15427,10 +15422,10 @@
       <c r="D2" s="775"/>
     </row>
     <row r="3" spans="1:4" ht="4.95" customHeight="1">
-      <c r="A3" s="914"/>
-      <c r="B3" s="915"/>
-      <c r="C3" s="915"/>
-      <c r="D3" s="915"/>
+      <c r="A3" s="920"/>
+      <c r="B3" s="921"/>
+      <c r="C3" s="921"/>
+      <c r="D3" s="921"/>
     </row>
     <row r="4" spans="1:4" ht="22.2" customHeight="1">
       <c r="A4" s="17" t="s">
@@ -15910,12 +15905,12 @@
       <c r="F2" s="775"/>
     </row>
     <row r="3" spans="1:6" ht="4.95" customHeight="1">
-      <c r="A3" s="914"/>
-      <c r="B3" s="915"/>
-      <c r="C3" s="915"/>
-      <c r="D3" s="915"/>
-      <c r="E3" s="915"/>
-      <c r="F3" s="915"/>
+      <c r="A3" s="920"/>
+      <c r="B3" s="921"/>
+      <c r="C3" s="921"/>
+      <c r="D3" s="921"/>
+      <c r="E3" s="921"/>
+      <c r="F3" s="921"/>
     </row>
     <row r="4" spans="1:6" ht="22.2" customHeight="1">
       <c r="A4" s="17" t="s">
@@ -16071,15 +16066,15 @@
       <c r="I2" s="775"/>
     </row>
     <row r="3" spans="1:9" ht="4.95" customHeight="1">
-      <c r="A3" s="914"/>
-      <c r="B3" s="915"/>
-      <c r="C3" s="915"/>
-      <c r="D3" s="915"/>
-      <c r="E3" s="915"/>
-      <c r="F3" s="915"/>
-      <c r="G3" s="915"/>
-      <c r="H3" s="915"/>
-      <c r="I3" s="915"/>
+      <c r="A3" s="920"/>
+      <c r="B3" s="921"/>
+      <c r="C3" s="921"/>
+      <c r="D3" s="921"/>
+      <c r="E3" s="921"/>
+      <c r="F3" s="921"/>
+      <c r="G3" s="921"/>
+      <c r="H3" s="921"/>
+      <c r="I3" s="921"/>
     </row>
     <row r="4" spans="1:9" ht="22.2" customHeight="1">
       <c r="A4" s="17" t="s">
@@ -16347,14 +16342,14 @@
       <c r="H2" s="775"/>
     </row>
     <row r="3" spans="1:8" ht="4.95" customHeight="1">
-      <c r="A3" s="914"/>
-      <c r="B3" s="915"/>
-      <c r="C3" s="915"/>
-      <c r="D3" s="915"/>
-      <c r="E3" s="915"/>
-      <c r="F3" s="915"/>
-      <c r="G3" s="915"/>
-      <c r="H3" s="915"/>
+      <c r="A3" s="920"/>
+      <c r="B3" s="921"/>
+      <c r="C3" s="921"/>
+      <c r="D3" s="921"/>
+      <c r="E3" s="921"/>
+      <c r="F3" s="921"/>
+      <c r="G3" s="921"/>
+      <c r="H3" s="921"/>
     </row>
     <row r="4" spans="1:8" ht="22.2" customHeight="1">
       <c r="A4" s="17" t="s">
@@ -16590,14 +16585,14 @@
       <c r="H2" s="775"/>
     </row>
     <row r="3" spans="1:8" ht="4.95" customHeight="1">
-      <c r="A3" s="914"/>
-      <c r="B3" s="915"/>
-      <c r="C3" s="915"/>
-      <c r="D3" s="915"/>
-      <c r="E3" s="915"/>
-      <c r="F3" s="915"/>
-      <c r="G3" s="915"/>
-      <c r="H3" s="915"/>
+      <c r="A3" s="920"/>
+      <c r="B3" s="921"/>
+      <c r="C3" s="921"/>
+      <c r="D3" s="921"/>
+      <c r="E3" s="921"/>
+      <c r="F3" s="921"/>
+      <c r="G3" s="921"/>
+      <c r="H3" s="921"/>
     </row>
     <row r="4" spans="1:8" ht="22.2" customHeight="1">
       <c r="A4" s="17" t="s">
@@ -16815,14 +16810,14 @@
       <c r="H2" s="775"/>
     </row>
     <row r="3" spans="1:8" ht="4.95" customHeight="1">
-      <c r="A3" s="914"/>
-      <c r="B3" s="915"/>
-      <c r="C3" s="915"/>
-      <c r="D3" s="915"/>
-      <c r="E3" s="915"/>
-      <c r="F3" s="915"/>
-      <c r="G3" s="915"/>
-      <c r="H3" s="915"/>
+      <c r="A3" s="920"/>
+      <c r="B3" s="921"/>
+      <c r="C3" s="921"/>
+      <c r="D3" s="921"/>
+      <c r="E3" s="921"/>
+      <c r="F3" s="921"/>
+      <c r="G3" s="921"/>
+      <c r="H3" s="921"/>
     </row>
     <row r="4" spans="1:8" ht="22.2" customHeight="1">
       <c r="A4" s="17" t="s">
@@ -17752,30 +17747,30 @@
       <c r="J2" s="775"/>
     </row>
     <row r="3" spans="1:10" ht="4.95" customHeight="1">
-      <c r="A3" s="914"/>
-      <c r="B3" s="915"/>
-      <c r="C3" s="915"/>
-      <c r="D3" s="915"/>
-      <c r="E3" s="915"/>
-      <c r="F3" s="915"/>
-      <c r="G3" s="915"/>
-      <c r="H3" s="915"/>
-      <c r="I3" s="915"/>
-      <c r="J3" s="915"/>
+      <c r="A3" s="920"/>
+      <c r="B3" s="921"/>
+      <c r="C3" s="921"/>
+      <c r="D3" s="921"/>
+      <c r="E3" s="921"/>
+      <c r="F3" s="921"/>
+      <c r="G3" s="921"/>
+      <c r="H3" s="921"/>
+      <c r="I3" s="921"/>
+      <c r="J3" s="921"/>
     </row>
     <row r="4" spans="1:10" ht="48" customHeight="1">
       <c r="A4" s="923" t="s">
         <v>957</v>
       </c>
-      <c r="B4" s="917"/>
-      <c r="C4" s="917"/>
-      <c r="D4" s="917"/>
-      <c r="E4" s="917"/>
-      <c r="F4" s="917"/>
-      <c r="G4" s="917"/>
-      <c r="H4" s="917"/>
-      <c r="I4" s="917"/>
-      <c r="J4" s="917"/>
+      <c r="B4" s="919"/>
+      <c r="C4" s="919"/>
+      <c r="D4" s="919"/>
+      <c r="E4" s="919"/>
+      <c r="F4" s="919"/>
+      <c r="G4" s="919"/>
+      <c r="H4" s="919"/>
+      <c r="I4" s="919"/>
+      <c r="J4" s="919"/>
     </row>
     <row r="5" spans="1:10" ht="22.2" customHeight="1">
       <c r="A5" s="17" t="s">
@@ -18027,14 +18022,14 @@
       <c r="H2" s="775"/>
     </row>
     <row r="3" spans="1:8" ht="4.95" customHeight="1">
-      <c r="A3" s="914"/>
-      <c r="B3" s="915"/>
-      <c r="C3" s="915"/>
-      <c r="D3" s="915"/>
-      <c r="E3" s="915"/>
-      <c r="F3" s="915"/>
-      <c r="G3" s="915"/>
-      <c r="H3" s="915"/>
+      <c r="A3" s="920"/>
+      <c r="B3" s="921"/>
+      <c r="C3" s="921"/>
+      <c r="D3" s="921"/>
+      <c r="E3" s="921"/>
+      <c r="F3" s="921"/>
+      <c r="G3" s="921"/>
+      <c r="H3" s="921"/>
     </row>
     <row r="4" spans="1:8" ht="22.2" customHeight="1">
       <c r="A4" s="17" t="s">
@@ -18251,12 +18246,12 @@
       <c r="F2" s="775"/>
     </row>
     <row r="3" spans="1:6" ht="4.95" customHeight="1">
-      <c r="A3" s="914"/>
-      <c r="B3" s="915"/>
-      <c r="C3" s="915"/>
-      <c r="D3" s="915"/>
-      <c r="E3" s="915"/>
-      <c r="F3" s="915"/>
+      <c r="A3" s="920"/>
+      <c r="B3" s="921"/>
+      <c r="C3" s="921"/>
+      <c r="D3" s="921"/>
+      <c r="E3" s="921"/>
+      <c r="F3" s="921"/>
     </row>
     <row r="4" spans="1:6" ht="22.2" customHeight="1">
       <c r="A4" s="17" t="s">
@@ -18465,16 +18460,16 @@
       <c r="J2" s="775"/>
     </row>
     <row r="3" spans="1:10" ht="4.95" customHeight="1">
-      <c r="A3" s="914"/>
-      <c r="B3" s="915"/>
-      <c r="C3" s="915"/>
-      <c r="D3" s="915"/>
-      <c r="E3" s="915"/>
-      <c r="F3" s="915"/>
-      <c r="G3" s="915"/>
-      <c r="H3" s="915"/>
-      <c r="I3" s="915"/>
-      <c r="J3" s="915"/>
+      <c r="A3" s="920"/>
+      <c r="B3" s="921"/>
+      <c r="C3" s="921"/>
+      <c r="D3" s="921"/>
+      <c r="E3" s="921"/>
+      <c r="F3" s="921"/>
+      <c r="G3" s="921"/>
+      <c r="H3" s="921"/>
+      <c r="I3" s="921"/>
+      <c r="J3" s="921"/>
     </row>
     <row r="4" spans="1:10" ht="22.2" customHeight="1">
       <c r="A4" s="17" t="s">
@@ -18757,14 +18752,14 @@
       <c r="H2" s="775"/>
     </row>
     <row r="3" spans="1:8" ht="4.95" customHeight="1">
-      <c r="A3" s="914"/>
-      <c r="B3" s="915"/>
-      <c r="C3" s="915"/>
-      <c r="D3" s="915"/>
-      <c r="E3" s="915"/>
-      <c r="F3" s="915"/>
-      <c r="G3" s="915"/>
-      <c r="H3" s="915"/>
+      <c r="A3" s="920"/>
+      <c r="B3" s="921"/>
+      <c r="C3" s="921"/>
+      <c r="D3" s="921"/>
+      <c r="E3" s="921"/>
+      <c r="F3" s="921"/>
+      <c r="G3" s="921"/>
+      <c r="H3" s="921"/>
     </row>
     <row r="4" spans="1:8" ht="22.2" customHeight="1">
       <c r="A4" s="17" t="s">
@@ -18975,11 +18970,11 @@
       <c r="E2" s="775"/>
     </row>
     <row r="3" spans="1:5" ht="4.95" customHeight="1">
-      <c r="A3" s="914"/>
-      <c r="B3" s="915"/>
-      <c r="C3" s="915"/>
-      <c r="D3" s="915"/>
-      <c r="E3" s="915"/>
+      <c r="A3" s="920"/>
+      <c r="B3" s="921"/>
+      <c r="C3" s="921"/>
+      <c r="D3" s="921"/>
+      <c r="E3" s="921"/>
     </row>
     <row r="4" spans="1:5" ht="22.2" customHeight="1">
       <c r="A4" s="17" t="s">
@@ -19117,13 +19112,13 @@
       <c r="G2" s="775"/>
     </row>
     <row r="3" spans="1:7" ht="4.95" customHeight="1">
-      <c r="A3" s="914"/>
-      <c r="B3" s="915"/>
-      <c r="C3" s="915"/>
-      <c r="D3" s="915"/>
-      <c r="E3" s="915"/>
-      <c r="F3" s="915"/>
-      <c r="G3" s="915"/>
+      <c r="A3" s="920"/>
+      <c r="B3" s="921"/>
+      <c r="C3" s="921"/>
+      <c r="D3" s="921"/>
+      <c r="E3" s="921"/>
+      <c r="F3" s="921"/>
+      <c r="G3" s="921"/>
     </row>
     <row r="4" spans="1:7" ht="22.2" customHeight="1">
       <c r="A4" s="17" t="s">
@@ -19306,10 +19301,10 @@
       <c r="D2" s="775"/>
     </row>
     <row r="3" spans="1:4" ht="4.95" customHeight="1">
-      <c r="A3" s="914"/>
-      <c r="B3" s="915"/>
-      <c r="C3" s="915"/>
-      <c r="D3" s="915"/>
+      <c r="A3" s="920"/>
+      <c r="B3" s="921"/>
+      <c r="C3" s="921"/>
+      <c r="D3" s="921"/>
     </row>
     <row r="4" spans="1:4" ht="22.2" customHeight="1">
       <c r="A4" s="17" t="s">
@@ -19658,9 +19653,9 @@
       <c r="C2" s="775"/>
     </row>
     <row r="3" spans="1:3" ht="4.95" customHeight="1">
-      <c r="A3" s="914"/>
-      <c r="B3" s="915"/>
-      <c r="C3" s="915"/>
+      <c r="A3" s="920"/>
+      <c r="B3" s="921"/>
+      <c r="C3" s="921"/>
     </row>
     <row r="4" spans="1:3" ht="22.2" customHeight="1">
       <c r="A4" s="17" t="s">
@@ -19793,13 +19788,13 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:7" ht="22.5" customHeight="1">
-      <c r="B2" s="781" t="s">
+      <c r="B2" s="785" t="s">
         <v>43</v>
       </c>
-      <c r="C2" s="782"/>
-      <c r="D2" s="782"/>
-      <c r="E2" s="782"/>
-      <c r="F2" s="782"/>
+      <c r="C2" s="786"/>
+      <c r="D2" s="786"/>
+      <c r="E2" s="786"/>
+      <c r="F2" s="786"/>
     </row>
     <row r="3" spans="2:7" ht="6" customHeight="1">
       <c r="B3" s="26"/>
@@ -19809,27 +19804,27 @@
       <c r="F3" s="27"/>
     </row>
     <row r="4" spans="2:7" ht="13.5" customHeight="1">
-      <c r="B4" s="783" t="s">
+      <c r="B4" s="787" t="s">
         <v>132</v>
       </c>
-      <c r="C4" s="784"/>
-      <c r="D4" s="784"/>
-      <c r="E4" s="784"/>
-      <c r="F4" s="784"/>
+      <c r="C4" s="788"/>
+      <c r="D4" s="788"/>
+      <c r="E4" s="788"/>
+      <c r="F4" s="788"/>
     </row>
     <row r="5" spans="2:7" ht="15.75" customHeight="1">
       <c r="B5" s="30"/>
-      <c r="E5" s="785" t="s">
+      <c r="E5" s="789" t="s">
         <v>133</v>
       </c>
-      <c r="F5" s="786"/>
+      <c r="F5" s="790"/>
     </row>
     <row r="6" spans="2:7" ht="13.5" customHeight="1">
-      <c r="B6" s="787" t="s">
+      <c r="B6" s="791" t="s">
         <v>134</v>
       </c>
-      <c r="C6" s="788"/>
-      <c r="D6" s="788" t="s">
+      <c r="C6" s="792"/>
+      <c r="D6" s="792" t="s">
         <v>135</v>
       </c>
       <c r="E6" s="33" t="s">
@@ -19840,9 +19835,9 @@
       </c>
     </row>
     <row r="7" spans="2:7" ht="15" customHeight="1">
-      <c r="B7" s="789"/>
-      <c r="C7" s="789"/>
-      <c r="D7" s="788"/>
+      <c r="B7" s="793"/>
+      <c r="C7" s="793"/>
+      <c r="D7" s="792"/>
       <c r="E7" s="34" t="s">
         <v>60</v>
       </c>
@@ -20050,17 +20045,17 @@
         <v>150</v>
       </c>
       <c r="C25" s="60"/>
-      <c r="D25" s="792">
+      <c r="D25" s="783">
         <v>4</v>
       </c>
       <c r="E25" s="50"/>
       <c r="F25" s="50"/>
     </row>
     <row r="26" spans="2:7" ht="12" customHeight="1">
-      <c r="B26" s="790" t="s">
+      <c r="B26" s="781" t="s">
         <v>151</v>
       </c>
-      <c r="C26" s="791"/>
+      <c r="C26" s="782"/>
       <c r="D26" s="778"/>
       <c r="E26" s="50">
         <f>'Note BS-Liab'!G106</f>
@@ -20072,10 +20067,10 @@
       </c>
     </row>
     <row r="27" spans="2:7" ht="12" customHeight="1">
-      <c r="B27" s="793" t="s">
+      <c r="B27" s="784" t="s">
         <v>152</v>
       </c>
-      <c r="C27" s="791"/>
+      <c r="C27" s="782"/>
       <c r="D27" s="778"/>
       <c r="E27" s="50">
         <v>-387035.18</v>
@@ -21023,15 +21018,15 @@
     </row>
     <row r="2" spans="1:25" s="23" customFormat="1" ht="18" customHeight="1">
       <c r="A2" s="32"/>
-      <c r="B2" s="781" t="s">
+      <c r="B2" s="785" t="s">
         <v>43</v>
       </c>
-      <c r="C2" s="781"/>
-      <c r="D2" s="781"/>
-      <c r="E2" s="781"/>
-      <c r="F2" s="781"/>
-      <c r="G2" s="781"/>
-      <c r="H2" s="781"/>
+      <c r="C2" s="785"/>
+      <c r="D2" s="785"/>
+      <c r="E2" s="785"/>
+      <c r="F2" s="785"/>
+      <c r="G2" s="785"/>
+      <c r="H2" s="785"/>
       <c r="J2" s="32"/>
       <c r="K2" s="32"/>
       <c r="L2" s="32"/>
@@ -21059,15 +21054,15 @@
     </row>
     <row r="4" spans="1:25" s="23" customFormat="1" ht="15" customHeight="1">
       <c r="A4" s="32"/>
-      <c r="B4" s="794" t="s">
+      <c r="B4" s="801" t="s">
         <v>187</v>
       </c>
-      <c r="C4" s="794"/>
-      <c r="D4" s="794"/>
-      <c r="E4" s="794"/>
-      <c r="F4" s="794"/>
-      <c r="G4" s="794"/>
-      <c r="H4" s="794"/>
+      <c r="C4" s="801"/>
+      <c r="D4" s="801"/>
+      <c r="E4" s="801"/>
+      <c r="F4" s="801"/>
+      <c r="G4" s="801"/>
+      <c r="H4" s="801"/>
       <c r="I4" s="29"/>
       <c r="J4" s="29"/>
       <c r="K4" s="29"/>
@@ -21091,10 +21086,10 @@
       <c r="D5" s="99"/>
       <c r="E5" s="99"/>
       <c r="F5" s="99"/>
-      <c r="G5" s="785" t="s">
+      <c r="G5" s="789" t="s">
         <v>133</v>
       </c>
-      <c r="H5" s="786"/>
+      <c r="H5" s="790"/>
       <c r="J5" s="32"/>
       <c r="K5" s="32"/>
       <c r="L5" s="32"/>
@@ -21112,19 +21107,19 @@
       <c r="T5" s="32"/>
     </row>
     <row r="6" spans="1:25" ht="22.2" customHeight="1">
-      <c r="B6" s="787" t="s">
+      <c r="B6" s="791" t="s">
         <v>134</v>
       </c>
-      <c r="C6" s="787"/>
-      <c r="D6" s="787"/>
-      <c r="E6" s="787"/>
-      <c r="F6" s="787" t="s">
+      <c r="C6" s="791"/>
+      <c r="D6" s="791"/>
+      <c r="E6" s="791"/>
+      <c r="F6" s="791" t="s">
         <v>135</v>
       </c>
-      <c r="G6" s="787" t="s">
+      <c r="G6" s="791" t="s">
         <v>60</v>
       </c>
-      <c r="H6" s="787" t="s">
+      <c r="H6" s="791" t="s">
         <v>63</v>
       </c>
       <c r="I6" s="101"/>
@@ -21140,13 +21135,13 @@
       </c>
     </row>
     <row r="7" spans="1:25" ht="16.5" customHeight="1">
-      <c r="B7" s="787"/>
-      <c r="C7" s="787"/>
-      <c r="D7" s="787"/>
-      <c r="E7" s="787"/>
-      <c r="F7" s="789"/>
-      <c r="G7" s="789"/>
-      <c r="H7" s="789"/>
+      <c r="B7" s="791"/>
+      <c r="C7" s="791"/>
+      <c r="D7" s="791"/>
+      <c r="E7" s="791"/>
+      <c r="F7" s="793"/>
+      <c r="G7" s="793"/>
+      <c r="H7" s="793"/>
       <c r="R7" s="103">
         <v>23366245.879999999</v>
       </c>
@@ -21318,11 +21313,11 @@
     </row>
     <row r="16" spans="1:25" ht="25.5" customHeight="1">
       <c r="B16" s="132"/>
-      <c r="C16" s="795" t="s">
+      <c r="C16" s="794" t="s">
         <v>199</v>
       </c>
-      <c r="D16" s="795"/>
-      <c r="E16" s="796"/>
+      <c r="D16" s="794"/>
+      <c r="E16" s="795"/>
       <c r="F16" s="136" t="s">
         <v>24</v>
       </c>
@@ -21670,11 +21665,11 @@
       <c r="B28" s="145" t="s">
         <v>221</v>
       </c>
-      <c r="C28" s="797" t="s">
+      <c r="C28" s="796" t="s">
         <v>222</v>
       </c>
-      <c r="D28" s="798"/>
-      <c r="E28" s="799"/>
+      <c r="D28" s="797"/>
+      <c r="E28" s="798"/>
       <c r="F28" s="126"/>
       <c r="G28" s="148">
         <f>G23-G27</f>
@@ -21702,7 +21697,7 @@
       </c>
       <c r="D29" s="120"/>
       <c r="E29" s="121"/>
-      <c r="F29" s="800" t="s">
+      <c r="F29" s="799" t="s">
         <v>24</v>
       </c>
       <c r="G29" s="131"/>
@@ -21731,7 +21726,7 @@
       </c>
       <c r="D30" s="120"/>
       <c r="E30" s="121"/>
-      <c r="F30" s="801"/>
+      <c r="F30" s="800"/>
       <c r="G30" s="64">
         <v>2310</v>
       </c>
@@ -21759,7 +21754,7 @@
       </c>
       <c r="D31" s="120"/>
       <c r="E31" s="121"/>
-      <c r="F31" s="801"/>
+      <c r="F31" s="800"/>
       <c r="G31" s="131">
         <v>1622</v>
       </c>
@@ -22221,16 +22216,16 @@
   <sheetData>
     <row r="1" spans="1:22" s="23" customFormat="1" ht="19.5" customHeight="1">
       <c r="A1" s="27"/>
-      <c r="B1" s="781" t="s">
+      <c r="B1" s="785" t="s">
         <v>43</v>
       </c>
-      <c r="C1" s="781"/>
-      <c r="D1" s="781"/>
-      <c r="E1" s="781"/>
-      <c r="F1" s="781"/>
-      <c r="G1" s="781"/>
-      <c r="H1" s="781"/>
-      <c r="I1" s="781"/>
+      <c r="C1" s="785"/>
+      <c r="D1" s="785"/>
+      <c r="E1" s="785"/>
+      <c r="F1" s="785"/>
+      <c r="G1" s="785"/>
+      <c r="H1" s="785"/>
+      <c r="I1" s="785"/>
       <c r="J1" s="172"/>
       <c r="K1" s="172"/>
       <c r="L1" s="25"/>
@@ -22240,13 +22235,13 @@
     <row r="2" spans="1:22" s="23" customFormat="1" ht="6" customHeight="1">
       <c r="A2" s="29"/>
       <c r="B2" s="98"/>
-      <c r="C2" s="783"/>
-      <c r="D2" s="783"/>
-      <c r="E2" s="783"/>
-      <c r="F2" s="783"/>
-      <c r="G2" s="783"/>
-      <c r="H2" s="783"/>
-      <c r="I2" s="783"/>
+      <c r="C2" s="787"/>
+      <c r="D2" s="787"/>
+      <c r="E2" s="787"/>
+      <c r="F2" s="787"/>
+      <c r="G2" s="787"/>
+      <c r="H2" s="787"/>
+      <c r="I2" s="787"/>
       <c r="J2" s="98"/>
       <c r="K2" s="98"/>
       <c r="L2" s="98"/>
@@ -22255,16 +22250,16 @@
     </row>
     <row r="3" spans="1:22" s="23" customFormat="1" ht="15.75" customHeight="1">
       <c r="A3" s="29"/>
-      <c r="B3" s="794" t="s">
+      <c r="B3" s="801" t="s">
         <v>242</v>
       </c>
-      <c r="C3" s="794"/>
-      <c r="D3" s="794"/>
-      <c r="E3" s="794"/>
-      <c r="F3" s="794"/>
-      <c r="G3" s="794"/>
-      <c r="H3" s="794"/>
-      <c r="I3" s="794"/>
+      <c r="C3" s="801"/>
+      <c r="D3" s="801"/>
+      <c r="E3" s="801"/>
+      <c r="F3" s="801"/>
+      <c r="G3" s="801"/>
+      <c r="H3" s="801"/>
+      <c r="I3" s="801"/>
       <c r="J3" s="172"/>
       <c r="K3" s="172"/>
       <c r="L3" s="25"/>
@@ -22278,26 +22273,26 @@
       <c r="E4" s="23"/>
       <c r="F4" s="23"/>
       <c r="G4" s="23"/>
-      <c r="H4" s="785" t="s">
+      <c r="H4" s="789" t="s">
         <v>133</v>
       </c>
-      <c r="I4" s="786"/>
+      <c r="I4" s="790"/>
       <c r="J4" s="173"/>
       <c r="K4" s="173"/>
     </row>
     <row r="5" spans="1:22" ht="15.75" customHeight="1">
-      <c r="B5" s="788" t="s">
+      <c r="B5" s="792" t="s">
         <v>134</v>
       </c>
-      <c r="C5" s="788"/>
-      <c r="D5" s="788"/>
-      <c r="E5" s="788"/>
-      <c r="F5" s="788"/>
-      <c r="G5" s="788"/>
-      <c r="H5" s="787" t="s">
+      <c r="C5" s="792"/>
+      <c r="D5" s="792"/>
+      <c r="E5" s="792"/>
+      <c r="F5" s="792"/>
+      <c r="G5" s="792"/>
+      <c r="H5" s="791" t="s">
         <v>243</v>
       </c>
-      <c r="I5" s="787" t="s">
+      <c r="I5" s="791" t="s">
         <v>243</v>
       </c>
       <c r="J5" s="174"/>
@@ -22305,14 +22300,14 @@
       <c r="L5" s="175"/>
     </row>
     <row r="6" spans="1:22" ht="12" customHeight="1">
-      <c r="B6" s="788"/>
-      <c r="C6" s="788"/>
-      <c r="D6" s="788"/>
-      <c r="E6" s="788"/>
-      <c r="F6" s="788"/>
-      <c r="G6" s="788"/>
-      <c r="H6" s="789"/>
-      <c r="I6" s="789"/>
+      <c r="B6" s="792"/>
+      <c r="C6" s="792"/>
+      <c r="D6" s="792"/>
+      <c r="E6" s="792"/>
+      <c r="F6" s="792"/>
+      <c r="G6" s="792"/>
+      <c r="H6" s="793"/>
+      <c r="I6" s="793"/>
       <c r="J6" s="174"/>
       <c r="K6" s="174"/>
     </row>
@@ -23341,38 +23336,38 @@
       <c r="G1" s="212"/>
     </row>
     <row r="2" spans="1:9" ht="15.75" customHeight="1">
-      <c r="A2" s="805" t="s">
+      <c r="A2" s="834" t="s">
         <v>43</v>
       </c>
-      <c r="B2" s="806"/>
-      <c r="C2" s="806"/>
-      <c r="D2" s="806"/>
-      <c r="E2" s="806"/>
-      <c r="F2" s="806"/>
-      <c r="G2" s="807"/>
-      <c r="H2" s="806"/>
+      <c r="B2" s="835"/>
+      <c r="C2" s="835"/>
+      <c r="D2" s="835"/>
+      <c r="E2" s="835"/>
+      <c r="F2" s="835"/>
+      <c r="G2" s="836"/>
+      <c r="H2" s="835"/>
     </row>
     <row r="3" spans="1:9" ht="11.4">
-      <c r="A3" s="808"/>
-      <c r="B3" s="798"/>
-      <c r="C3" s="798"/>
-      <c r="D3" s="798"/>
-      <c r="E3" s="798"/>
-      <c r="F3" s="798"/>
+      <c r="A3" s="837"/>
+      <c r="B3" s="797"/>
+      <c r="C3" s="797"/>
+      <c r="D3" s="797"/>
+      <c r="E3" s="797"/>
+      <c r="F3" s="797"/>
       <c r="G3" s="809"/>
       <c r="H3" s="213"/>
     </row>
     <row r="4" spans="1:9" ht="15" customHeight="1">
-      <c r="A4" s="810" t="s">
+      <c r="A4" s="838" t="s">
         <v>282</v>
       </c>
-      <c r="B4" s="811"/>
-      <c r="C4" s="811"/>
-      <c r="D4" s="811"/>
-      <c r="E4" s="811"/>
-      <c r="F4" s="811"/>
-      <c r="G4" s="812"/>
-      <c r="H4" s="811"/>
+      <c r="B4" s="839"/>
+      <c r="C4" s="839"/>
+      <c r="D4" s="839"/>
+      <c r="E4" s="839"/>
+      <c r="F4" s="839"/>
+      <c r="G4" s="840"/>
+      <c r="H4" s="839"/>
     </row>
     <row r="5" spans="1:9" ht="15" customHeight="1">
       <c r="A5" s="98">
@@ -23393,13 +23388,13 @@
       </c>
     </row>
     <row r="6" spans="1:9" ht="24" customHeight="1">
-      <c r="B6" s="813" t="s">
+      <c r="B6" s="863" t="s">
         <v>134</v>
       </c>
-      <c r="C6" s="813"/>
-      <c r="D6" s="813"/>
-      <c r="E6" s="813"/>
-      <c r="F6" s="813"/>
+      <c r="C6" s="863"/>
+      <c r="D6" s="863"/>
+      <c r="E6" s="863"/>
+      <c r="F6" s="863"/>
       <c r="G6" s="218" t="s">
         <v>243</v>
       </c>
@@ -23489,13 +23484,13 @@
       <c r="B15" s="79"/>
     </row>
     <row r="16" spans="1:9" ht="24" customHeight="1">
-      <c r="B16" s="814" t="s">
+      <c r="B16" s="813" t="s">
         <v>134</v>
       </c>
-      <c r="C16" s="815"/>
-      <c r="D16" s="815"/>
-      <c r="E16" s="815"/>
-      <c r="F16" s="816"/>
+      <c r="C16" s="814"/>
+      <c r="D16" s="814"/>
+      <c r="E16" s="814"/>
+      <c r="F16" s="815"/>
       <c r="G16" s="239" t="str">
         <f>+G6</f>
         <v>As at 31 March, 2026</v>
@@ -23592,26 +23587,26 @@
     </row>
     <row r="24" spans="1:8" ht="11.4">
       <c r="A24" s="258"/>
-      <c r="B24" s="817" t="s">
+      <c r="B24" s="849" t="s">
         <v>299</v>
       </c>
-      <c r="C24" s="818"/>
-      <c r="D24" s="819"/>
-      <c r="E24" s="823" t="str">
+      <c r="C24" s="850"/>
+      <c r="D24" s="851"/>
+      <c r="E24" s="855" t="str">
         <f>+G16</f>
         <v>As at 31 March, 2026</v>
       </c>
-      <c r="F24" s="824"/>
-      <c r="G24" s="823" t="str">
+      <c r="F24" s="856"/>
+      <c r="G24" s="855" t="str">
         <f>+H16</f>
         <v>As at 31 March, 2026</v>
       </c>
-      <c r="H24" s="824"/>
+      <c r="H24" s="856"/>
     </row>
     <row r="25" spans="1:8" ht="15.75" customHeight="1">
-      <c r="B25" s="820"/>
-      <c r="C25" s="821"/>
-      <c r="D25" s="822"/>
+      <c r="B25" s="852"/>
+      <c r="C25" s="853"/>
+      <c r="D25" s="854"/>
       <c r="E25" s="260" t="s">
         <v>300</v>
       </c>
@@ -23699,38 +23694,38 @@
       <c r="A32" s="258" t="s">
         <v>302</v>
       </c>
-      <c r="B32" s="825" t="s">
+      <c r="B32" s="857" t="s">
         <v>303</v>
       </c>
-      <c r="C32" s="798"/>
-      <c r="D32" s="798"/>
-      <c r="E32" s="798"/>
+      <c r="C32" s="797"/>
+      <c r="D32" s="797"/>
+      <c r="E32" s="797"/>
       <c r="F32" s="272"/>
       <c r="G32" s="273"/>
       <c r="H32" s="23"/>
     </row>
     <row r="33" spans="1:10" ht="24" customHeight="1">
-      <c r="A33" s="831"/>
-      <c r="B33" s="826" t="s">
+      <c r="A33" s="841"/>
+      <c r="B33" s="858" t="s">
         <v>304</v>
       </c>
-      <c r="C33" s="827"/>
-      <c r="D33" s="829" t="s">
+      <c r="C33" s="859"/>
+      <c r="D33" s="861" t="s">
         <v>305</v>
       </c>
-      <c r="E33" s="830"/>
-      <c r="F33" s="829" t="s">
+      <c r="E33" s="862"/>
+      <c r="F33" s="861" t="s">
         <v>306</v>
       </c>
-      <c r="G33" s="830"/>
-      <c r="H33" s="833" t="s">
+      <c r="G33" s="862"/>
+      <c r="H33" s="843" t="s">
         <v>307</v>
       </c>
     </row>
     <row r="34" spans="1:10" ht="22.95" customHeight="1">
-      <c r="A34" s="832"/>
-      <c r="B34" s="828"/>
-      <c r="C34" s="799"/>
+      <c r="A34" s="842"/>
+      <c r="B34" s="860"/>
+      <c r="C34" s="798"/>
       <c r="D34" s="274" t="s">
         <v>308</v>
       </c>
@@ -23743,7 +23738,7 @@
       <c r="G34" s="276" t="s">
         <v>309</v>
       </c>
-      <c r="H34" s="834"/>
+      <c r="H34" s="844"/>
     </row>
     <row r="35" spans="1:10" ht="13.2" customHeight="1">
       <c r="A35" s="277"/>
@@ -23779,10 +23774,10 @@
       <c r="H37" s="291"/>
     </row>
     <row r="38" spans="1:10" ht="15.75" customHeight="1">
-      <c r="B38" s="835" t="s">
+      <c r="B38" s="845" t="s">
         <v>310</v>
       </c>
-      <c r="C38" s="836"/>
+      <c r="C38" s="846"/>
       <c r="D38" s="292">
         <f>SUM(D35:D37)</f>
         <v>0</v>
@@ -23829,13 +23824,13 @@
     </row>
     <row r="41" spans="1:10" ht="24" customHeight="1">
       <c r="A41" s="172"/>
-      <c r="B41" s="814" t="s">
+      <c r="B41" s="813" t="s">
         <v>134</v>
       </c>
-      <c r="C41" s="815"/>
-      <c r="D41" s="815"/>
-      <c r="E41" s="815"/>
-      <c r="F41" s="816"/>
+      <c r="C41" s="814"/>
+      <c r="D41" s="814"/>
+      <c r="E41" s="814"/>
+      <c r="F41" s="815"/>
       <c r="G41" s="239" t="str">
         <f>+G16</f>
         <v>As at 31 March, 2026</v>
@@ -24021,10 +24016,10 @@
       <c r="H53" s="305"/>
     </row>
     <row r="54" spans="1:10" ht="13.95" customHeight="1">
-      <c r="B54" s="837" t="s">
+      <c r="B54" s="847" t="s">
         <v>310</v>
       </c>
-      <c r="C54" s="838"/>
+      <c r="C54" s="848"/>
       <c r="D54" s="251"/>
       <c r="E54" s="251"/>
       <c r="F54" s="306" t="s">
@@ -24050,40 +24045,40 @@
       <c r="H56" s="312"/>
     </row>
     <row r="57" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A57" s="805" t="str">
+      <c r="A57" s="834" t="str">
         <f>+A2</f>
         <v>KWIKTEAM SUPPORT SERVICES PVT LTD</v>
       </c>
-      <c r="B57" s="806"/>
-      <c r="C57" s="806"/>
-      <c r="D57" s="806"/>
-      <c r="E57" s="806"/>
-      <c r="F57" s="806"/>
-      <c r="G57" s="807"/>
-      <c r="H57" s="806"/>
+      <c r="B57" s="835"/>
+      <c r="C57" s="835"/>
+      <c r="D57" s="835"/>
+      <c r="E57" s="835"/>
+      <c r="F57" s="835"/>
+      <c r="G57" s="836"/>
+      <c r="H57" s="835"/>
     </row>
     <row r="58" spans="1:10" ht="11.4">
-      <c r="A58" s="808"/>
-      <c r="B58" s="798"/>
-      <c r="C58" s="798"/>
-      <c r="D58" s="798"/>
-      <c r="E58" s="798"/>
-      <c r="F58" s="798"/>
+      <c r="A58" s="837"/>
+      <c r="B58" s="797"/>
+      <c r="C58" s="797"/>
+      <c r="D58" s="797"/>
+      <c r="E58" s="797"/>
+      <c r="F58" s="797"/>
       <c r="G58" s="809"/>
       <c r="H58" s="213"/>
     </row>
     <row r="59" spans="1:10" ht="12.75" customHeight="1">
-      <c r="A59" s="810" t="str">
+      <c r="A59" s="838" t="str">
         <f>+A4</f>
         <v>Schedules to Balance Sheet as at 31 March, 2026</v>
       </c>
-      <c r="B59" s="811"/>
-      <c r="C59" s="811"/>
-      <c r="D59" s="811"/>
-      <c r="E59" s="811"/>
-      <c r="F59" s="811"/>
-      <c r="G59" s="812"/>
-      <c r="H59" s="811"/>
+      <c r="B59" s="839"/>
+      <c r="C59" s="839"/>
+      <c r="D59" s="839"/>
+      <c r="E59" s="839"/>
+      <c r="F59" s="839"/>
+      <c r="G59" s="840"/>
+      <c r="H59" s="839"/>
     </row>
     <row r="60" spans="1:10" ht="11.4">
       <c r="A60" s="98" t="str">
@@ -24095,13 +24090,13 @@
       </c>
     </row>
     <row r="61" spans="1:10" ht="24" customHeight="1">
-      <c r="B61" s="814" t="s">
+      <c r="B61" s="813" t="s">
         <v>134</v>
       </c>
-      <c r="C61" s="815"/>
-      <c r="D61" s="815"/>
-      <c r="E61" s="815"/>
-      <c r="F61" s="816"/>
+      <c r="C61" s="814"/>
+      <c r="D61" s="814"/>
+      <c r="E61" s="814"/>
+      <c r="F61" s="815"/>
       <c r="G61" s="239" t="str">
         <f>+G41</f>
         <v>As at 31 March, 2026</v>
@@ -24211,10 +24206,10 @@
       <c r="H69" s="266"/>
     </row>
     <row r="70" spans="1:8" ht="13.95" customHeight="1">
-      <c r="B70" s="839" t="s">
+      <c r="B70" s="806" t="s">
         <v>310</v>
       </c>
-      <c r="C70" s="840"/>
+      <c r="C70" s="807"/>
       <c r="D70" s="321"/>
       <c r="E70" s="321"/>
       <c r="F70" s="322"/>
@@ -24246,13 +24241,13 @@
       </c>
     </row>
     <row r="73" spans="1:8" ht="24" customHeight="1">
-      <c r="B73" s="814" t="s">
+      <c r="B73" s="813" t="s">
         <v>134</v>
       </c>
-      <c r="C73" s="815"/>
-      <c r="D73" s="815"/>
-      <c r="E73" s="815"/>
-      <c r="F73" s="816"/>
+      <c r="C73" s="814"/>
+      <c r="D73" s="814"/>
+      <c r="E73" s="814"/>
+      <c r="F73" s="815"/>
       <c r="G73" s="218" t="str">
         <f>+G61</f>
         <v>As at 31 March, 2026</v>
@@ -24287,12 +24282,12 @@
       </c>
     </row>
     <row r="76" spans="1:8" ht="11.4">
-      <c r="B76" s="841" t="s">
+      <c r="B76" s="805" t="s">
         <v>329</v>
       </c>
-      <c r="C76" s="798"/>
-      <c r="D76" s="798"/>
-      <c r="E76" s="798"/>
+      <c r="C76" s="797"/>
+      <c r="D76" s="797"/>
+      <c r="E76" s="797"/>
       <c r="F76" s="121"/>
       <c r="G76" s="248">
         <v>0</v>
@@ -24302,12 +24297,12 @@
       </c>
     </row>
     <row r="77" spans="1:8" ht="11.4">
-      <c r="B77" s="841" t="s">
+      <c r="B77" s="805" t="s">
         <v>330</v>
       </c>
-      <c r="C77" s="798"/>
-      <c r="D77" s="798"/>
-      <c r="E77" s="798"/>
+      <c r="C77" s="797"/>
+      <c r="D77" s="797"/>
+      <c r="E77" s="797"/>
       <c r="F77" s="121"/>
       <c r="G77" s="248">
         <v>0</v>
@@ -24326,10 +24321,10 @@
       <c r="H78" s="305"/>
     </row>
     <row r="79" spans="1:8" ht="13.95" customHeight="1">
-      <c r="B79" s="839" t="s">
+      <c r="B79" s="806" t="s">
         <v>310</v>
       </c>
-      <c r="C79" s="840"/>
+      <c r="C79" s="807"/>
       <c r="D79" s="321"/>
       <c r="E79" s="321"/>
       <c r="F79" s="322"/>
@@ -24361,13 +24356,13 @@
       </c>
     </row>
     <row r="82" spans="1:8" ht="24" customHeight="1">
-      <c r="B82" s="814" t="s">
+      <c r="B82" s="813" t="s">
         <v>134</v>
       </c>
-      <c r="C82" s="815"/>
-      <c r="D82" s="815"/>
-      <c r="E82" s="815"/>
-      <c r="F82" s="816"/>
+      <c r="C82" s="814"/>
+      <c r="D82" s="814"/>
+      <c r="E82" s="814"/>
+      <c r="F82" s="815"/>
       <c r="G82" s="218" t="str">
         <f>+G73</f>
         <v>As at 31 March, 2026</v>
@@ -24402,12 +24397,12 @@
       </c>
     </row>
     <row r="85" spans="1:8" ht="11.4">
-      <c r="B85" s="841" t="s">
+      <c r="B85" s="805" t="s">
         <v>333</v>
       </c>
-      <c r="C85" s="798"/>
-      <c r="D85" s="798"/>
-      <c r="E85" s="798"/>
+      <c r="C85" s="797"/>
+      <c r="D85" s="797"/>
+      <c r="E85" s="797"/>
       <c r="F85" s="121"/>
       <c r="G85" s="248">
         <v>0</v>
@@ -24426,10 +24421,10 @@
       <c r="H86" s="305"/>
     </row>
     <row r="87" spans="1:8" ht="13.95" customHeight="1">
-      <c r="B87" s="839" t="s">
+      <c r="B87" s="806" t="s">
         <v>310</v>
       </c>
-      <c r="C87" s="840"/>
+      <c r="C87" s="807"/>
       <c r="D87" s="321"/>
       <c r="E87" s="321"/>
       <c r="F87" s="322"/>
@@ -24461,13 +24456,13 @@
       </c>
     </row>
     <row r="90" spans="1:8" ht="24" customHeight="1">
-      <c r="B90" s="814" t="s">
+      <c r="B90" s="813" t="s">
         <v>134</v>
       </c>
-      <c r="C90" s="815"/>
-      <c r="D90" s="815"/>
-      <c r="E90" s="815"/>
-      <c r="F90" s="816"/>
+      <c r="C90" s="814"/>
+      <c r="D90" s="814"/>
+      <c r="E90" s="814"/>
+      <c r="F90" s="815"/>
       <c r="G90" s="218" t="str">
         <f>+G82</f>
         <v>As at 31 March, 2026</v>
@@ -24585,10 +24580,10 @@
       <c r="H99" s="305"/>
     </row>
     <row r="100" spans="1:8" ht="13.95" customHeight="1">
-      <c r="B100" s="839" t="s">
+      <c r="B100" s="806" t="s">
         <v>310</v>
       </c>
-      <c r="C100" s="840"/>
+      <c r="C100" s="807"/>
       <c r="D100" s="333"/>
       <c r="E100" s="333"/>
       <c r="F100" s="322"/>
@@ -24620,13 +24615,13 @@
       </c>
     </row>
     <row r="103" spans="1:8" ht="24" customHeight="1">
-      <c r="B103" s="814" t="s">
+      <c r="B103" s="813" t="s">
         <v>134</v>
       </c>
-      <c r="C103" s="815"/>
-      <c r="D103" s="815"/>
-      <c r="E103" s="815"/>
-      <c r="F103" s="816"/>
+      <c r="C103" s="814"/>
+      <c r="D103" s="814"/>
+      <c r="E103" s="814"/>
+      <c r="F103" s="815"/>
       <c r="G103" s="218" t="str">
         <f>+G90</f>
         <v>As at 31 March, 2026</v>
@@ -24661,12 +24656,12 @@
       </c>
     </row>
     <row r="106" spans="1:8" ht="11.4">
-      <c r="B106" s="841" t="s">
+      <c r="B106" s="805" t="s">
         <v>344</v>
       </c>
-      <c r="C106" s="798"/>
-      <c r="D106" s="798"/>
-      <c r="E106" s="798"/>
+      <c r="C106" s="797"/>
+      <c r="D106" s="797"/>
+      <c r="E106" s="797"/>
       <c r="F106" s="121"/>
       <c r="G106" s="248">
         <v>0</v>
@@ -24685,10 +24680,10 @@
       <c r="H107" s="305"/>
     </row>
     <row r="108" spans="1:8" ht="13.95" customHeight="1">
-      <c r="B108" s="839" t="s">
+      <c r="B108" s="806" t="s">
         <v>310</v>
       </c>
-      <c r="C108" s="840"/>
+      <c r="C108" s="807"/>
       <c r="D108" s="333"/>
       <c r="E108" s="333"/>
       <c r="F108" s="322"/>
@@ -24720,40 +24715,40 @@
       <c r="H110" s="325"/>
     </row>
     <row r="111" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A111" s="805" t="str">
+      <c r="A111" s="834" t="str">
         <f>+A57</f>
         <v>KWIKTEAM SUPPORT SERVICES PVT LTD</v>
       </c>
-      <c r="B111" s="806"/>
-      <c r="C111" s="806"/>
-      <c r="D111" s="806"/>
-      <c r="E111" s="806"/>
-      <c r="F111" s="806"/>
-      <c r="G111" s="807"/>
-      <c r="H111" s="806"/>
+      <c r="B111" s="835"/>
+      <c r="C111" s="835"/>
+      <c r="D111" s="835"/>
+      <c r="E111" s="835"/>
+      <c r="F111" s="835"/>
+      <c r="G111" s="836"/>
+      <c r="H111" s="835"/>
     </row>
     <row r="112" spans="1:8" ht="11.4">
-      <c r="A112" s="808"/>
-      <c r="B112" s="798"/>
-      <c r="C112" s="798"/>
-      <c r="D112" s="798"/>
-      <c r="E112" s="798"/>
-      <c r="F112" s="798"/>
+      <c r="A112" s="837"/>
+      <c r="B112" s="797"/>
+      <c r="C112" s="797"/>
+      <c r="D112" s="797"/>
+      <c r="E112" s="797"/>
+      <c r="F112" s="797"/>
       <c r="G112" s="809"/>
       <c r="H112" s="213"/>
     </row>
     <row r="113" spans="1:18" ht="12.75" customHeight="1">
-      <c r="A113" s="810" t="str">
+      <c r="A113" s="838" t="str">
         <f>+A59</f>
         <v>Schedules to Balance Sheet as at 31 March, 2026</v>
       </c>
-      <c r="B113" s="811"/>
-      <c r="C113" s="811"/>
-      <c r="D113" s="811"/>
-      <c r="E113" s="811"/>
-      <c r="F113" s="811"/>
-      <c r="G113" s="812"/>
-      <c r="H113" s="811"/>
+      <c r="B113" s="839"/>
+      <c r="C113" s="839"/>
+      <c r="D113" s="839"/>
+      <c r="E113" s="839"/>
+      <c r="F113" s="839"/>
+      <c r="G113" s="840"/>
+      <c r="H113" s="839"/>
     </row>
     <row r="114" spans="1:18" ht="6.9" customHeight="1">
       <c r="A114" s="214"/>
@@ -24777,22 +24772,22 @@
       <c r="H115" s="338"/>
     </row>
     <row r="116" spans="1:18" ht="21.75" customHeight="1">
-      <c r="B116" s="842" t="s">
+      <c r="B116" s="825" t="s">
         <v>134</v>
       </c>
-      <c r="C116" s="843"/>
-      <c r="D116" s="845" t="s">
+      <c r="C116" s="829"/>
+      <c r="D116" s="827" t="s">
         <v>346</v>
       </c>
-      <c r="E116" s="846"/>
-      <c r="F116" s="846"/>
-      <c r="G116" s="846"/>
-      <c r="H116" s="847" t="s">
+      <c r="E116" s="831"/>
+      <c r="F116" s="831"/>
+      <c r="G116" s="831"/>
+      <c r="H116" s="832" t="s">
         <v>310</v>
       </c>
     </row>
     <row r="117" spans="1:18" ht="28.5" customHeight="1">
-      <c r="B117" s="844"/>
+      <c r="B117" s="830"/>
       <c r="C117" s="778"/>
       <c r="D117" s="339" t="s">
         <v>347</v>
@@ -24806,16 +24801,16 @@
       <c r="G117" s="339" t="s">
         <v>350</v>
       </c>
-      <c r="H117" s="848"/>
+      <c r="H117" s="833"/>
       <c r="J117" s="340" t="s">
         <v>351</v>
       </c>
     </row>
     <row r="118" spans="1:18" ht="15" customHeight="1">
-      <c r="B118" s="849" t="s">
+      <c r="B118" s="818" t="s">
         <v>352</v>
       </c>
-      <c r="C118" s="843"/>
+      <c r="C118" s="829"/>
       <c r="D118" s="341">
         <f>G105</f>
         <v>0</v>
@@ -24841,10 +24836,10 @@
       </c>
     </row>
     <row r="119" spans="1:18" ht="15" customHeight="1">
-      <c r="B119" s="850" t="s">
+      <c r="B119" s="820" t="s">
         <v>355</v>
       </c>
-      <c r="C119" s="851"/>
+      <c r="C119" s="823"/>
       <c r="D119" s="341">
         <f>G106</f>
         <v>0</v>
@@ -24876,10 +24871,10 @@
       </c>
     </row>
     <row r="120" spans="1:18" ht="15" customHeight="1">
-      <c r="B120" s="850" t="s">
+      <c r="B120" s="820" t="s">
         <v>358</v>
       </c>
-      <c r="C120" s="851"/>
+      <c r="C120" s="823"/>
       <c r="D120" s="341">
         <v>0</v>
       </c>
@@ -24907,10 +24902,10 @@
       </c>
     </row>
     <row r="121" spans="1:18" ht="15" customHeight="1">
-      <c r="B121" s="852" t="s">
+      <c r="B121" s="822" t="s">
         <v>360</v>
       </c>
-      <c r="C121" s="851"/>
+      <c r="C121" s="823"/>
       <c r="D121" s="341">
         <v>0</v>
       </c>
@@ -24938,8 +24933,8 @@
       </c>
     </row>
     <row r="122" spans="1:18" ht="15.75" customHeight="1">
-      <c r="B122" s="853"/>
-      <c r="C122" s="854"/>
+      <c r="B122" s="810"/>
+      <c r="C122" s="824"/>
       <c r="D122" s="344"/>
       <c r="E122" s="344"/>
       <c r="F122" s="344"/>
@@ -24987,17 +24982,17 @@
       </c>
     </row>
     <row r="125" spans="1:18" ht="21.75" customHeight="1">
-      <c r="B125" s="842" t="s">
+      <c r="B125" s="825" t="s">
         <v>134</v>
       </c>
-      <c r="C125" s="855"/>
-      <c r="D125" s="845" t="s">
+      <c r="C125" s="819"/>
+      <c r="D125" s="827" t="s">
         <v>346</v>
       </c>
-      <c r="E125" s="857"/>
-      <c r="F125" s="857"/>
-      <c r="G125" s="857"/>
-      <c r="H125" s="858" t="s">
+      <c r="E125" s="828"/>
+      <c r="F125" s="828"/>
+      <c r="G125" s="828"/>
+      <c r="H125" s="816" t="s">
         <v>310</v>
       </c>
       <c r="L125" s="92" t="s">
@@ -25011,8 +25006,8 @@
       </c>
     </row>
     <row r="126" spans="1:18" ht="28.5" customHeight="1">
-      <c r="B126" s="856"/>
-      <c r="C126" s="786"/>
+      <c r="B126" s="826"/>
+      <c r="C126" s="790"/>
       <c r="D126" s="348" t="s">
         <v>347</v>
       </c>
@@ -25025,7 +25020,7 @@
       <c r="G126" s="348" t="s">
         <v>350</v>
       </c>
-      <c r="H126" s="859"/>
+      <c r="H126" s="817"/>
       <c r="L126" s="92" t="s">
         <v>361</v>
       </c>
@@ -25037,10 +25032,10 @@
       </c>
     </row>
     <row r="127" spans="1:18" ht="15" customHeight="1">
-      <c r="B127" s="849" t="s">
+      <c r="B127" s="818" t="s">
         <v>352</v>
       </c>
-      <c r="C127" s="855"/>
+      <c r="C127" s="819"/>
       <c r="D127" s="341">
         <f>+H105</f>
         <v>0</v>
@@ -25069,10 +25064,10 @@
       </c>
     </row>
     <row r="128" spans="1:18" ht="15" customHeight="1">
-      <c r="B128" s="850" t="s">
+      <c r="B128" s="820" t="s">
         <v>355</v>
       </c>
-      <c r="C128" s="860"/>
+      <c r="C128" s="821"/>
       <c r="D128" s="341">
         <f>+H106</f>
         <v>0</v>
@@ -25092,10 +25087,10 @@
       </c>
     </row>
     <row r="129" spans="1:18" ht="15" customHeight="1">
-      <c r="B129" s="850" t="s">
+      <c r="B129" s="820" t="s">
         <v>358</v>
       </c>
-      <c r="C129" s="860"/>
+      <c r="C129" s="821"/>
       <c r="D129" s="341">
         <v>0</v>
       </c>
@@ -25123,10 +25118,10 @@
       </c>
     </row>
     <row r="130" spans="1:18" ht="15" customHeight="1">
-      <c r="B130" s="852" t="s">
+      <c r="B130" s="822" t="s">
         <v>360</v>
       </c>
-      <c r="C130" s="860"/>
+      <c r="C130" s="821"/>
       <c r="D130" s="341">
         <v>0</v>
       </c>
@@ -25154,8 +25149,8 @@
       </c>
     </row>
     <row r="131" spans="1:18" ht="15.75" customHeight="1">
-      <c r="B131" s="853"/>
-      <c r="C131" s="861"/>
+      <c r="B131" s="810"/>
+      <c r="C131" s="811"/>
       <c r="D131" s="344"/>
       <c r="E131" s="344"/>
       <c r="F131" s="344"/>
@@ -25194,15 +25189,15 @@
       <c r="H134" s="354"/>
     </row>
     <row r="135" spans="1:18" ht="26.4" customHeight="1">
-      <c r="B135" s="862" t="s">
+      <c r="B135" s="812" t="s">
         <v>369</v>
       </c>
-      <c r="C135" s="862"/>
-      <c r="D135" s="862"/>
-      <c r="E135" s="862"/>
-      <c r="F135" s="862"/>
-      <c r="G135" s="862"/>
-      <c r="H135" s="862"/>
+      <c r="C135" s="812"/>
+      <c r="D135" s="812"/>
+      <c r="E135" s="812"/>
+      <c r="F135" s="812"/>
+      <c r="G135" s="812"/>
+      <c r="H135" s="812"/>
     </row>
     <row r="136" spans="1:18" ht="11.4">
       <c r="B136" s="205"/>
@@ -25223,13 +25218,13 @@
       </c>
     </row>
     <row r="138" spans="1:18" ht="24" customHeight="1">
-      <c r="B138" s="814" t="s">
+      <c r="B138" s="813" t="s">
         <v>134</v>
       </c>
-      <c r="C138" s="815"/>
-      <c r="D138" s="815"/>
-      <c r="E138" s="815"/>
-      <c r="F138" s="816"/>
+      <c r="C138" s="814"/>
+      <c r="D138" s="814"/>
+      <c r="E138" s="814"/>
+      <c r="F138" s="815"/>
       <c r="G138" s="218" t="str">
         <f>+G103</f>
         <v>As at 31 March, 2026</v>
@@ -25354,10 +25349,10 @@
       <c r="H146" s="248"/>
     </row>
     <row r="147" spans="1:8" ht="13.95" customHeight="1">
-      <c r="B147" s="839" t="s">
+      <c r="B147" s="806" t="s">
         <v>310</v>
       </c>
-      <c r="C147" s="840"/>
+      <c r="C147" s="807"/>
       <c r="D147" s="333"/>
       <c r="E147" s="333"/>
       <c r="F147" s="322"/>
@@ -25389,13 +25384,13 @@
       </c>
     </row>
     <row r="150" spans="1:8" ht="24" customHeight="1">
-      <c r="B150" s="814" t="s">
+      <c r="B150" s="813" t="s">
         <v>134</v>
       </c>
-      <c r="C150" s="815"/>
-      <c r="D150" s="815"/>
-      <c r="E150" s="815"/>
-      <c r="F150" s="816"/>
+      <c r="C150" s="814"/>
+      <c r="D150" s="814"/>
+      <c r="E150" s="814"/>
+      <c r="F150" s="815"/>
       <c r="G150" s="218" t="str">
         <f>+G138</f>
         <v>As at 31 March, 2026</v>
@@ -25430,12 +25425,12 @@
       </c>
     </row>
     <row r="153" spans="1:8" ht="11.4">
-      <c r="B153" s="841" t="s">
+      <c r="B153" s="805" t="s">
         <v>377</v>
       </c>
-      <c r="C153" s="798"/>
-      <c r="D153" s="798"/>
-      <c r="E153" s="798"/>
+      <c r="C153" s="797"/>
+      <c r="D153" s="797"/>
+      <c r="E153" s="797"/>
       <c r="F153" s="121"/>
       <c r="G153" s="248">
         <v>0</v>
@@ -25484,10 +25479,10 @@
       <c r="H158" s="305"/>
     </row>
     <row r="159" spans="1:8" ht="13.95" customHeight="1">
-      <c r="B159" s="839" t="s">
+      <c r="B159" s="806" t="s">
         <v>310</v>
       </c>
-      <c r="C159" s="840"/>
+      <c r="C159" s="807"/>
       <c r="D159" s="333"/>
       <c r="E159" s="333"/>
       <c r="F159" s="322"/>
@@ -25510,19 +25505,71 @@
       <c r="H160" s="325"/>
     </row>
     <row r="163" spans="1:8" ht="11.4">
-      <c r="A163" s="863" t="s">
+      <c r="A163" s="808" t="s">
         <v>379</v>
       </c>
-      <c r="B163" s="798"/>
-      <c r="C163" s="798"/>
-      <c r="D163" s="798"/>
-      <c r="E163" s="798"/>
-      <c r="F163" s="798"/>
+      <c r="B163" s="797"/>
+      <c r="C163" s="797"/>
+      <c r="D163" s="797"/>
+      <c r="E163" s="797"/>
+      <c r="F163" s="797"/>
       <c r="G163" s="809"/>
-      <c r="H163" s="798"/>
+      <c r="H163" s="797"/>
     </row>
   </sheetData>
   <mergeCells count="60">
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="B16:F16"/>
+    <mergeCell ref="B24:D25"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="G24:H24"/>
+    <mergeCell ref="B32:E32"/>
+    <mergeCell ref="B33:C34"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="F33:G33"/>
+    <mergeCell ref="A33:A34"/>
+    <mergeCell ref="H33:H34"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B41:F41"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="A57:H57"/>
+    <mergeCell ref="A58:G58"/>
+    <mergeCell ref="A59:H59"/>
+    <mergeCell ref="B61:F61"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B76:E76"/>
+    <mergeCell ref="B77:E77"/>
+    <mergeCell ref="B79:C79"/>
+    <mergeCell ref="B82:F82"/>
+    <mergeCell ref="B85:E85"/>
+    <mergeCell ref="B87:C87"/>
+    <mergeCell ref="B90:F90"/>
+    <mergeCell ref="B100:C100"/>
+    <mergeCell ref="B103:F103"/>
+    <mergeCell ref="B106:E106"/>
+    <mergeCell ref="B108:C108"/>
+    <mergeCell ref="A111:H111"/>
+    <mergeCell ref="A112:G112"/>
+    <mergeCell ref="A113:H113"/>
+    <mergeCell ref="B116:C117"/>
+    <mergeCell ref="D116:G116"/>
+    <mergeCell ref="H116:H117"/>
+    <mergeCell ref="B118:C118"/>
+    <mergeCell ref="B119:C119"/>
+    <mergeCell ref="B120:C120"/>
+    <mergeCell ref="B121:C121"/>
+    <mergeCell ref="B122:C122"/>
+    <mergeCell ref="B125:C126"/>
+    <mergeCell ref="D125:G125"/>
+    <mergeCell ref="H125:H126"/>
+    <mergeCell ref="B127:C127"/>
+    <mergeCell ref="B128:C128"/>
+    <mergeCell ref="B129:C129"/>
+    <mergeCell ref="B130:C130"/>
     <mergeCell ref="B153:E153"/>
     <mergeCell ref="B159:C159"/>
     <mergeCell ref="A163:H163"/>
@@ -25531,58 +25578,6 @@
     <mergeCell ref="B138:F138"/>
     <mergeCell ref="B147:C147"/>
     <mergeCell ref="B150:F150"/>
-    <mergeCell ref="H125:H126"/>
-    <mergeCell ref="B127:C127"/>
-    <mergeCell ref="B128:C128"/>
-    <mergeCell ref="B129:C129"/>
-    <mergeCell ref="B130:C130"/>
-    <mergeCell ref="B120:C120"/>
-    <mergeCell ref="B121:C121"/>
-    <mergeCell ref="B122:C122"/>
-    <mergeCell ref="B125:C126"/>
-    <mergeCell ref="D125:G125"/>
-    <mergeCell ref="B116:C117"/>
-    <mergeCell ref="D116:G116"/>
-    <mergeCell ref="H116:H117"/>
-    <mergeCell ref="B118:C118"/>
-    <mergeCell ref="B119:C119"/>
-    <mergeCell ref="B106:E106"/>
-    <mergeCell ref="B108:C108"/>
-    <mergeCell ref="A111:H111"/>
-    <mergeCell ref="A112:G112"/>
-    <mergeCell ref="A113:H113"/>
-    <mergeCell ref="B85:E85"/>
-    <mergeCell ref="B87:C87"/>
-    <mergeCell ref="B90:F90"/>
-    <mergeCell ref="B100:C100"/>
-    <mergeCell ref="B103:F103"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B76:E76"/>
-    <mergeCell ref="B77:E77"/>
-    <mergeCell ref="B79:C79"/>
-    <mergeCell ref="B82:F82"/>
-    <mergeCell ref="A57:H57"/>
-    <mergeCell ref="A58:G58"/>
-    <mergeCell ref="A59:H59"/>
-    <mergeCell ref="B61:F61"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="A33:A34"/>
-    <mergeCell ref="H33:H34"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B41:F41"/>
-    <mergeCell ref="B54:C54"/>
-    <mergeCell ref="B24:D25"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="G24:H24"/>
-    <mergeCell ref="B32:E32"/>
-    <mergeCell ref="B33:C34"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="F33:G33"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A4:H4"/>
-    <mergeCell ref="B6:F6"/>
-    <mergeCell ref="B16:F16"/>
   </mergeCells>
   <conditionalFormatting sqref="B35:C36">
     <cfRule type="cellIs" dxfId="34" priority="10" operator="lessThan">
@@ -25754,33 +25749,33 @@
       <c r="N5" s="363"/>
     </row>
     <row r="6" spans="1:15" ht="19.5" customHeight="1">
-      <c r="B6" s="868" t="s">
+      <c r="B6" s="873" t="s">
         <v>134</v>
       </c>
-      <c r="C6" s="870" t="s">
+      <c r="C6" s="875" t="s">
         <v>382</v>
       </c>
-      <c r="D6" s="864" t="s">
+      <c r="D6" s="869" t="s">
         <v>383</v>
       </c>
-      <c r="E6" s="865"/>
-      <c r="F6" s="865"/>
-      <c r="G6" s="866"/>
-      <c r="H6" s="867" t="s">
+      <c r="E6" s="870"/>
+      <c r="F6" s="870"/>
+      <c r="G6" s="871"/>
+      <c r="H6" s="872" t="s">
         <v>384</v>
       </c>
-      <c r="I6" s="865"/>
-      <c r="J6" s="865"/>
-      <c r="K6" s="866"/>
-      <c r="L6" s="864" t="s">
+      <c r="I6" s="870"/>
+      <c r="J6" s="870"/>
+      <c r="K6" s="871"/>
+      <c r="L6" s="869" t="s">
         <v>385</v>
       </c>
-      <c r="M6" s="866"/>
+      <c r="M6" s="871"/>
       <c r="N6" s="370"/>
     </row>
     <row r="7" spans="1:15" s="53" customFormat="1" ht="39.75" customHeight="1">
-      <c r="B7" s="869"/>
-      <c r="C7" s="871"/>
+      <c r="B7" s="874"/>
+      <c r="C7" s="876"/>
       <c r="D7" s="371" t="s">
         <v>386</v>
       </c>
@@ -26264,10 +26259,10 @@
       <c r="N21" s="389"/>
     </row>
     <row r="22" spans="2:16" ht="12.75" customHeight="1">
-      <c r="B22" s="872" t="s">
+      <c r="B22" s="864" t="s">
         <v>400</v>
       </c>
-      <c r="C22" s="873"/>
+      <c r="C22" s="865"/>
       <c r="D22" s="391">
         <f>SUM(D10:D21)</f>
         <v>0</v>
@@ -26312,10 +26307,10 @@
       <c r="P22" s="24"/>
     </row>
     <row r="23" spans="2:16" ht="12.75" customHeight="1">
-      <c r="B23" s="872" t="s">
+      <c r="B23" s="864" t="s">
         <v>401</v>
       </c>
-      <c r="C23" s="873"/>
+      <c r="C23" s="865"/>
       <c r="D23" s="393">
         <v>0</v>
       </c>
@@ -26382,19 +26377,19 @@
       <c r="M25" s="397"/>
     </row>
     <row r="26" spans="2:16" ht="13.2" customHeight="1">
-      <c r="B26" s="874" t="s">
+      <c r="B26" s="866" t="s">
         <v>403</v>
       </c>
-      <c r="C26" s="874"/>
-      <c r="D26" s="875"/>
-      <c r="E26" s="876"/>
-      <c r="F26" s="875"/>
-      <c r="G26" s="875"/>
-      <c r="H26" s="875"/>
-      <c r="I26" s="875"/>
-      <c r="J26" s="875"/>
-      <c r="K26" s="875"/>
-      <c r="L26" s="875"/>
+      <c r="C26" s="866"/>
+      <c r="D26" s="867"/>
+      <c r="E26" s="868"/>
+      <c r="F26" s="867"/>
+      <c r="G26" s="867"/>
+      <c r="H26" s="867"/>
+      <c r="I26" s="867"/>
+      <c r="J26" s="867"/>
+      <c r="K26" s="867"/>
+      <c r="L26" s="867"/>
       <c r="M26" s="397"/>
     </row>
     <row r="205" spans="2:2" ht="11.4" hidden="1">
@@ -26444,17 +26439,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A1" s="877" t="str">
+      <c r="A1" s="878" t="str">
         <f>BS!B2</f>
         <v>KWIKTEAM SUPPORT SERVICES PVT LTD</v>
       </c>
-      <c r="B1" s="877"/>
-      <c r="C1" s="877"/>
-      <c r="D1" s="877"/>
-      <c r="E1" s="877"/>
-      <c r="F1" s="877"/>
-      <c r="G1" s="877"/>
-      <c r="H1" s="877"/>
+      <c r="B1" s="878"/>
+      <c r="C1" s="878"/>
+      <c r="D1" s="878"/>
+      <c r="E1" s="878"/>
+      <c r="F1" s="878"/>
+      <c r="G1" s="878"/>
+      <c r="H1" s="878"/>
     </row>
     <row r="2" spans="1:12" ht="15.75" customHeight="1">
       <c r="A2" s="399"/>
@@ -26467,16 +26462,16 @@
       <c r="H2" s="400"/>
     </row>
     <row r="3" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A3" s="878" t="s">
+      <c r="A3" s="879" t="s">
         <v>282</v>
       </c>
-      <c r="B3" s="878"/>
-      <c r="C3" s="878"/>
-      <c r="D3" s="878"/>
-      <c r="E3" s="878"/>
-      <c r="F3" s="878"/>
-      <c r="G3" s="878"/>
-      <c r="H3" s="878"/>
+      <c r="B3" s="879"/>
+      <c r="C3" s="879"/>
+      <c r="D3" s="879"/>
+      <c r="E3" s="879"/>
+      <c r="F3" s="879"/>
+      <c r="G3" s="879"/>
+      <c r="H3" s="879"/>
     </row>
     <row r="4" spans="1:12" ht="5.0999999999999996" customHeight="1">
       <c r="A4" s="201"/>
@@ -26591,10 +26586,10 @@
     </row>
     <row r="12" spans="1:12" s="23" customFormat="1" ht="13.95" customHeight="1">
       <c r="A12" s="183"/>
-      <c r="B12" s="879" t="s">
+      <c r="B12" s="888" t="s">
         <v>310</v>
       </c>
-      <c r="C12" s="880"/>
+      <c r="C12" s="885"/>
       <c r="D12" s="413"/>
       <c r="E12" s="413"/>
       <c r="F12" s="322"/>
@@ -26636,13 +26631,13 @@
     </row>
     <row r="15" spans="1:12" ht="24" customHeight="1">
       <c r="A15" s="211"/>
-      <c r="B15" s="813" t="s">
+      <c r="B15" s="863" t="s">
         <v>134</v>
       </c>
-      <c r="C15" s="813"/>
-      <c r="D15" s="813"/>
-      <c r="E15" s="813"/>
-      <c r="F15" s="813"/>
+      <c r="C15" s="863"/>
+      <c r="D15" s="863"/>
+      <c r="E15" s="863"/>
+      <c r="F15" s="863"/>
       <c r="G15" s="218" t="str">
         <f>+'Note BS-Liab'!G6</f>
         <v>As at 31 March, 2026</v>
@@ -26663,23 +26658,23 @@
     </row>
     <row r="16" spans="1:12" ht="11.4">
       <c r="A16" s="120"/>
-      <c r="B16" s="881"/>
-      <c r="C16" s="798"/>
-      <c r="D16" s="798"/>
-      <c r="E16" s="798"/>
+      <c r="B16" s="889"/>
+      <c r="C16" s="797"/>
+      <c r="D16" s="797"/>
+      <c r="E16" s="797"/>
       <c r="F16" s="121"/>
       <c r="G16" s="299"/>
       <c r="H16" s="248"/>
     </row>
     <row r="17" spans="1:9" ht="29.1" customHeight="1">
       <c r="A17" s="120"/>
-      <c r="B17" s="882" t="s">
+      <c r="B17" s="887" t="s">
         <v>415</v>
       </c>
-      <c r="C17" s="795"/>
-      <c r="D17" s="795"/>
-      <c r="E17" s="795"/>
-      <c r="F17" s="796"/>
+      <c r="C17" s="794"/>
+      <c r="D17" s="794"/>
+      <c r="E17" s="794"/>
+      <c r="F17" s="795"/>
       <c r="G17" s="420">
         <v>0</v>
       </c>
@@ -26699,10 +26694,10 @@
     </row>
     <row r="19" spans="1:9" ht="13.95" customHeight="1">
       <c r="A19" s="319"/>
-      <c r="B19" s="839" t="s">
+      <c r="B19" s="806" t="s">
         <v>310</v>
       </c>
-      <c r="C19" s="840"/>
+      <c r="C19" s="807"/>
       <c r="D19" s="321"/>
       <c r="E19" s="321"/>
       <c r="F19" s="322"/>
@@ -26736,13 +26731,13 @@
       </c>
     </row>
     <row r="22" spans="1:9" ht="24" customHeight="1">
-      <c r="B22" s="813" t="s">
+      <c r="B22" s="863" t="s">
         <v>134</v>
       </c>
-      <c r="C22" s="813"/>
-      <c r="D22" s="813"/>
-      <c r="E22" s="813"/>
-      <c r="F22" s="813"/>
+      <c r="C22" s="863"/>
+      <c r="D22" s="863"/>
+      <c r="E22" s="863"/>
+      <c r="F22" s="863"/>
       <c r="G22" s="218" t="str">
         <f>+G15</f>
         <v>As at 31 March, 2026</v>
@@ -26768,12 +26763,12 @@
       </c>
     </row>
     <row r="24" spans="1:9" ht="11.4">
-      <c r="B24" s="841" t="s">
+      <c r="B24" s="805" t="s">
         <v>418</v>
       </c>
-      <c r="C24" s="798"/>
-      <c r="D24" s="798"/>
-      <c r="E24" s="798"/>
+      <c r="C24" s="797"/>
+      <c r="D24" s="797"/>
+      <c r="E24" s="797"/>
       <c r="F24" s="121"/>
       <c r="G24" s="248">
         <v>0</v>
@@ -26783,12 +26778,12 @@
       </c>
     </row>
     <row r="25" spans="1:9" ht="11.4">
-      <c r="B25" s="841" t="s">
+      <c r="B25" s="805" t="s">
         <v>419</v>
       </c>
-      <c r="C25" s="798"/>
-      <c r="D25" s="798"/>
-      <c r="E25" s="798"/>
+      <c r="C25" s="797"/>
+      <c r="D25" s="797"/>
+      <c r="E25" s="797"/>
       <c r="F25" s="121"/>
       <c r="G25" s="248">
         <v>0</v>
@@ -26807,10 +26802,10 @@
       <c r="H26" s="305"/>
     </row>
     <row r="27" spans="1:9" ht="13.95" customHeight="1">
-      <c r="B27" s="839" t="s">
+      <c r="B27" s="806" t="s">
         <v>310</v>
       </c>
-      <c r="C27" s="840"/>
+      <c r="C27" s="807"/>
       <c r="D27" s="321"/>
       <c r="E27" s="321"/>
       <c r="F27" s="322"/>
@@ -26850,13 +26845,13 @@
     </row>
     <row r="31" spans="1:9" ht="22.95" customHeight="1">
       <c r="A31" s="120"/>
-      <c r="B31" s="813" t="s">
+      <c r="B31" s="863" t="s">
         <v>134</v>
       </c>
-      <c r="C31" s="813"/>
-      <c r="D31" s="813"/>
-      <c r="E31" s="813"/>
-      <c r="F31" s="813"/>
+      <c r="C31" s="863"/>
+      <c r="D31" s="863"/>
+      <c r="E31" s="863"/>
+      <c r="F31" s="863"/>
       <c r="G31" s="218" t="str">
         <f>+G22</f>
         <v>As at 31 March, 2026</v>
@@ -26910,10 +26905,10 @@
     </row>
     <row r="35" spans="1:8" ht="13.95" customHeight="1">
       <c r="A35" s="120"/>
-      <c r="B35" s="839" t="s">
+      <c r="B35" s="806" t="s">
         <v>423</v>
       </c>
-      <c r="C35" s="840"/>
+      <c r="C35" s="807"/>
       <c r="D35" s="321"/>
       <c r="E35" s="321"/>
       <c r="F35" s="322"/>
@@ -27028,10 +27023,10 @@
       <c r="H43" s="305"/>
     </row>
     <row r="44" spans="1:8" ht="13.95" customHeight="1">
-      <c r="B44" s="839" t="s">
+      <c r="B44" s="806" t="s">
         <v>423</v>
       </c>
-      <c r="C44" s="840"/>
+      <c r="C44" s="807"/>
       <c r="D44" s="321"/>
       <c r="E44" s="321"/>
       <c r="F44" s="322"/>
@@ -27070,13 +27065,13 @@
     </row>
     <row r="47" spans="1:8" ht="24" customHeight="1">
       <c r="A47" s="79"/>
-      <c r="B47" s="813" t="s">
+      <c r="B47" s="863" t="s">
         <v>134</v>
       </c>
-      <c r="C47" s="813"/>
-      <c r="D47" s="813"/>
-      <c r="E47" s="813"/>
-      <c r="F47" s="813"/>
+      <c r="C47" s="863"/>
+      <c r="D47" s="863"/>
+      <c r="E47" s="863"/>
+      <c r="F47" s="863"/>
       <c r="G47" s="218" t="str">
         <f>+G31</f>
         <v>As at 31 March, 2026</v>
@@ -27116,10 +27111,10 @@
     </row>
     <row r="50" spans="1:9" ht="13.95" customHeight="1">
       <c r="A50" s="120"/>
-      <c r="B50" s="839" t="s">
+      <c r="B50" s="806" t="s">
         <v>423</v>
       </c>
-      <c r="C50" s="840"/>
+      <c r="C50" s="807"/>
       <c r="D50" s="321"/>
       <c r="E50" s="321"/>
       <c r="F50" s="322"/>
@@ -27158,17 +27153,17 @@
       <c r="I52" s="446"/>
     </row>
     <row r="53" spans="1:9" ht="15" customHeight="1">
-      <c r="A53" s="877" t="str">
+      <c r="A53" s="878" t="str">
         <f>+A1</f>
         <v>KWIKTEAM SUPPORT SERVICES PVT LTD</v>
       </c>
-      <c r="B53" s="877"/>
-      <c r="C53" s="877"/>
-      <c r="D53" s="877"/>
-      <c r="E53" s="877"/>
-      <c r="F53" s="877"/>
-      <c r="G53" s="877"/>
-      <c r="H53" s="877"/>
+      <c r="B53" s="878"/>
+      <c r="C53" s="878"/>
+      <c r="D53" s="878"/>
+      <c r="E53" s="878"/>
+      <c r="F53" s="878"/>
+      <c r="G53" s="878"/>
+      <c r="H53" s="878"/>
       <c r="I53" s="446"/>
     </row>
     <row r="54" spans="1:9" ht="9.9" customHeight="1">
@@ -27183,17 +27178,17 @@
       <c r="I54" s="446"/>
     </row>
     <row r="55" spans="1:9" ht="15" customHeight="1">
-      <c r="A55" s="878" t="str">
+      <c r="A55" s="879" t="str">
         <f>+A3</f>
         <v>Schedules to Balance Sheet as at 31 March, 2026</v>
       </c>
-      <c r="B55" s="878"/>
-      <c r="C55" s="878"/>
-      <c r="D55" s="878"/>
-      <c r="E55" s="878"/>
-      <c r="F55" s="878"/>
-      <c r="G55" s="878"/>
-      <c r="H55" s="878"/>
+      <c r="B55" s="879"/>
+      <c r="C55" s="879"/>
+      <c r="D55" s="879"/>
+      <c r="E55" s="879"/>
+      <c r="F55" s="879"/>
+      <c r="G55" s="879"/>
+      <c r="H55" s="879"/>
       <c r="I55" s="446"/>
     </row>
     <row r="56" spans="1:9" ht="9.9" customHeight="1">
@@ -27226,13 +27221,13 @@
     </row>
     <row r="58" spans="1:9" ht="24" customHeight="1">
       <c r="A58" s="120"/>
-      <c r="B58" s="813" t="s">
+      <c r="B58" s="863" t="s">
         <v>134</v>
       </c>
-      <c r="C58" s="813"/>
-      <c r="D58" s="813"/>
-      <c r="E58" s="813"/>
-      <c r="F58" s="813"/>
+      <c r="C58" s="863"/>
+      <c r="D58" s="863"/>
+      <c r="E58" s="863"/>
+      <c r="F58" s="863"/>
       <c r="G58" s="218" t="str">
         <f>+G47</f>
         <v>As at 31 March, 2026</v>
@@ -27260,13 +27255,13 @@
     </row>
     <row r="60" spans="1:9" ht="15" customHeight="1">
       <c r="A60" s="120"/>
-      <c r="B60" s="883" t="s">
+      <c r="B60" s="886" t="s">
         <v>433</v>
       </c>
-      <c r="C60" s="798"/>
-      <c r="D60" s="798"/>
-      <c r="E60" s="798"/>
-      <c r="F60" s="799"/>
+      <c r="C60" s="797"/>
+      <c r="D60" s="797"/>
+      <c r="E60" s="797"/>
+      <c r="F60" s="798"/>
       <c r="G60" s="162">
         <v>0</v>
       </c>
@@ -27286,10 +27281,10 @@
     </row>
     <row r="62" spans="1:9" ht="13.95" customHeight="1">
       <c r="A62" s="120"/>
-      <c r="B62" s="839" t="s">
+      <c r="B62" s="806" t="s">
         <v>423</v>
       </c>
-      <c r="C62" s="840"/>
+      <c r="C62" s="807"/>
       <c r="D62" s="321"/>
       <c r="E62" s="321"/>
       <c r="F62" s="322"/>
@@ -27326,23 +27321,23 @@
     </row>
     <row r="65" spans="1:9" ht="13.2" customHeight="1">
       <c r="A65" s="120"/>
-      <c r="B65" s="885" t="s">
+      <c r="B65" s="882" t="s">
         <v>134</v>
       </c>
-      <c r="C65" s="884" t="s">
+      <c r="C65" s="881" t="s">
         <v>346</v>
       </c>
-      <c r="D65" s="840"/>
-      <c r="E65" s="840"/>
-      <c r="F65" s="840"/>
-      <c r="G65" s="840"/>
-      <c r="H65" s="847" t="s">
+      <c r="D65" s="807"/>
+      <c r="E65" s="807"/>
+      <c r="F65" s="807"/>
+      <c r="G65" s="807"/>
+      <c r="H65" s="832" t="s">
         <v>310</v>
       </c>
     </row>
     <row r="66" spans="1:9" ht="25.5" customHeight="1">
       <c r="A66" s="120"/>
-      <c r="B66" s="886"/>
+      <c r="B66" s="883"/>
       <c r="C66" s="449" t="s">
         <v>435</v>
       </c>
@@ -27358,7 +27353,7 @@
       <c r="G66" s="450" t="s">
         <v>438</v>
       </c>
-      <c r="H66" s="848"/>
+      <c r="H66" s="833"/>
     </row>
     <row r="67" spans="1:9" ht="24" customHeight="1">
       <c r="A67" s="120"/>
@@ -27483,24 +27478,24 @@
     </row>
     <row r="73" spans="1:9" ht="15" customHeight="1">
       <c r="A73" s="120"/>
-      <c r="B73" s="885" t="s">
+      <c r="B73" s="882" t="s">
         <v>134</v>
       </c>
-      <c r="C73" s="887" t="s">
+      <c r="C73" s="884" t="s">
         <v>346</v>
       </c>
-      <c r="D73" s="880"/>
-      <c r="E73" s="880"/>
-      <c r="F73" s="880"/>
-      <c r="G73" s="880"/>
-      <c r="H73" s="858" t="s">
+      <c r="D73" s="885"/>
+      <c r="E73" s="885"/>
+      <c r="F73" s="885"/>
+      <c r="G73" s="885"/>
+      <c r="H73" s="816" t="s">
         <v>310</v>
       </c>
       <c r="I73" s="23"/>
     </row>
     <row r="74" spans="1:9" ht="25.5" customHeight="1">
       <c r="A74" s="120"/>
-      <c r="B74" s="886"/>
+      <c r="B74" s="883"/>
       <c r="C74" s="461" t="s">
         <v>435</v>
       </c>
@@ -27516,7 +27511,7 @@
       <c r="G74" s="462" t="s">
         <v>438</v>
       </c>
-      <c r="H74" s="859"/>
+      <c r="H74" s="817"/>
       <c r="I74" s="23"/>
     </row>
     <row r="75" spans="1:9" ht="24" customHeight="1">
@@ -27682,13 +27677,13 @@
     </row>
     <row r="84" spans="1:10" ht="24" customHeight="1">
       <c r="A84" s="120"/>
-      <c r="B84" s="813" t="s">
+      <c r="B84" s="863" t="s">
         <v>134</v>
       </c>
-      <c r="C84" s="813"/>
-      <c r="D84" s="813"/>
-      <c r="E84" s="813"/>
-      <c r="F84" s="813"/>
+      <c r="C84" s="863"/>
+      <c r="D84" s="863"/>
+      <c r="E84" s="863"/>
+      <c r="F84" s="863"/>
       <c r="G84" s="218" t="str">
         <f>+G58</f>
         <v>As at 31 March, 2026</v>
@@ -27789,10 +27784,10 @@
     </row>
     <row r="92" spans="1:10" ht="13.95" customHeight="1">
       <c r="A92" s="120"/>
-      <c r="B92" s="839" t="s">
+      <c r="B92" s="806" t="s">
         <v>423</v>
       </c>
-      <c r="C92" s="840"/>
+      <c r="C92" s="807"/>
       <c r="D92" s="321"/>
       <c r="E92" s="321"/>
       <c r="F92" s="322"/>
@@ -27807,13 +27802,13 @@
     </row>
     <row r="93" spans="1:10" ht="12.75" customHeight="1">
       <c r="A93" s="120"/>
-      <c r="B93" s="888"/>
-      <c r="C93" s="798"/>
-      <c r="D93" s="798"/>
-      <c r="E93" s="798"/>
-      <c r="F93" s="798"/>
+      <c r="B93" s="880"/>
+      <c r="C93" s="797"/>
+      <c r="D93" s="797"/>
+      <c r="E93" s="797"/>
+      <c r="F93" s="797"/>
       <c r="G93" s="809"/>
-      <c r="H93" s="798"/>
+      <c r="H93" s="797"/>
     </row>
     <row r="94" spans="1:10" ht="11.4">
       <c r="A94" s="425" t="str">
@@ -27832,13 +27827,13 @@
     </row>
     <row r="95" spans="1:10" ht="24" customHeight="1">
       <c r="A95" s="120"/>
-      <c r="B95" s="813" t="s">
+      <c r="B95" s="863" t="s">
         <v>134</v>
       </c>
-      <c r="C95" s="813"/>
-      <c r="D95" s="813"/>
-      <c r="E95" s="813"/>
-      <c r="F95" s="813"/>
+      <c r="C95" s="863"/>
+      <c r="D95" s="863"/>
+      <c r="E95" s="863"/>
+      <c r="F95" s="863"/>
       <c r="G95" s="218" t="str">
         <f>+G84</f>
         <v>As at 31 March, 2026</v>
@@ -27911,10 +27906,10 @@
     </row>
     <row r="100" spans="1:9" ht="13.95" customHeight="1">
       <c r="A100" s="120"/>
-      <c r="B100" s="839" t="s">
+      <c r="B100" s="806" t="s">
         <v>423</v>
       </c>
-      <c r="C100" s="840"/>
+      <c r="C100" s="807"/>
       <c r="D100" s="321"/>
       <c r="E100" s="321"/>
       <c r="F100" s="322"/>
@@ -27928,30 +27923,30 @@
       </c>
     </row>
     <row r="101" spans="1:9" ht="12" customHeight="1">
-      <c r="A101" s="889"/>
-      <c r="B101" s="798"/>
-      <c r="C101" s="798"/>
-      <c r="D101" s="798"/>
-      <c r="E101" s="798"/>
-      <c r="F101" s="798"/>
+      <c r="A101" s="877"/>
+      <c r="B101" s="797"/>
+      <c r="C101" s="797"/>
+      <c r="D101" s="797"/>
+      <c r="E101" s="797"/>
+      <c r="F101" s="797"/>
       <c r="G101" s="809"/>
-      <c r="H101" s="798"/>
+      <c r="H101" s="797"/>
     </row>
     <row r="102" spans="1:9" ht="12" customHeight="1">
       <c r="A102" s="473"/>
     </row>
     <row r="103" spans="1:9" ht="15" customHeight="1">
-      <c r="A103" s="877" t="str">
+      <c r="A103" s="878" t="str">
         <f>+A53</f>
         <v>KWIKTEAM SUPPORT SERVICES PVT LTD</v>
       </c>
-      <c r="B103" s="877"/>
-      <c r="C103" s="877"/>
-      <c r="D103" s="877"/>
-      <c r="E103" s="877"/>
-      <c r="F103" s="877"/>
-      <c r="G103" s="877"/>
-      <c r="H103" s="877"/>
+      <c r="B103" s="878"/>
+      <c r="C103" s="878"/>
+      <c r="D103" s="878"/>
+      <c r="E103" s="878"/>
+      <c r="F103" s="878"/>
+      <c r="G103" s="878"/>
+      <c r="H103" s="878"/>
       <c r="I103" s="446"/>
     </row>
     <row r="104" spans="1:9" ht="9.9" customHeight="1">
@@ -27966,17 +27961,17 @@
       <c r="I104" s="446"/>
     </row>
     <row r="105" spans="1:9" ht="15" customHeight="1">
-      <c r="A105" s="878" t="str">
+      <c r="A105" s="879" t="str">
         <f>+A55</f>
         <v>Schedules to Balance Sheet as at 31 March, 2026</v>
       </c>
-      <c r="B105" s="878"/>
-      <c r="C105" s="878"/>
-      <c r="D105" s="878"/>
-      <c r="E105" s="878"/>
-      <c r="F105" s="878"/>
-      <c r="G105" s="878"/>
-      <c r="H105" s="878"/>
+      <c r="B105" s="879"/>
+      <c r="C105" s="879"/>
+      <c r="D105" s="879"/>
+      <c r="E105" s="879"/>
+      <c r="F105" s="879"/>
+      <c r="G105" s="879"/>
+      <c r="H105" s="879"/>
       <c r="I105" s="446"/>
     </row>
     <row r="106" spans="1:9" ht="15" customHeight="1">
@@ -28129,10 +28124,10 @@
     </row>
     <row r="116" spans="1:8" ht="13.95" customHeight="1">
       <c r="A116" s="120"/>
-      <c r="B116" s="839" t="s">
+      <c r="B116" s="806" t="s">
         <v>423</v>
       </c>
-      <c r="C116" s="840"/>
+      <c r="C116" s="807"/>
       <c r="D116" s="321"/>
       <c r="E116" s="321"/>
       <c r="F116" s="322"/>
@@ -28146,26 +28141,26 @@
       </c>
     </row>
     <row r="117" spans="1:8" ht="12" customHeight="1">
-      <c r="A117" s="889"/>
-      <c r="B117" s="798"/>
-      <c r="C117" s="798"/>
-      <c r="D117" s="798"/>
-      <c r="E117" s="798"/>
-      <c r="F117" s="798"/>
+      <c r="A117" s="877"/>
+      <c r="B117" s="797"/>
+      <c r="C117" s="797"/>
+      <c r="D117" s="797"/>
+      <c r="E117" s="797"/>
+      <c r="F117" s="797"/>
       <c r="G117" s="809"/>
-      <c r="H117" s="798"/>
+      <c r="H117" s="797"/>
     </row>
     <row r="120" spans="1:8" ht="11.4">
-      <c r="A120" s="863" t="s">
+      <c r="A120" s="808" t="s">
         <v>379</v>
       </c>
-      <c r="B120" s="798"/>
-      <c r="C120" s="798"/>
-      <c r="D120" s="798"/>
-      <c r="E120" s="798"/>
-      <c r="F120" s="798"/>
+      <c r="B120" s="797"/>
+      <c r="C120" s="797"/>
+      <c r="D120" s="797"/>
+      <c r="E120" s="797"/>
+      <c r="F120" s="797"/>
       <c r="G120" s="809"/>
-      <c r="H120" s="798"/>
+      <c r="H120" s="797"/>
     </row>
     <row r="122" spans="1:8" ht="13.2" hidden="1" customHeight="1">
       <c r="A122" s="120"/>
@@ -28179,17 +28174,26 @@
     </row>
   </sheetData>
   <mergeCells count="38">
-    <mergeCell ref="A120:H120"/>
-    <mergeCell ref="A101:H101"/>
-    <mergeCell ref="A103:H103"/>
-    <mergeCell ref="A105:H105"/>
-    <mergeCell ref="B116:C116"/>
-    <mergeCell ref="A117:H117"/>
-    <mergeCell ref="B84:F84"/>
-    <mergeCell ref="B92:C92"/>
-    <mergeCell ref="B93:H93"/>
-    <mergeCell ref="B95:F95"/>
-    <mergeCell ref="B100:C100"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="B16:E16"/>
+    <mergeCell ref="B17:F17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B22:F22"/>
+    <mergeCell ref="B24:E24"/>
+    <mergeCell ref="B25:E25"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B31:F31"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="A53:H53"/>
+    <mergeCell ref="A55:H55"/>
+    <mergeCell ref="B58:F58"/>
+    <mergeCell ref="B60:F60"/>
     <mergeCell ref="B62:C62"/>
     <mergeCell ref="C65:G65"/>
     <mergeCell ref="B65:B66"/>
@@ -28197,26 +28201,17 @@
     <mergeCell ref="C73:G73"/>
     <mergeCell ref="B73:B74"/>
     <mergeCell ref="H73:H74"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="A53:H53"/>
-    <mergeCell ref="A55:H55"/>
-    <mergeCell ref="B58:F58"/>
-    <mergeCell ref="B60:F60"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B31:F31"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B47:F47"/>
-    <mergeCell ref="B17:F17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B22:F22"/>
-    <mergeCell ref="B24:E24"/>
-    <mergeCell ref="B25:E25"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B15:F15"/>
-    <mergeCell ref="B16:E16"/>
+    <mergeCell ref="B84:F84"/>
+    <mergeCell ref="B92:C92"/>
+    <mergeCell ref="B93:H93"/>
+    <mergeCell ref="B95:F95"/>
+    <mergeCell ref="B100:C100"/>
+    <mergeCell ref="A120:H120"/>
+    <mergeCell ref="A101:H101"/>
+    <mergeCell ref="A103:H103"/>
+    <mergeCell ref="A105:H105"/>
+    <mergeCell ref="B116:C116"/>
+    <mergeCell ref="A117:H117"/>
   </mergeCells>
   <conditionalFormatting sqref="G6:H7">
     <cfRule type="cellIs" dxfId="22" priority="9" operator="lessThan">
